--- a/all_generations_pokemon_families.xlsx
+++ b/all_generations_pokemon_families.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3c6863eb3d429a98/Documents/GitHub/pokefirered-expansion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="742" documentId="8_{3DE7B663-32D8-4B09-ACF8-07A7237E0E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48789260-441F-45EA-AFB1-B38B8688DF15}"/>
+  <xr:revisionPtr revIDLastSave="775" documentId="8_{3DE7B663-32D8-4B09-ACF8-07A7237E0E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F82EE78-4464-48E5-931E-8410CA463C16}"/>
   <bookViews>
     <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{913F818F-7E2F-42B8-8FB9-B28A63806581}"/>
   </bookViews>
@@ -4485,9 +4485,9 @@
     <col min="1" max="1" width="11.90625" bestFit="1" customWidth="1"/>
     <col min="2" max="8" width="8.7265625" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="8.7265625" customWidth="1"/>
-    <col min="10" max="11" width="13.6328125" hidden="1" customWidth="1"/>
+    <col min="10" max="11" width="13.6328125" customWidth="1"/>
     <col min="12" max="13" width="8.7265625" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="27.6328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="27.6328125" hidden="1" customWidth="1"/>
     <col min="15" max="15" width="25.36328125" hidden="1" customWidth="1"/>
     <col min="16" max="16" width="12.36328125" bestFit="1" customWidth="1"/>
   </cols>
@@ -4542,7 +4542,7 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>41</v>
       </c>
@@ -4592,7 +4592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>779</v>
       </c>
@@ -4742,7 +4742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>79</v>
       </c>
@@ -4792,7 +4792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>114</v>
       </c>
@@ -4842,7 +4842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>46</v>
       </c>
@@ -4892,7 +4892,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>84</v>
       </c>
@@ -4942,7 +4942,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>84</v>
       </c>
@@ -4992,7 +4992,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>573</v>
       </c>
@@ -5042,7 +5042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>136</v>
       </c>
@@ -5092,7 +5092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>515</v>
       </c>
@@ -5292,7 +5292,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>735</v>
       </c>
@@ -5342,7 +5342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>739</v>
       </c>
@@ -5392,7 +5392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>1039</v>
       </c>
@@ -5892,7 +5892,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>1045</v>
       </c>
@@ -5942,7 +5942,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>55</v>
       </c>
@@ -5992,7 +5992,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>535</v>
       </c>
@@ -6042,7 +6042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>653</v>
       </c>
@@ -6092,7 +6092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>657</v>
       </c>
@@ -6142,7 +6142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>771</v>
       </c>
@@ -6192,7 +6192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>101</v>
       </c>
@@ -6242,7 +6242,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>108</v>
       </c>
@@ -6292,7 +6292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>527</v>
       </c>
@@ -6342,7 +6342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>552</v>
       </c>
@@ -6442,7 +6442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>813</v>
       </c>
@@ -6492,7 +6492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>1090</v>
       </c>
@@ -6542,7 +6542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>1053</v>
       </c>
@@ -6592,7 +6592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>857</v>
       </c>
@@ -6642,7 +6642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>1131</v>
       </c>
@@ -6692,7 +6692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>782</v>
       </c>
@@ -6742,7 +6742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>782</v>
       </c>
@@ -6792,7 +6792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>798</v>
       </c>
@@ -6842,7 +6842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>519</v>
       </c>
@@ -7142,7 +7142,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>606</v>
       </c>
@@ -7192,7 +7192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>91</v>
       </c>
@@ -7242,7 +7242,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>91</v>
       </c>
@@ -7542,7 +7542,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>122</v>
       </c>
@@ -7592,7 +7592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>152</v>
       </c>
@@ -7692,7 +7692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>220</v>
       </c>
@@ -8242,7 +8242,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>230</v>
       </c>
@@ -8292,7 +8292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>230</v>
       </c>
@@ -8392,7 +8392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>430</v>
       </c>
@@ -8442,7 +8442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>486</v>
       </c>
@@ -8542,7 +8542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>581</v>
       </c>
@@ -8592,7 +8592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>705</v>
       </c>
@@ -8642,7 +8642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>739</v>
       </c>
@@ -8742,7 +8742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>793</v>
       </c>
@@ -8792,7 +8792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>804</v>
       </c>
@@ -8842,7 +8842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>804</v>
       </c>
@@ -8892,7 +8892,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>819</v>
       </c>
@@ -8942,7 +8942,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>841</v>
       </c>
@@ -8992,7 +8992,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>845</v>
       </c>
@@ -9042,7 +9042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>887</v>
       </c>
@@ -9092,7 +9092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>917</v>
       </c>
@@ -9142,7 +9142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>942</v>
       </c>
@@ -9192,7 +9192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>946</v>
       </c>
@@ -9242,7 +9242,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>961</v>
       </c>
@@ -9292,7 +9292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>961</v>
       </c>
@@ -9342,7 +9342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>968</v>
       </c>
@@ -9392,7 +9392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>992</v>
       </c>
@@ -9442,7 +9442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>1117</v>
       </c>
@@ -9492,7 +9492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>1125</v>
       </c>
@@ -9542,7 +9542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>1143</v>
       </c>
@@ -9592,7 +9592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>863</v>
       </c>
@@ -9642,7 +9642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>48</v>
       </c>
@@ -9692,7 +9692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>156</v>
       </c>
@@ -9742,7 +9742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>179</v>
       </c>
@@ -9792,7 +9792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>214</v>
       </c>
@@ -9892,7 +9892,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>546</v>
       </c>
@@ -9942,7 +9942,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>875</v>
       </c>
@@ -10242,7 +10242,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>26</v>
       </c>
@@ -10292,7 +10292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>502</v>
       </c>
@@ -10342,7 +10342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>1027</v>
       </c>
@@ -10392,7 +10392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>207</v>
       </c>
@@ -10442,7 +10442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>270</v>
       </c>
@@ -10492,7 +10492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>288</v>
       </c>
@@ -10542,7 +10542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>384</v>
       </c>
@@ -10592,7 +10592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>384</v>
       </c>
@@ -10642,7 +10642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>717</v>
       </c>
@@ -10692,7 +10692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>723</v>
       </c>
@@ -10942,7 +10942,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>897</v>
       </c>
@@ -11542,7 +11542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="142" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>245</v>
       </c>
@@ -11592,7 +11592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="143" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>245</v>
       </c>
@@ -11642,7 +11642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="144" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>15</v>
       </c>
@@ -11692,7 +11692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="145" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>496</v>
       </c>
@@ -11742,7 +11742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="146" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>1021</v>
       </c>
@@ -11942,7 +11942,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="150" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>319</v>
       </c>
@@ -11992,7 +11992,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="151" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>319</v>
       </c>
@@ -12042,7 +12042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="152" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>319</v>
       </c>
@@ -12092,7 +12092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="153" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>542</v>
       </c>
@@ -12142,7 +12142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="154" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>119</v>
       </c>
@@ -12192,7 +12192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="155" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>256</v>
       </c>
@@ -12242,7 +12242,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="156" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>313</v>
       </c>
@@ -12292,7 +12292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="157" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>313</v>
       </c>
@@ -12342,7 +12342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="158" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>432</v>
       </c>
@@ -12392,7 +12392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="159" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>432</v>
       </c>
@@ -12442,7 +12442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="160" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>432</v>
       </c>
@@ -12492,7 +12492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="161" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>432</v>
       </c>
@@ -12542,7 +12542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="162" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>432</v>
       </c>
@@ -12992,7 +12992,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="171" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>432</v>
       </c>
@@ -13042,7 +13042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="172" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>432</v>
       </c>
@@ -13092,7 +13092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="173" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>432</v>
       </c>
@@ -13192,7 +13192,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="175" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>432</v>
       </c>
@@ -13242,7 +13242,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="176" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>432</v>
       </c>
@@ -13292,7 +13292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="177" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>299</v>
       </c>
@@ -13542,7 +13542,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="182" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>1113</v>
       </c>
@@ -13592,7 +13592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="183" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>307</v>
       </c>
@@ -13642,7 +13642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="184" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>307</v>
       </c>
@@ -13742,7 +13742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="186" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>682</v>
       </c>
@@ -13792,7 +13792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="187" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>686</v>
       </c>
@@ -13942,7 +13942,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="190" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>835</v>
       </c>
@@ -13992,7 +13992,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="191" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>881</v>
       </c>
@@ -14092,7 +14092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="193" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>1135</v>
       </c>
@@ -14142,7 +14142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="194" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>1139</v>
       </c>
@@ -14192,7 +14192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="195" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>1153</v>
       </c>
@@ -14292,7 +14292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="197" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>893</v>
       </c>
@@ -14342,7 +14342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="198" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>310</v>
       </c>
@@ -14392,7 +14392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="199" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>310</v>
       </c>
@@ -14442,7 +14442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="200" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>342</v>
       </c>
@@ -14592,7 +14592,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="203" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>342</v>
       </c>
@@ -14742,7 +14742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="206" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>890</v>
       </c>
@@ -14792,7 +14792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="207" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>1042</v>
       </c>
@@ -14842,7 +14842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="208" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>347</v>
       </c>
@@ -15442,7 +15442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="220" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>1101</v>
       </c>
@@ -15492,7 +15492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="221" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>59</v>
       </c>
@@ -15542,7 +15542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="222" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>189</v>
       </c>
@@ -15592,7 +15592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="223" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>189</v>
       </c>
@@ -15642,7 +15642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="224" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>1059</v>
       </c>
@@ -15692,7 +15692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="225" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>1063</v>
       </c>
@@ -15742,7 +15742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="226" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>1105</v>
       </c>
@@ -15792,7 +15792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="227" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>463</v>
       </c>
@@ -15842,7 +15842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="228" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>467</v>
       </c>
@@ -15892,7 +15892,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="229" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>921</v>
       </c>
@@ -15942,7 +15942,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="230" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>925</v>
       </c>
@@ -15992,7 +15992,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="231" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>403</v>
       </c>
@@ -16042,7 +16042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="232" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>812</v>
       </c>
@@ -16092,7 +16092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="233" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>1056</v>
       </c>
@@ -16142,7 +16142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="234" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>104</v>
       </c>
@@ -16192,7 +16192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="235" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>111</v>
       </c>
@@ -16292,7 +16292,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="237" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>410</v>
       </c>
@@ -16342,7 +16342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="238" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>549</v>
       </c>
@@ -16442,7 +16442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="240" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>522</v>
       </c>
@@ -16492,7 +16492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="241" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>816</v>
       </c>
@@ -16642,7 +16642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="244" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>294</v>
       </c>
@@ -16692,7 +16692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="245" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>121</v>
       </c>
@@ -16742,7 +16742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="246" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>223</v>
       </c>
@@ -16792,7 +16792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="247" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>233</v>
       </c>
@@ -16842,7 +16842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="248" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>233</v>
       </c>
@@ -16892,7 +16892,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="249" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>233</v>
       </c>
@@ -16942,7 +16942,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="250" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>233</v>
       </c>
@@ -16992,7 +16992,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="251" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>473</v>
       </c>
@@ -17042,7 +17042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="252" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>455</v>
       </c>
@@ -17092,7 +17092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="253" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>210</v>
       </c>
@@ -17142,7 +17142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="254" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>210</v>
       </c>
@@ -17192,7 +17192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="255" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>656</v>
       </c>
@@ -17242,7 +17242,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="256" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>860</v>
       </c>
@@ -17342,7 +17342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="258" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>22</v>
       </c>
@@ -17392,7 +17392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="259" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>30</v>
       </c>
@@ -17492,7 +17492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="261" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>213</v>
       </c>
@@ -17542,7 +17542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="262" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>217</v>
       </c>
@@ -17592,7 +17592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="263" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>217</v>
       </c>
@@ -17642,7 +17642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="264" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>291</v>
       </c>
@@ -17692,7 +17692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="265" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>291</v>
       </c>
@@ -17742,7 +17742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="266" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>499</v>
       </c>
@@ -17792,7 +17792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="267" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>505</v>
       </c>
@@ -17842,7 +17842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="268" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>505</v>
       </c>
@@ -17942,7 +17942,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="270" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>588</v>
       </c>
@@ -17992,7 +17992,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="271" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>720</v>
       </c>
@@ -18042,7 +18042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="272" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>726</v>
       </c>
@@ -18242,7 +18242,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="276" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>1024</v>
       </c>
@@ -18292,7 +18292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="277" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>1030</v>
       </c>
@@ -18392,7 +18392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="279" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>708</v>
       </c>
@@ -18442,7 +18442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="280" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>971</v>
       </c>
@@ -18492,7 +18492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="281" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>1048</v>
       </c>
@@ -18542,7 +18542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="282" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>1128</v>
       </c>
@@ -18642,7 +18642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="284" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
         <v>489</v>
       </c>
@@ -18692,7 +18692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="285" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>995</v>
       </c>
@@ -18742,7 +18742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="286" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>518</v>
       </c>
@@ -18792,7 +18792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="287" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
         <v>538</v>
       </c>
@@ -18842,7 +18842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="288" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>833</v>
       </c>
@@ -18892,7 +18892,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="289" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>618</v>
       </c>
@@ -19292,7 +19292,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="297" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>618</v>
       </c>
@@ -19342,7 +19342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="298" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>637</v>
       </c>
@@ -19492,7 +19492,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="301" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
         <v>637</v>
       </c>
@@ -19542,7 +19542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="302" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
         <v>637</v>
       </c>
@@ -19592,7 +19592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="303" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
         <v>637</v>
       </c>
@@ -19642,7 +19642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="304" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
         <v>838</v>
       </c>
@@ -19692,7 +19692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="305" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
         <v>362</v>
       </c>
@@ -19742,7 +19742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="306" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
         <v>432</v>
       </c>
@@ -19792,7 +19792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="307" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
         <v>593</v>
       </c>
@@ -19992,7 +19992,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="311" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
         <v>801</v>
       </c>
@@ -20042,7 +20042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="312" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
         <v>95</v>
       </c>
@@ -20092,7 +20092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="313" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
         <v>95</v>
       </c>
@@ -20142,7 +20142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="314" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
         <v>159</v>
       </c>
@@ -20392,7 +20392,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="319" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
         <v>530</v>
       </c>
@@ -20442,7 +20442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="320" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
         <v>660</v>
       </c>
@@ -20492,7 +20492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="321" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
         <v>1093</v>
       </c>
@@ -20792,7 +20792,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="327" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
         <v>1093</v>
       </c>
@@ -20842,7 +20842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="328" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
         <v>139</v>
       </c>
@@ -20892,7 +20892,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="329" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
         <v>183</v>
       </c>
@@ -20942,7 +20942,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="330" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
         <v>811</v>
       </c>
@@ -20992,7 +20992,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="331" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
         <v>389</v>
       </c>
@@ -21042,7 +21042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="332" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
         <v>389</v>
       </c>
@@ -21092,7 +21092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="333" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
         <v>742</v>
       </c>
@@ -21142,7 +21142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="334" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
         <v>742</v>
       </c>
@@ -21442,7 +21442,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="340" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
         <v>844</v>
       </c>
@@ -21492,7 +21492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="341" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
         <v>905</v>
       </c>
@@ -21542,7 +21542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="342" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
         <v>907</v>
       </c>
@@ -21592,7 +21592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="343" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
         <v>953</v>
       </c>
@@ -21642,7 +21642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="344" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
         <v>155</v>
       </c>
@@ -21992,7 +21992,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="351" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
         <v>324</v>
       </c>
@@ -22042,7 +22042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="352" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
         <v>324</v>
       </c>
@@ -22092,7 +22092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="353" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
         <v>273</v>
       </c>
@@ -22142,7 +22142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="354" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
         <v>738</v>
       </c>
@@ -22192,7 +22192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="355" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
         <v>884</v>
       </c>
@@ -22292,7 +22292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="357" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
         <v>587</v>
       </c>
@@ -22492,7 +22492,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="361" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
         <v>601</v>
       </c>
@@ -22542,7 +22542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="362" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
         <v>774</v>
       </c>
@@ -22592,7 +22592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="363" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
         <v>848</v>
       </c>
@@ -22642,7 +22642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="364" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
         <v>879</v>
       </c>
@@ -22692,7 +22692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="365" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
         <v>945</v>
       </c>
@@ -22742,7 +22742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="366" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
         <v>949</v>
       </c>
@@ -22792,7 +22792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="367" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
         <v>61</v>
       </c>
@@ -22842,7 +22842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="368" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
         <v>1116</v>
       </c>
@@ -22892,7 +22892,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="369" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
         <v>259</v>
       </c>
@@ -22942,7 +22942,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="370" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
         <v>259</v>
       </c>
@@ -23042,7 +23042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="372" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
         <v>680</v>
       </c>
@@ -23142,7 +23142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="374" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
         <v>1108</v>
       </c>
@@ -23242,7 +23242,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="376" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
         <v>822</v>
       </c>
@@ -23292,7 +23292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="377" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
         <v>350</v>
       </c>
@@ -23342,7 +23342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="378" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
         <v>878</v>
       </c>
@@ -23392,7 +23392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="379" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
         <v>896</v>
       </c>
@@ -23442,7 +23442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="380" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
         <v>1044</v>
       </c>
@@ -23492,7 +23492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="381" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
         <v>1123</v>
       </c>
@@ -23542,7 +23542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="382" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
         <v>346</v>
       </c>
@@ -23592,7 +23592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="383" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
         <v>367</v>
       </c>
@@ -23642,7 +23642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="384" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
         <v>406</v>
       </c>
@@ -23742,7 +23742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="386" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
         <v>697</v>
       </c>
@@ -24092,7 +24092,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="393" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
         <v>797</v>
       </c>
@@ -24142,7 +24142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="394" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
         <v>302</v>
       </c>
@@ -24192,7 +24192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="395" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
         <v>413</v>
       </c>
@@ -24392,7 +24392,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="399" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
         <v>466</v>
       </c>
@@ -24442,7 +24442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="400" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
         <v>470</v>
       </c>
@@ -24492,7 +24492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="401" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
         <v>596</v>
       </c>
@@ -24542,7 +24542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="402" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
         <v>866</v>
       </c>
@@ -24592,7 +24592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="403" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
         <v>924</v>
       </c>
@@ -24642,7 +24642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="404" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
         <v>928</v>
       </c>
@@ -24692,7 +24692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="405" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
         <v>1062</v>
       </c>
@@ -24742,7 +24742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="406" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
         <v>1066</v>
       </c>
@@ -24942,7 +24942,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="410" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
         <v>1104</v>
       </c>
@@ -24992,7 +24992,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="411" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
         <v>89</v>
       </c>
@@ -25042,7 +25042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="412" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
         <v>89</v>
       </c>
@@ -25142,7 +25142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="414" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
         <v>293</v>
       </c>
@@ -25192,7 +25192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="415" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
         <v>392</v>
       </c>
@@ -25242,7 +25242,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="416" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
         <v>392</v>
       </c>
@@ -25292,7 +25292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="417" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
         <v>397</v>
       </c>
@@ -25342,7 +25342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="418" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
         <v>398</v>
       </c>
@@ -25392,7 +25392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="419" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
         <v>545</v>
       </c>
@@ -25442,7 +25442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="420" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
         <v>609</v>
       </c>
@@ -25492,7 +25492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="421" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
         <v>635</v>
       </c>
@@ -25542,7 +25542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="422" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
         <v>685</v>
       </c>
@@ -25592,7 +25592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="423" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
         <v>689</v>
       </c>
@@ -26042,7 +26042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="432" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
         <v>920</v>
       </c>
@@ -26092,7 +26092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="433" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
         <v>1120</v>
       </c>
@@ -26142,7 +26142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="434" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
         <v>1142</v>
       </c>
@@ -26192,7 +26192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="435" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
         <v>1146</v>
       </c>
@@ -26242,7 +26242,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="436" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
         <v>1156</v>
       </c>
@@ -26292,7 +26292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="437" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
         <v>107</v>
       </c>
@@ -26542,7 +26542,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="442" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
         <v>113</v>
       </c>
@@ -26592,7 +26592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="443" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
         <v>126</v>
       </c>
@@ -26642,7 +26642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="444" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
         <v>633</v>
       </c>
@@ -26692,7 +26692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="445" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
         <v>862</v>
       </c>
@@ -26942,7 +26942,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="450" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
         <v>235</v>
       </c>
@@ -26992,7 +26992,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="451" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
         <v>235</v>
       </c>
@@ -27142,7 +27142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="454" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
         <v>249</v>
       </c>
@@ -27192,7 +27192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="455" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
         <v>250</v>
       </c>
@@ -27292,7 +27292,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="457" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
         <v>298</v>
       </c>
@@ -27342,7 +27342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="458" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
         <v>641</v>
       </c>
@@ -27392,7 +27392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="459" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
         <v>644</v>
       </c>
@@ -27442,7 +27442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="460" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
         <v>900</v>
       </c>
@@ -27492,7 +27492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="461" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
         <v>966</v>
       </c>
@@ -27542,7 +27542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="462" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
         <v>967</v>
       </c>
@@ -27942,7 +27942,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="470" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
         <v>459</v>
       </c>
@@ -27992,7 +27992,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="471" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
         <v>471</v>
       </c>
@@ -28042,7 +28042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="472" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
         <v>592</v>
       </c>
@@ -28092,7 +28092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="473" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
         <v>787</v>
       </c>
@@ -28142,7 +28142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="474" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
         <v>788</v>
       </c>
@@ -28192,7 +28192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="475" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
         <v>225</v>
       </c>
@@ -28242,7 +28242,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="476" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
         <v>317</v>
       </c>
@@ -28292,7 +28292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="477" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
         <v>317</v>
       </c>
@@ -28392,7 +28392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="479" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
         <v>391</v>
       </c>
@@ -28442,7 +28442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="480" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
         <v>551</v>
       </c>
@@ -28742,7 +28742,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="486" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
         <v>605</v>
       </c>
@@ -28792,7 +28792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="487" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
         <v>746</v>
       </c>
@@ -28842,7 +28842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="488" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
         <v>818</v>
       </c>
@@ -28892,7 +28892,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="489" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
         <v>892</v>
       </c>
@@ -28942,7 +28942,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="490" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
         <v>1058</v>
       </c>
@@ -28992,7 +28992,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="491" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
         <v>24</v>
       </c>
@@ -29192,7 +29192,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="495" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
         <v>219</v>
       </c>
@@ -29342,7 +29342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="498" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
         <v>448</v>
       </c>
@@ -29392,7 +29392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="499" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
         <v>449</v>
       </c>
@@ -29442,7 +29442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="500" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
         <v>450</v>
       </c>
@@ -29492,7 +29492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="501" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
         <v>451</v>
       </c>
@@ -29542,7 +29542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="502" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
         <v>452</v>
       </c>
@@ -29592,7 +29592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="503" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
         <v>453</v>
       </c>
@@ -29642,7 +29642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="504" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
         <v>501</v>
       </c>
@@ -29692,7 +29692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="505" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
         <v>622</v>
       </c>
@@ -29992,7 +29992,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="511" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
         <v>952</v>
       </c>
@@ -30042,7 +30042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="512" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
         <v>1026</v>
       </c>
@@ -30092,7 +30092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="513" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
         <v>1134</v>
       </c>
@@ -30142,7 +30142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="514" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
         <v>1138</v>
       </c>
@@ -30292,7 +30292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="517" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
         <v>662</v>
       </c>
@@ -30342,7 +30342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="518" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
         <v>722</v>
       </c>
@@ -30392,7 +30392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="519" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
         <v>728</v>
       </c>
@@ -30442,7 +30442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="520" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
         <v>840</v>
       </c>
@@ -30492,7 +30492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="521" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
         <v>973</v>
       </c>
@@ -30592,7 +30592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="523" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
         <v>32</v>
       </c>
@@ -30642,7 +30642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="524" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
         <v>508</v>
       </c>
@@ -30692,7 +30692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="525" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
         <v>508</v>
       </c>
@@ -30742,7 +30742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="526" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
         <v>1032</v>
       </c>
@@ -30792,7 +30792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="527" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
         <v>141</v>
       </c>
@@ -30842,7 +30842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="528" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
         <v>187</v>
       </c>
@@ -30892,7 +30892,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="529" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
         <v>353</v>
       </c>
@@ -30942,7 +30942,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="530" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
         <v>366</v>
       </c>
@@ -31042,7 +31042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="532" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
         <v>462</v>
       </c>
@@ -31192,7 +31192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="535" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
         <v>409</v>
       </c>
@@ -31242,7 +31242,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="536" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
         <v>416</v>
       </c>
@@ -31292,7 +31292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="537" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
         <v>476</v>
       </c>
@@ -31342,7 +31342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="538" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
         <v>576</v>
       </c>
@@ -31442,7 +31442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="540" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
         <v>263</v>
       </c>
@@ -31592,7 +31592,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="543" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
         <v>541</v>
       </c>
@@ -31642,7 +31642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="544" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
         <v>193</v>
       </c>
@@ -31692,7 +31692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="545" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
         <v>193</v>
       </c>
@@ -31742,7 +31742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="546" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
         <v>477</v>
       </c>
@@ -31792,7 +31792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="547" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
         <v>477</v>
       </c>
@@ -31842,7 +31842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="548" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
         <v>480</v>
       </c>
@@ -31892,7 +31892,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="549" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
         <v>480</v>
       </c>
@@ -32542,7 +32542,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="562" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
         <v>483</v>
       </c>
@@ -32592,7 +32592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="563" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
         <v>483</v>
       </c>
@@ -32642,7 +32642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="564" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
         <v>699</v>
       </c>
@@ -32692,7 +32692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="565" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
         <v>701</v>
       </c>
@@ -32992,7 +32992,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="571" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
         <v>998</v>
       </c>
@@ -33042,7 +33042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="572" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
         <v>1000</v>
       </c>
@@ -33092,7 +33092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="573" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A573" t="s">
         <v>1002</v>
       </c>
@@ -33142,7 +33142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="574" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A574" t="s">
         <v>1164</v>
       </c>
@@ -33292,7 +33292,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="577" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A577" t="s">
         <v>1166</v>
       </c>
@@ -33342,7 +33342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="578" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A578" t="s">
         <v>1168</v>
       </c>
@@ -33392,7 +33392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="579" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A579" t="s">
         <v>491</v>
       </c>
@@ -33442,7 +33442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="580" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A580" t="s">
         <v>494</v>
       </c>
@@ -33542,7 +33542,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="582" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A582" t="s">
         <v>710</v>
       </c>
@@ -33592,7 +33592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="583" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A583" t="s">
         <v>715</v>
       </c>
@@ -33642,7 +33642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="584" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A584" t="s">
         <v>997</v>
       </c>
@@ -33692,7 +33692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="585" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A585" t="s">
         <v>1004</v>
       </c>
@@ -33742,7 +33742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="586" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A586" t="s">
         <v>1006</v>
       </c>
@@ -33792,7 +33792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="587" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A587" t="s">
         <v>1014</v>
       </c>
@@ -33842,7 +33842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="588" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A588" t="s">
         <v>1016</v>
       </c>
@@ -33892,7 +33892,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="589" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A589" t="s">
         <v>1016</v>
       </c>
@@ -33942,7 +33942,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="590" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="590" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A590" t="s">
         <v>1016</v>
       </c>
@@ -33992,7 +33992,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="591" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="591" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A591" t="s">
         <v>1016</v>
       </c>
@@ -34042,7 +34042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="592" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A592" t="s">
         <v>1130</v>
       </c>
@@ -34092,7 +34092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="593" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="593" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A593" t="s">
         <v>1176</v>
       </c>
@@ -34292,7 +34292,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="597" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="597" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A597" t="s">
         <v>1183</v>
       </c>
@@ -34692,7 +34692,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="605" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="605" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A605" t="s">
         <v>1189</v>
       </c>
@@ -34742,7 +34742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="606" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="606" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A606" t="s">
         <v>1191</v>
       </c>
@@ -34792,7 +34792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="607" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="607" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A607" t="s">
         <v>1191</v>
       </c>
@@ -34842,7 +34842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="608" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="608" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A608" t="s">
         <v>803</v>
       </c>
@@ -34942,7 +34942,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="610" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="610" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A610" t="s">
         <v>1010</v>
       </c>
@@ -34992,7 +34992,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="611" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="611" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A611" t="s">
         <v>1178</v>
       </c>
@@ -35042,7 +35042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="612" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="612" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A612" t="s">
         <v>492</v>
       </c>
@@ -35092,7 +35092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="613" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="613" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A613" t="s">
         <v>711</v>
       </c>
@@ -35142,7 +35142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="614" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="614" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A614" t="s">
         <v>713</v>
       </c>
@@ -35192,7 +35192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="615" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="615" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A615" t="s">
         <v>1012</v>
       </c>
@@ -35242,7 +35242,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="616" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="616" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A616" t="s">
         <v>1170</v>
       </c>
@@ -35292,7 +35292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="617" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="617" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A617" t="s">
         <v>1170</v>
       </c>
@@ -35442,7 +35442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="620" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="620" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A620" t="s">
         <v>1180</v>
       </c>
@@ -35492,7 +35492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="621" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="621" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A621" t="s">
         <v>1180</v>
       </c>
@@ -35544,6 +35544,11 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:P621" xr:uid="{6A7ECD2C-6F5B-4E4D-962E-4B55F2FEEDC6}">
+    <filterColumn colId="9">
+      <filters>
+        <filter val="TYPE_WATER"/>
+      </filters>
+    </filterColumn>
     <filterColumn colId="15">
       <filters>
         <filter val="Y"/>

--- a/all_generations_pokemon_families.xlsx
+++ b/all_generations_pokemon_families.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3c6863eb3d429a98/Documents/GitHub/pokefirered-expansion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="775" documentId="8_{3DE7B663-32D8-4B09-ACF8-07A7237E0E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F82EE78-4464-48E5-931E-8410CA463C16}"/>
+  <xr:revisionPtr revIDLastSave="778" documentId="8_{3DE7B663-32D8-4B09-ACF8-07A7237E0E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F18E100-9E3F-410E-B464-42AE4650C295}"/>
   <bookViews>
     <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{913F818F-7E2F-42B8-8FB9-B28A63806581}"/>
   </bookViews>
@@ -4542,7 +4542,7 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="2" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>41</v>
       </c>
@@ -4592,7 +4592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="3" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>779</v>
       </c>
@@ -4742,7 +4742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="6" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>79</v>
       </c>
@@ -4792,7 +4792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="7" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>114</v>
       </c>
@@ -4842,7 +4842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="8" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>46</v>
       </c>
@@ -4892,7 +4892,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="9" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>84</v>
       </c>
@@ -4942,7 +4942,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="10" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>84</v>
       </c>
@@ -4992,7 +4992,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="11" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>573</v>
       </c>
@@ -5042,7 +5042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="12" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>136</v>
       </c>
@@ -5092,7 +5092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="13" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>515</v>
       </c>
@@ -5292,7 +5292,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="17" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>735</v>
       </c>
@@ -5342,7 +5342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="18" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>739</v>
       </c>
@@ -5392,7 +5392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="19" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>1039</v>
       </c>
@@ -5892,7 +5892,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="29" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>1045</v>
       </c>
@@ -5942,7 +5942,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="30" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>55</v>
       </c>
@@ -5992,7 +5992,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="31" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>535</v>
       </c>
@@ -6042,7 +6042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="32" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>653</v>
       </c>
@@ -6092,7 +6092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="33" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>657</v>
       </c>
@@ -6142,7 +6142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="34" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>771</v>
       </c>
@@ -6192,7 +6192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="35" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>101</v>
       </c>
@@ -6242,7 +6242,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="36" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>108</v>
       </c>
@@ -6292,7 +6292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="37" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>527</v>
       </c>
@@ -6342,7 +6342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="38" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>552</v>
       </c>
@@ -6442,7 +6442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="40" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>813</v>
       </c>
@@ -6492,7 +6492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="41" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>1090</v>
       </c>
@@ -6542,7 +6542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="42" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>1053</v>
       </c>
@@ -6592,7 +6592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="43" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>857</v>
       </c>
@@ -6642,7 +6642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="44" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>1131</v>
       </c>
@@ -6692,7 +6692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="45" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>782</v>
       </c>
@@ -6742,7 +6742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="46" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>782</v>
       </c>
@@ -6792,7 +6792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="47" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>798</v>
       </c>
@@ -6842,7 +6842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="48" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>519</v>
       </c>
@@ -7142,7 +7142,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="54" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>606</v>
       </c>
@@ -7192,7 +7192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>91</v>
       </c>
@@ -7242,7 +7242,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="56" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>91</v>
       </c>
@@ -7542,7 +7542,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="62" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>122</v>
       </c>
@@ -7592,7 +7592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="63" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>152</v>
       </c>
@@ -7692,7 +7692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="65" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>220</v>
       </c>
@@ -8242,7 +8242,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="76" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>230</v>
       </c>
@@ -8292,7 +8292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="77" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>230</v>
       </c>
@@ -8392,7 +8392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="79" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>430</v>
       </c>
@@ -8442,7 +8442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="80" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>486</v>
       </c>
@@ -8542,7 +8542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="82" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>581</v>
       </c>
@@ -8592,7 +8592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="83" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>705</v>
       </c>
@@ -8642,7 +8642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="84" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>739</v>
       </c>
@@ -8742,7 +8742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="86" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>793</v>
       </c>
@@ -8792,7 +8792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="87" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>804</v>
       </c>
@@ -8842,7 +8842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="88" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>804</v>
       </c>
@@ -8892,7 +8892,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="89" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>819</v>
       </c>
@@ -8942,7 +8942,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="90" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>841</v>
       </c>
@@ -8992,7 +8992,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="91" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>845</v>
       </c>
@@ -9042,7 +9042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="92" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>887</v>
       </c>
@@ -9092,7 +9092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="93" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>917</v>
       </c>
@@ -9142,7 +9142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="94" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>942</v>
       </c>
@@ -9192,7 +9192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="95" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>946</v>
       </c>
@@ -9242,7 +9242,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="96" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>961</v>
       </c>
@@ -9292,7 +9292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="97" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>961</v>
       </c>
@@ -9342,7 +9342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="98" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>968</v>
       </c>
@@ -9392,7 +9392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="99" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>992</v>
       </c>
@@ -9442,7 +9442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="100" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>1117</v>
       </c>
@@ -9492,7 +9492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="101" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>1125</v>
       </c>
@@ -9542,7 +9542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="102" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>1143</v>
       </c>
@@ -9592,7 +9592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="103" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>863</v>
       </c>
@@ -9642,7 +9642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="104" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>48</v>
       </c>
@@ -9692,7 +9692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="105" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>156</v>
       </c>
@@ -9742,7 +9742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="106" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>179</v>
       </c>
@@ -9792,7 +9792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="107" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>214</v>
       </c>
@@ -9892,7 +9892,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="109" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>546</v>
       </c>
@@ -9942,7 +9942,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="110" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>875</v>
       </c>
@@ -10242,7 +10242,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="116" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>26</v>
       </c>
@@ -10292,7 +10292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="117" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>502</v>
       </c>
@@ -10342,7 +10342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="118" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>1027</v>
       </c>
@@ -10392,7 +10392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="119" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>207</v>
       </c>
@@ -10442,7 +10442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="120" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>270</v>
       </c>
@@ -10492,7 +10492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="121" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>288</v>
       </c>
@@ -10542,7 +10542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="122" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>384</v>
       </c>
@@ -10592,7 +10592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="123" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>384</v>
       </c>
@@ -10642,7 +10642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="124" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>717</v>
       </c>
@@ -10692,7 +10692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="125" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>723</v>
       </c>
@@ -10942,7 +10942,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="130" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>897</v>
       </c>
@@ -11542,7 +11542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="142" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>245</v>
       </c>
@@ -11592,7 +11592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="143" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>245</v>
       </c>
@@ -11642,7 +11642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="144" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>15</v>
       </c>
@@ -11692,7 +11692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="145" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>496</v>
       </c>
@@ -11742,7 +11742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="146" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>1021</v>
       </c>
@@ -11942,7 +11942,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="150" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>319</v>
       </c>
@@ -11992,7 +11992,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="151" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>319</v>
       </c>
@@ -12042,7 +12042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="152" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>319</v>
       </c>
@@ -12092,7 +12092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="153" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>542</v>
       </c>
@@ -12142,7 +12142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="154" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>119</v>
       </c>
@@ -12192,7 +12192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="155" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>256</v>
       </c>
@@ -12242,7 +12242,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="156" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>313</v>
       </c>
@@ -12292,7 +12292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="157" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>313</v>
       </c>
@@ -12342,7 +12342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="158" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>432</v>
       </c>
@@ -12392,7 +12392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="159" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>432</v>
       </c>
@@ -12442,7 +12442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="160" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>432</v>
       </c>
@@ -12492,7 +12492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="161" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>432</v>
       </c>
@@ -12542,7 +12542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="162" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>432</v>
       </c>
@@ -12992,7 +12992,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="171" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>432</v>
       </c>
@@ -13042,7 +13042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="172" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>432</v>
       </c>
@@ -13092,7 +13092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="173" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>432</v>
       </c>
@@ -13192,7 +13192,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="175" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>432</v>
       </c>
@@ -13242,7 +13242,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="176" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>432</v>
       </c>
@@ -13292,7 +13292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="177" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>299</v>
       </c>
@@ -13542,7 +13542,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="182" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>1113</v>
       </c>
@@ -13592,7 +13592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="183" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>307</v>
       </c>
@@ -13642,7 +13642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="184" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>307</v>
       </c>
@@ -13742,7 +13742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="186" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>682</v>
       </c>
@@ -13792,7 +13792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="187" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>686</v>
       </c>
@@ -13942,7 +13942,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="190" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>835</v>
       </c>
@@ -13992,7 +13992,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="191" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>881</v>
       </c>
@@ -14092,7 +14092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="193" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>1135</v>
       </c>
@@ -14142,7 +14142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="194" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>1139</v>
       </c>
@@ -14192,7 +14192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="195" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>1153</v>
       </c>
@@ -14292,7 +14292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="197" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>893</v>
       </c>
@@ -14342,7 +14342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="198" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>310</v>
       </c>
@@ -14392,7 +14392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="199" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>310</v>
       </c>
@@ -14442,7 +14442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="200" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>342</v>
       </c>
@@ -14592,7 +14592,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="203" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>342</v>
       </c>
@@ -14742,7 +14742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="206" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>890</v>
       </c>
@@ -14792,7 +14792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="207" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>1042</v>
       </c>
@@ -14842,7 +14842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="208" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>347</v>
       </c>
@@ -15442,7 +15442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="220" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>1101</v>
       </c>
@@ -15492,7 +15492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="221" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>59</v>
       </c>
@@ -15542,7 +15542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="222" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>189</v>
       </c>
@@ -15592,7 +15592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="223" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>189</v>
       </c>
@@ -15642,7 +15642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="224" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>1059</v>
       </c>
@@ -15692,7 +15692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="225" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>1063</v>
       </c>
@@ -15742,7 +15742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="226" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>1105</v>
       </c>
@@ -15792,7 +15792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="227" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>463</v>
       </c>
@@ -15842,7 +15842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="228" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>467</v>
       </c>
@@ -15892,7 +15892,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="229" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>921</v>
       </c>
@@ -15942,7 +15942,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="230" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>925</v>
       </c>
@@ -15992,7 +15992,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="231" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>403</v>
       </c>
@@ -16042,7 +16042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="232" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>812</v>
       </c>
@@ -16092,7 +16092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="233" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>1056</v>
       </c>
@@ -16142,7 +16142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="234" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>104</v>
       </c>
@@ -16192,7 +16192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="235" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>111</v>
       </c>
@@ -16292,7 +16292,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="237" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>410</v>
       </c>
@@ -16342,7 +16342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="238" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>549</v>
       </c>
@@ -16442,7 +16442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="240" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>522</v>
       </c>
@@ -16492,7 +16492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="241" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>816</v>
       </c>
@@ -16642,7 +16642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="244" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>294</v>
       </c>
@@ -16692,7 +16692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="245" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>121</v>
       </c>
@@ -16742,7 +16742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="246" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>223</v>
       </c>
@@ -16792,7 +16792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="247" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>233</v>
       </c>
@@ -16842,7 +16842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="248" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>233</v>
       </c>
@@ -16892,7 +16892,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="249" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>233</v>
       </c>
@@ -16942,7 +16942,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="250" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>233</v>
       </c>
@@ -16992,7 +16992,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="251" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>473</v>
       </c>
@@ -17042,7 +17042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="252" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>455</v>
       </c>
@@ -17092,7 +17092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="253" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>210</v>
       </c>
@@ -17142,7 +17142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="254" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>210</v>
       </c>
@@ -17192,7 +17192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="255" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>656</v>
       </c>
@@ -17242,7 +17242,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="256" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>860</v>
       </c>
@@ -17342,7 +17342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="258" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>22</v>
       </c>
@@ -17392,7 +17392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="259" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>30</v>
       </c>
@@ -17492,7 +17492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="261" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>213</v>
       </c>
@@ -17542,7 +17542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="262" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>217</v>
       </c>
@@ -17592,7 +17592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="263" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>217</v>
       </c>
@@ -17642,7 +17642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="264" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>291</v>
       </c>
@@ -17692,7 +17692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="265" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>291</v>
       </c>
@@ -17742,7 +17742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="266" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>499</v>
       </c>
@@ -17792,7 +17792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="267" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>505</v>
       </c>
@@ -17842,7 +17842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="268" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>505</v>
       </c>
@@ -17942,7 +17942,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="270" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>588</v>
       </c>
@@ -17992,7 +17992,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="271" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>720</v>
       </c>
@@ -18042,7 +18042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="272" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>726</v>
       </c>
@@ -18242,7 +18242,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="276" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>1024</v>
       </c>
@@ -18292,7 +18292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="277" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>1030</v>
       </c>
@@ -18392,7 +18392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="279" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>708</v>
       </c>
@@ -18442,7 +18442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="280" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>971</v>
       </c>
@@ -18492,7 +18492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="281" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>1048</v>
       </c>
@@ -18542,7 +18542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="282" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>1128</v>
       </c>
@@ -18642,7 +18642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="284" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
         <v>489</v>
       </c>
@@ -18692,7 +18692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="285" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>995</v>
       </c>
@@ -18742,7 +18742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="286" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>518</v>
       </c>
@@ -18792,7 +18792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="287" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
         <v>538</v>
       </c>
@@ -18842,7 +18842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="288" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>833</v>
       </c>
@@ -18892,7 +18892,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="289" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>618</v>
       </c>
@@ -19292,7 +19292,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="297" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>618</v>
       </c>
@@ -19342,7 +19342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="298" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>637</v>
       </c>
@@ -19492,7 +19492,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="301" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
         <v>637</v>
       </c>
@@ -19542,7 +19542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="302" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
         <v>637</v>
       </c>
@@ -19592,7 +19592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="303" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
         <v>637</v>
       </c>
@@ -19642,7 +19642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="304" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
         <v>838</v>
       </c>
@@ -19692,7 +19692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="305" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
         <v>362</v>
       </c>
@@ -19742,7 +19742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="306" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
         <v>432</v>
       </c>
@@ -19792,7 +19792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="307" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
         <v>593</v>
       </c>
@@ -19992,7 +19992,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="311" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
         <v>801</v>
       </c>
@@ -20042,7 +20042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="312" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
         <v>95</v>
       </c>
@@ -20092,7 +20092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="313" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
         <v>95</v>
       </c>
@@ -20142,7 +20142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="314" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
         <v>159</v>
       </c>
@@ -20392,7 +20392,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="319" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
         <v>530</v>
       </c>
@@ -20442,7 +20442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="320" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
         <v>660</v>
       </c>
@@ -20492,7 +20492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="321" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
         <v>1093</v>
       </c>
@@ -20792,7 +20792,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="327" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
         <v>1093</v>
       </c>
@@ -20842,7 +20842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="328" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
         <v>139</v>
       </c>
@@ -20892,7 +20892,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="329" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
         <v>183</v>
       </c>
@@ -20942,7 +20942,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="330" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
         <v>811</v>
       </c>
@@ -20992,7 +20992,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="331" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
         <v>389</v>
       </c>
@@ -21042,7 +21042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="332" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
         <v>389</v>
       </c>
@@ -21092,7 +21092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="333" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
         <v>742</v>
       </c>
@@ -21142,7 +21142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="334" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
         <v>742</v>
       </c>
@@ -21442,7 +21442,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="340" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
         <v>844</v>
       </c>
@@ -21492,7 +21492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="341" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
         <v>905</v>
       </c>
@@ -21542,7 +21542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="342" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
         <v>907</v>
       </c>
@@ -21592,7 +21592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="343" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
         <v>953</v>
       </c>
@@ -21642,7 +21642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="344" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
         <v>155</v>
       </c>
@@ -21992,7 +21992,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="351" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
         <v>324</v>
       </c>
@@ -22042,7 +22042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="352" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
         <v>324</v>
       </c>
@@ -22092,7 +22092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="353" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
         <v>273</v>
       </c>
@@ -22142,7 +22142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="354" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
         <v>738</v>
       </c>
@@ -22192,7 +22192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="355" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
         <v>884</v>
       </c>
@@ -22292,7 +22292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="357" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
         <v>587</v>
       </c>
@@ -22492,7 +22492,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="361" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
         <v>601</v>
       </c>
@@ -22542,7 +22542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="362" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
         <v>774</v>
       </c>
@@ -22592,7 +22592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="363" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
         <v>848</v>
       </c>
@@ -22642,7 +22642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="364" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
         <v>879</v>
       </c>
@@ -22692,7 +22692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="365" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
         <v>945</v>
       </c>
@@ -22742,7 +22742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="366" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
         <v>949</v>
       </c>
@@ -22792,7 +22792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="367" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
         <v>61</v>
       </c>
@@ -22842,7 +22842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="368" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
         <v>1116</v>
       </c>
@@ -22892,7 +22892,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="369" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
         <v>259</v>
       </c>
@@ -22942,7 +22942,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="370" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
         <v>259</v>
       </c>
@@ -23042,7 +23042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="372" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
         <v>680</v>
       </c>
@@ -23142,7 +23142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="374" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
         <v>1108</v>
       </c>
@@ -23242,7 +23242,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="376" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
         <v>822</v>
       </c>
@@ -23292,7 +23292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="377" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
         <v>350</v>
       </c>
@@ -23342,7 +23342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="378" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
         <v>878</v>
       </c>
@@ -23392,7 +23392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="379" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
         <v>896</v>
       </c>
@@ -23442,7 +23442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="380" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
         <v>1044</v>
       </c>
@@ -23492,7 +23492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="381" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
         <v>1123</v>
       </c>
@@ -23542,7 +23542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="382" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
         <v>346</v>
       </c>
@@ -23592,7 +23592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="383" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
         <v>367</v>
       </c>
@@ -23642,7 +23642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="384" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
         <v>406</v>
       </c>
@@ -23742,7 +23742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="386" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
         <v>697</v>
       </c>
@@ -24092,7 +24092,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="393" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
         <v>797</v>
       </c>
@@ -24142,7 +24142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="394" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
         <v>302</v>
       </c>
@@ -24192,7 +24192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="395" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
         <v>413</v>
       </c>
@@ -24392,7 +24392,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="399" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
         <v>466</v>
       </c>
@@ -24442,7 +24442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="400" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
         <v>470</v>
       </c>
@@ -24492,7 +24492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="401" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
         <v>596</v>
       </c>
@@ -24542,7 +24542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="402" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
         <v>866</v>
       </c>
@@ -24592,7 +24592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="403" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
         <v>924</v>
       </c>
@@ -24642,7 +24642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="404" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
         <v>928</v>
       </c>
@@ -24692,7 +24692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="405" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
         <v>1062</v>
       </c>
@@ -24742,7 +24742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="406" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
         <v>1066</v>
       </c>
@@ -24942,7 +24942,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="410" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
         <v>1104</v>
       </c>
@@ -24992,7 +24992,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="411" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
         <v>89</v>
       </c>
@@ -25042,7 +25042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="412" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
         <v>89</v>
       </c>
@@ -25142,7 +25142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="414" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
         <v>293</v>
       </c>
@@ -25192,7 +25192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="415" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
         <v>392</v>
       </c>
@@ -25242,7 +25242,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="416" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
         <v>392</v>
       </c>
@@ -25292,7 +25292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="417" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
         <v>397</v>
       </c>
@@ -25342,7 +25342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="418" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
         <v>398</v>
       </c>
@@ -25392,7 +25392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="419" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
         <v>545</v>
       </c>
@@ -25442,7 +25442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="420" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
         <v>609</v>
       </c>
@@ -25492,7 +25492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="421" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
         <v>635</v>
       </c>
@@ -25542,7 +25542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="422" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
         <v>685</v>
       </c>
@@ -25592,7 +25592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="423" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
         <v>689</v>
       </c>
@@ -26042,7 +26042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="432" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
         <v>920</v>
       </c>
@@ -26092,7 +26092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="433" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
         <v>1120</v>
       </c>
@@ -26142,7 +26142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="434" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
         <v>1142</v>
       </c>
@@ -26192,7 +26192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="435" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
         <v>1146</v>
       </c>
@@ -26242,7 +26242,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="436" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
         <v>1156</v>
       </c>
@@ -26292,7 +26292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="437" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
         <v>107</v>
       </c>
@@ -26542,7 +26542,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="442" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
         <v>113</v>
       </c>
@@ -26592,7 +26592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="443" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
         <v>126</v>
       </c>
@@ -26642,7 +26642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="444" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
         <v>633</v>
       </c>
@@ -26692,7 +26692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="445" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
         <v>862</v>
       </c>
@@ -26942,7 +26942,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="450" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
         <v>235</v>
       </c>
@@ -26992,7 +26992,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="451" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
         <v>235</v>
       </c>
@@ -27142,7 +27142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="454" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
         <v>249</v>
       </c>
@@ -27192,7 +27192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="455" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
         <v>250</v>
       </c>
@@ -27292,7 +27292,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="457" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
         <v>298</v>
       </c>
@@ -27342,7 +27342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="458" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
         <v>641</v>
       </c>
@@ -27392,7 +27392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="459" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
         <v>644</v>
       </c>
@@ -27442,7 +27442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="460" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
         <v>900</v>
       </c>
@@ -27492,7 +27492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="461" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
         <v>966</v>
       </c>
@@ -27542,7 +27542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="462" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
         <v>967</v>
       </c>
@@ -27942,7 +27942,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="470" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
         <v>459</v>
       </c>
@@ -27992,7 +27992,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="471" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
         <v>471</v>
       </c>
@@ -28042,7 +28042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="472" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
         <v>592</v>
       </c>
@@ -28092,7 +28092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="473" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
         <v>787</v>
       </c>
@@ -28142,7 +28142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="474" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
         <v>788</v>
       </c>
@@ -28192,7 +28192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="475" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
         <v>225</v>
       </c>
@@ -28242,7 +28242,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="476" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
         <v>317</v>
       </c>
@@ -28292,7 +28292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="477" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
         <v>317</v>
       </c>
@@ -28392,7 +28392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="479" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
         <v>391</v>
       </c>
@@ -28442,7 +28442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="480" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
         <v>551</v>
       </c>
@@ -28742,7 +28742,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="486" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
         <v>605</v>
       </c>
@@ -28792,7 +28792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="487" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
         <v>746</v>
       </c>
@@ -28842,7 +28842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="488" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
         <v>818</v>
       </c>
@@ -28892,7 +28892,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="489" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
         <v>892</v>
       </c>
@@ -28942,7 +28942,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="490" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
         <v>1058</v>
       </c>
@@ -28992,7 +28992,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="491" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
         <v>24</v>
       </c>
@@ -29192,7 +29192,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="495" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
         <v>219</v>
       </c>
@@ -29342,7 +29342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="498" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
         <v>448</v>
       </c>
@@ -29392,7 +29392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="499" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
         <v>449</v>
       </c>
@@ -29442,7 +29442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="500" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
         <v>450</v>
       </c>
@@ -29492,7 +29492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="501" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
         <v>451</v>
       </c>
@@ -29542,7 +29542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="502" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
         <v>452</v>
       </c>
@@ -29592,7 +29592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="503" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
         <v>453</v>
       </c>
@@ -29642,7 +29642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="504" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
         <v>501</v>
       </c>
@@ -29692,7 +29692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="505" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
         <v>622</v>
       </c>
@@ -29992,7 +29992,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="511" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
         <v>952</v>
       </c>
@@ -30042,7 +30042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="512" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
         <v>1026</v>
       </c>
@@ -30092,7 +30092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="513" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
         <v>1134</v>
       </c>
@@ -30142,7 +30142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="514" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
         <v>1138</v>
       </c>
@@ -30292,7 +30292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="517" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
         <v>662</v>
       </c>
@@ -30342,7 +30342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="518" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
         <v>722</v>
       </c>
@@ -30392,7 +30392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="519" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
         <v>728</v>
       </c>
@@ -30442,7 +30442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="520" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
         <v>840</v>
       </c>
@@ -30492,7 +30492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="521" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
         <v>973</v>
       </c>
@@ -30592,7 +30592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="523" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
         <v>32</v>
       </c>
@@ -30642,7 +30642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="524" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
         <v>508</v>
       </c>
@@ -30692,7 +30692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="525" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
         <v>508</v>
       </c>
@@ -30742,7 +30742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="526" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
         <v>1032</v>
       </c>
@@ -30792,7 +30792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="527" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
         <v>141</v>
       </c>
@@ -30842,7 +30842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="528" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
         <v>187</v>
       </c>
@@ -30892,7 +30892,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="529" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
         <v>353</v>
       </c>
@@ -30942,7 +30942,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="530" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
         <v>366</v>
       </c>
@@ -31042,7 +31042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="532" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
         <v>462</v>
       </c>
@@ -31192,7 +31192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="535" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
         <v>409</v>
       </c>
@@ -31242,7 +31242,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="536" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
         <v>416</v>
       </c>
@@ -31292,7 +31292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="537" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
         <v>476</v>
       </c>
@@ -31342,7 +31342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="538" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
         <v>576</v>
       </c>
@@ -31442,7 +31442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="540" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
         <v>263</v>
       </c>
@@ -31592,7 +31592,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="543" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
         <v>541</v>
       </c>
@@ -31642,7 +31642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="544" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
         <v>193</v>
       </c>
@@ -31692,7 +31692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="545" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
         <v>193</v>
       </c>
@@ -31742,7 +31742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="546" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
         <v>477</v>
       </c>
@@ -31792,7 +31792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="547" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
         <v>477</v>
       </c>
@@ -31842,7 +31842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="548" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
         <v>480</v>
       </c>
@@ -31892,7 +31892,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="549" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
         <v>480</v>
       </c>
@@ -32542,7 +32542,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="562" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
         <v>483</v>
       </c>
@@ -32592,7 +32592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="563" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
         <v>483</v>
       </c>
@@ -32642,7 +32642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="564" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
         <v>699</v>
       </c>
@@ -32692,7 +32692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="565" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
         <v>701</v>
       </c>
@@ -32992,7 +32992,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="571" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
         <v>998</v>
       </c>
@@ -33042,7 +33042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="572" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
         <v>1000</v>
       </c>
@@ -33092,7 +33092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="573" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A573" t="s">
         <v>1002</v>
       </c>
@@ -33142,7 +33142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="574" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A574" t="s">
         <v>1164</v>
       </c>
@@ -33292,7 +33292,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="577" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A577" t="s">
         <v>1166</v>
       </c>
@@ -33342,7 +33342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="578" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A578" t="s">
         <v>1168</v>
       </c>
@@ -33392,7 +33392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="579" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A579" t="s">
         <v>491</v>
       </c>
@@ -33442,7 +33442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="580" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A580" t="s">
         <v>494</v>
       </c>
@@ -33542,7 +33542,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="582" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A582" t="s">
         <v>710</v>
       </c>
@@ -33592,7 +33592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="583" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A583" t="s">
         <v>715</v>
       </c>
@@ -33642,7 +33642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="584" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A584" t="s">
         <v>997</v>
       </c>
@@ -33692,7 +33692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="585" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A585" t="s">
         <v>1004</v>
       </c>
@@ -33742,7 +33742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="586" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A586" t="s">
         <v>1006</v>
       </c>
@@ -33792,7 +33792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="587" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A587" t="s">
         <v>1014</v>
       </c>
@@ -33842,7 +33842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="588" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A588" t="s">
         <v>1016</v>
       </c>
@@ -33892,7 +33892,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="589" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A589" t="s">
         <v>1016</v>
       </c>
@@ -33942,7 +33942,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="590" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="590" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A590" t="s">
         <v>1016</v>
       </c>
@@ -33992,7 +33992,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="591" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="591" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A591" t="s">
         <v>1016</v>
       </c>
@@ -34042,7 +34042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="592" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A592" t="s">
         <v>1130</v>
       </c>
@@ -34092,7 +34092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="593" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="593" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A593" t="s">
         <v>1176</v>
       </c>
@@ -34292,7 +34292,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="597" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="597" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A597" t="s">
         <v>1183</v>
       </c>
@@ -34692,7 +34692,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="605" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="605" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A605" t="s">
         <v>1189</v>
       </c>
@@ -34742,7 +34742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="606" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="606" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A606" t="s">
         <v>1191</v>
       </c>
@@ -34792,7 +34792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="607" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="607" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A607" t="s">
         <v>1191</v>
       </c>
@@ -34842,7 +34842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="608" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="608" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A608" t="s">
         <v>803</v>
       </c>
@@ -34942,7 +34942,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="610" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="610" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A610" t="s">
         <v>1010</v>
       </c>
@@ -34992,7 +34992,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="611" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="611" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A611" t="s">
         <v>1178</v>
       </c>
@@ -35042,7 +35042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="612" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="612" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A612" t="s">
         <v>492</v>
       </c>
@@ -35092,7 +35092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="613" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="613" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A613" t="s">
         <v>711</v>
       </c>
@@ -35142,7 +35142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="614" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="614" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A614" t="s">
         <v>713</v>
       </c>
@@ -35192,7 +35192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="615" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="615" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A615" t="s">
         <v>1012</v>
       </c>
@@ -35242,7 +35242,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="616" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="616" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A616" t="s">
         <v>1170</v>
       </c>
@@ -35292,7 +35292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="617" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="617" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A617" t="s">
         <v>1170</v>
       </c>
@@ -35442,7 +35442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="620" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="620" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A620" t="s">
         <v>1180</v>
       </c>
@@ -35492,7 +35492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="621" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="621" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A621" t="s">
         <v>1180</v>
       </c>
@@ -35544,11 +35544,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:P621" xr:uid="{6A7ECD2C-6F5B-4E4D-962E-4B55F2FEEDC6}">
-    <filterColumn colId="9">
-      <filters>
-        <filter val="TYPE_WATER"/>
-      </filters>
-    </filterColumn>
     <filterColumn colId="15">
       <filters>
         <filter val="Y"/>

--- a/all_generations_pokemon_families.xlsx
+++ b/all_generations_pokemon_families.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3c6863eb3d429a98/Documents/GitHub/pokefirered-expansion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="778" documentId="8_{3DE7B663-32D8-4B09-ACF8-07A7237E0E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F18E100-9E3F-410E-B464-42AE4650C295}"/>
+  <xr:revisionPtr revIDLastSave="795" documentId="8_{3DE7B663-32D8-4B09-ACF8-07A7237E0E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F9A492F-C0FC-463D-9259-7C378A0ABEA4}"/>
   <bookViews>
     <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{913F818F-7E2F-42B8-8FB9-B28A63806581}"/>
   </bookViews>

--- a/all_generations_pokemon_families.xlsx
+++ b/all_generations_pokemon_families.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3c6863eb3d429a98/Documents/GitHub/pokefirered-expansion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="795" documentId="8_{3DE7B663-32D8-4B09-ACF8-07A7237E0E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F9A492F-C0FC-463D-9259-7C378A0ABEA4}"/>
+  <xr:revisionPtr revIDLastSave="823" documentId="8_{3DE7B663-32D8-4B09-ACF8-07A7237E0E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C181B9F9-BB70-491F-A447-42283E9B0E19}"/>
   <bookViews>
     <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{913F818F-7E2F-42B8-8FB9-B28A63806581}"/>
   </bookViews>
@@ -4542,7 +4542,7 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>41</v>
       </c>
@@ -4592,7 +4592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>779</v>
       </c>
@@ -4642,7 +4642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>929</v>
       </c>
@@ -4692,7 +4692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>929</v>
       </c>
@@ -4742,7 +4742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>79</v>
       </c>
@@ -4792,7 +4792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>114</v>
       </c>
@@ -4842,7 +4842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>46</v>
       </c>
@@ -4892,7 +4892,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>84</v>
       </c>
@@ -4942,7 +4942,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>84</v>
       </c>
@@ -4992,7 +4992,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>573</v>
       </c>
@@ -5042,7 +5042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>136</v>
       </c>
@@ -5092,7 +5092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>515</v>
       </c>
@@ -5142,7 +5142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="14" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>49</v>
       </c>
@@ -5192,7 +5192,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="15" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>52</v>
       </c>
@@ -5242,7 +5242,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="16" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>54</v>
       </c>
@@ -5292,7 +5292,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>735</v>
       </c>
@@ -5342,7 +5342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>739</v>
       </c>
@@ -5392,7 +5392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>1039</v>
       </c>
@@ -5442,7 +5442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="20" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>62</v>
       </c>
@@ -5492,7 +5492,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="21" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>65</v>
       </c>
@@ -5542,7 +5542,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="22" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>62</v>
       </c>
@@ -5592,7 +5592,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="23" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>62</v>
       </c>
@@ -5642,7 +5642,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="24" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>65</v>
       </c>
@@ -5692,7 +5692,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="25" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>71</v>
       </c>
@@ -5742,7 +5742,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="26" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>74</v>
       </c>
@@ -5792,7 +5792,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="27" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>75</v>
       </c>
@@ -5842,7 +5842,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="28" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>78</v>
       </c>
@@ -5892,7 +5892,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>1045</v>
       </c>
@@ -5942,7 +5942,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>55</v>
       </c>
@@ -5992,7 +5992,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>535</v>
       </c>
@@ -6042,7 +6042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>653</v>
       </c>
@@ -6092,7 +6092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>657</v>
       </c>
@@ -6142,7 +6142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>771</v>
       </c>
@@ -6192,7 +6192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>101</v>
       </c>
@@ -6242,7 +6242,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>108</v>
       </c>
@@ -6292,7 +6292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>527</v>
       </c>
@@ -6342,7 +6342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>552</v>
       </c>
@@ -6392,7 +6392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>759</v>
       </c>
@@ -6442,7 +6442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>813</v>
       </c>
@@ -6492,7 +6492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>1090</v>
       </c>
@@ -6542,7 +6542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>1053</v>
       </c>
@@ -6592,7 +6592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>857</v>
       </c>
@@ -6642,7 +6642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>1131</v>
       </c>
@@ -6692,7 +6692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>782</v>
       </c>
@@ -6742,7 +6742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>782</v>
       </c>
@@ -6792,7 +6792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>798</v>
       </c>
@@ -6842,7 +6842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>519</v>
       </c>
@@ -6892,7 +6892,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="49" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>122</v>
       </c>
@@ -6942,7 +6942,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="50" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>126</v>
       </c>
@@ -6992,7 +6992,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="51" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>130</v>
       </c>
@@ -7042,7 +7042,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="52" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>133</v>
       </c>
@@ -7092,7 +7092,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>135</v>
       </c>
@@ -7142,7 +7142,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>606</v>
       </c>
@@ -7192,7 +7192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>91</v>
       </c>
@@ -7242,7 +7242,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>91</v>
       </c>
@@ -7292,7 +7292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="57" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>142</v>
       </c>
@@ -7342,7 +7342,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="58" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>145</v>
       </c>
@@ -7392,7 +7392,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="59" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>145</v>
       </c>
@@ -7442,7 +7442,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="60" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>150</v>
       </c>
@@ -7492,7 +7492,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="61" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>151</v>
       </c>
@@ -7542,7 +7542,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>122</v>
       </c>
@@ -7592,7 +7592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>152</v>
       </c>
@@ -7642,7 +7642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>197</v>
       </c>
@@ -7692,7 +7692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>220</v>
       </c>
@@ -7742,7 +7742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="66" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>160</v>
       </c>
@@ -7792,7 +7792,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="67" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>163</v>
       </c>
@@ -7842,7 +7842,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="68" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>160</v>
       </c>
@@ -7892,7 +7892,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="69" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>163</v>
       </c>
@@ -7942,7 +7942,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="70" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>166</v>
       </c>
@@ -7992,7 +7992,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="71" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>169</v>
       </c>
@@ -8042,7 +8042,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="72" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>166</v>
       </c>
@@ -8092,7 +8092,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="73" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>169</v>
       </c>
@@ -8142,7 +8142,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="74" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>166</v>
       </c>
@@ -8192,7 +8192,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="75" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>174</v>
       </c>
@@ -8242,7 +8242,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>230</v>
       </c>
@@ -8292,7 +8292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>230</v>
       </c>
@@ -8342,7 +8342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>369</v>
       </c>
@@ -8392,7 +8392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>430</v>
       </c>
@@ -8442,7 +8442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>486</v>
       </c>
@@ -8492,7 +8492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>581</v>
       </c>
@@ -8542,7 +8542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>581</v>
       </c>
@@ -8592,7 +8592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>705</v>
       </c>
@@ -8642,7 +8642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>739</v>
       </c>
@@ -8692,7 +8692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>775</v>
       </c>
@@ -8742,7 +8742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>793</v>
       </c>
@@ -8792,7 +8792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>804</v>
       </c>
@@ -8842,7 +8842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>804</v>
       </c>
@@ -8892,7 +8892,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>819</v>
       </c>
@@ -8942,7 +8942,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>841</v>
       </c>
@@ -8992,7 +8992,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>845</v>
       </c>
@@ -9042,7 +9042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>887</v>
       </c>
@@ -9092,7 +9092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>917</v>
       </c>
@@ -9142,7 +9142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>942</v>
       </c>
@@ -9192,7 +9192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>946</v>
       </c>
@@ -9242,7 +9242,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>961</v>
       </c>
@@ -9292,7 +9292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>961</v>
       </c>
@@ -9342,7 +9342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>968</v>
       </c>
@@ -9392,7 +9392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>992</v>
       </c>
@@ -9442,7 +9442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>1117</v>
       </c>
@@ -9492,7 +9492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>1125</v>
       </c>
@@ -9542,7 +9542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>1143</v>
       </c>
@@ -9592,7 +9592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>863</v>
       </c>
@@ -9642,7 +9642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>48</v>
       </c>
@@ -9692,7 +9692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>156</v>
       </c>
@@ -9742,7 +9742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>179</v>
       </c>
@@ -9792,7 +9792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>214</v>
       </c>
@@ -9842,7 +9842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>284</v>
       </c>
@@ -9892,7 +9892,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>546</v>
       </c>
@@ -9942,7 +9942,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>875</v>
       </c>
@@ -9992,7 +9992,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="111" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>239</v>
       </c>
@@ -10042,7 +10042,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="112" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>242</v>
       </c>
@@ -10092,7 +10092,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="113" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>239</v>
       </c>
@@ -10142,7 +10142,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="114" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>242</v>
       </c>
@@ -10192,7 +10192,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>913</v>
       </c>
@@ -10242,7 +10242,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>26</v>
       </c>
@@ -10292,7 +10292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>502</v>
       </c>
@@ -10342,7 +10342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>1027</v>
       </c>
@@ -10392,7 +10392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>207</v>
       </c>
@@ -10442,7 +10442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>270</v>
       </c>
@@ -10492,7 +10492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>288</v>
       </c>
@@ -10542,7 +10542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>384</v>
       </c>
@@ -10592,7 +10592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>384</v>
       </c>
@@ -10642,7 +10642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>717</v>
       </c>
@@ -10692,7 +10692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>723</v>
       </c>
@@ -10742,7 +10742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>729</v>
       </c>
@@ -10792,7 +10792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="127" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>264</v>
       </c>
@@ -10842,7 +10842,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="128" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>264</v>
       </c>
@@ -10892,7 +10892,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="129" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>269</v>
       </c>
@@ -10942,7 +10942,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>897</v>
       </c>
@@ -10992,7 +10992,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="131" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>34</v>
       </c>
@@ -11042,7 +11042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="132" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>274</v>
       </c>
@@ -11092,7 +11092,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="133" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>277</v>
       </c>
@@ -11142,7 +11142,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="134" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>278</v>
       </c>
@@ -11192,7 +11192,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="135" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>281</v>
       </c>
@@ -11242,7 +11242,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="136" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>278</v>
       </c>
@@ -11292,7 +11292,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="137" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>281</v>
       </c>
@@ -11342,7 +11342,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="138" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>509</v>
       </c>
@@ -11392,7 +11392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>1033</v>
       </c>
@@ -11442,7 +11442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="140" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>245</v>
       </c>
@@ -11492,7 +11492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="141" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>245</v>
       </c>
@@ -11542,7 +11542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="142" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>245</v>
       </c>
@@ -11592,7 +11592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="143" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>245</v>
       </c>
@@ -11642,7 +11642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="144" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>15</v>
       </c>
@@ -11692,7 +11692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="145" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>496</v>
       </c>
@@ -11742,7 +11742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="146" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>1021</v>
       </c>
@@ -11792,7 +11792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="147" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>175</v>
       </c>
@@ -11842,7 +11842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="148" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>303</v>
       </c>
@@ -11892,7 +11892,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="149" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>306</v>
       </c>
@@ -11942,7 +11942,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="150" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>319</v>
       </c>
@@ -11992,7 +11992,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="151" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>319</v>
       </c>
@@ -12042,7 +12042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="152" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>319</v>
       </c>
@@ -12092,7 +12092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="153" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>542</v>
       </c>
@@ -12142,7 +12142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="154" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>119</v>
       </c>
@@ -12192,7 +12192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="155" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>256</v>
       </c>
@@ -12242,7 +12242,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="156" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>313</v>
       </c>
@@ -12292,7 +12292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="157" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>313</v>
       </c>
@@ -12342,7 +12342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="158" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>432</v>
       </c>
@@ -12392,7 +12392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="159" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>432</v>
       </c>
@@ -12442,7 +12442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="160" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>432</v>
       </c>
@@ -12492,7 +12492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="161" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>432</v>
       </c>
@@ -12542,7 +12542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="162" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>432</v>
       </c>
@@ -12592,7 +12592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="163" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>325</v>
       </c>
@@ -12642,7 +12642,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="164" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>325</v>
       </c>
@@ -12692,7 +12692,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="165" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>325</v>
       </c>
@@ -12742,7 +12742,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="166" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>333</v>
       </c>
@@ -12792,7 +12792,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="167" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>334</v>
       </c>
@@ -12842,7 +12842,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="168" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>335</v>
       </c>
@@ -12892,7 +12892,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="169" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>336</v>
       </c>
@@ -12942,7 +12942,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="170" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>341</v>
       </c>
@@ -12992,7 +12992,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="171" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>432</v>
       </c>
@@ -13042,7 +13042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="172" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>432</v>
       </c>
@@ -13092,7 +13092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="173" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>432</v>
       </c>
@@ -13142,7 +13142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="174" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>346</v>
       </c>
@@ -13192,7 +13192,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="175" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>432</v>
       </c>
@@ -13242,7 +13242,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="176" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>432</v>
       </c>
@@ -13292,7 +13292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="177" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>299</v>
       </c>
@@ -13342,7 +13342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="178" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>354</v>
       </c>
@@ -13392,7 +13392,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="179" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>354</v>
       </c>
@@ -13442,7 +13442,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="180" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>359</v>
       </c>
@@ -13492,7 +13492,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="181" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>361</v>
       </c>
@@ -13542,7 +13542,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="182" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>1113</v>
       </c>
@@ -13592,7 +13592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="183" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>307</v>
       </c>
@@ -13642,7 +13642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="184" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>307</v>
       </c>
@@ -13692,7 +13692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="185" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>531</v>
       </c>
@@ -13742,7 +13742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="186" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>682</v>
       </c>
@@ -13792,7 +13792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="187" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>686</v>
       </c>
@@ -13842,7 +13842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="188" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>376</v>
       </c>
@@ -13892,7 +13892,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="189" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>379</v>
       </c>
@@ -13942,7 +13942,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="190" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>835</v>
       </c>
@@ -13992,7 +13992,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="191" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>881</v>
       </c>
@@ -14042,7 +14042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="192" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>1086</v>
       </c>
@@ -14092,7 +14092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="193" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>1135</v>
       </c>
@@ -14142,7 +14142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="194" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>1139</v>
       </c>
@@ -14192,7 +14192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="195" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>1153</v>
       </c>
@@ -14242,7 +14242,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="196" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>226</v>
       </c>
@@ -14292,7 +14292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="197" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>893</v>
       </c>
@@ -14342,7 +14342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="198" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>310</v>
       </c>
@@ -14392,7 +14392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="199" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>310</v>
       </c>
@@ -14442,7 +14442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="200" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>342</v>
       </c>
@@ -14492,7 +14492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="201" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>399</v>
       </c>
@@ -14542,7 +14542,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="202" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>402</v>
       </c>
@@ -14592,7 +14592,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="203" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>342</v>
       </c>
@@ -14642,7 +14642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="204" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>380</v>
       </c>
@@ -14692,7 +14692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="205" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>762</v>
       </c>
@@ -14742,7 +14742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="206" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>890</v>
       </c>
@@ -14792,7 +14792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="207" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>1042</v>
       </c>
@@ -14842,7 +14842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="208" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>347</v>
       </c>
@@ -14892,7 +14892,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="209" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>417</v>
       </c>
@@ -14942,7 +14942,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="210" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>419</v>
       </c>
@@ -14992,7 +14992,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="211" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>419</v>
       </c>
@@ -15042,7 +15042,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="212" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>419</v>
       </c>
@@ -15092,7 +15092,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="213" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>419</v>
       </c>
@@ -15142,7 +15142,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="214" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>424</v>
       </c>
@@ -15192,7 +15192,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="215" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>427</v>
       </c>
@@ -15242,7 +15242,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="216" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>555</v>
       </c>
@@ -15292,7 +15292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="217" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>674</v>
       </c>
@@ -15342,7 +15342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="218" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>974</v>
       </c>
@@ -15392,7 +15392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="219" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>974</v>
       </c>
@@ -15442,7 +15442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="220" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>1101</v>
       </c>
@@ -15492,7 +15492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="221" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>59</v>
       </c>
@@ -15542,7 +15542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="222" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>189</v>
       </c>
@@ -15592,7 +15592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="223" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>189</v>
       </c>
@@ -15642,7 +15642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="224" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>1059</v>
       </c>
@@ -15692,7 +15692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="225" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>1063</v>
       </c>
@@ -15742,7 +15742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="226" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>1105</v>
       </c>
@@ -15792,7 +15792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="227" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>463</v>
       </c>
@@ -15842,7 +15842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="228" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>467</v>
       </c>
@@ -15892,7 +15892,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="229" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>921</v>
       </c>
@@ -15942,7 +15942,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="230" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>925</v>
       </c>
@@ -15992,7 +15992,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="231" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>403</v>
       </c>
@@ -16042,7 +16042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="232" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>812</v>
       </c>
@@ -16092,7 +16092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="233" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>1056</v>
       </c>
@@ -16142,7 +16142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="234" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>104</v>
       </c>
@@ -16192,7 +16192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="235" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>111</v>
       </c>
@@ -16242,7 +16242,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="236" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>454</v>
       </c>
@@ -16292,7 +16292,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="237" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>410</v>
       </c>
@@ -16342,7 +16342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="238" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>549</v>
       </c>
@@ -16392,7 +16392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="239" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>778</v>
       </c>
@@ -16442,7 +16442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="240" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>522</v>
       </c>
@@ -16492,7 +16492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="241" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>816</v>
       </c>
@@ -16542,7 +16542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="242" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>200</v>
       </c>
@@ -16592,7 +16592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="243" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>200</v>
       </c>
@@ -16642,7 +16642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="244" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>294</v>
       </c>
@@ -16692,7 +16692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="245" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>121</v>
       </c>
@@ -16742,7 +16742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="246" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>223</v>
       </c>
@@ -16792,7 +16792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="247" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>233</v>
       </c>
@@ -16842,7 +16842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="248" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>233</v>
       </c>
@@ -16892,7 +16892,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="249" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>233</v>
       </c>
@@ -16942,7 +16942,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="250" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>233</v>
       </c>
@@ -16992,7 +16992,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="251" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>473</v>
       </c>
@@ -17042,7 +17042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="252" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>455</v>
       </c>
@@ -17092,7 +17092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="253" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>210</v>
       </c>
@@ -17142,7 +17142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="254" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>210</v>
       </c>
@@ -17192,7 +17192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="255" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>656</v>
       </c>
@@ -17242,7 +17242,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="256" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>860</v>
       </c>
@@ -17292,7 +17292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="257" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>871</v>
       </c>
@@ -17342,7 +17342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="258" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>22</v>
       </c>
@@ -17392,7 +17392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="259" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>30</v>
       </c>
@@ -17442,7 +17442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="260" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>38</v>
       </c>
@@ -17492,7 +17492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="261" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>213</v>
       </c>
@@ -17542,7 +17542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="262" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>217</v>
       </c>
@@ -17592,7 +17592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="263" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>217</v>
       </c>
@@ -17642,7 +17642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="264" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>291</v>
       </c>
@@ -17692,7 +17692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="265" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>291</v>
       </c>
@@ -17742,7 +17742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="266" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>499</v>
       </c>
@@ -17792,7 +17792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="267" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>505</v>
       </c>
@@ -17842,7 +17842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="268" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>505</v>
       </c>
@@ -17892,7 +17892,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="269" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>512</v>
       </c>
@@ -17942,7 +17942,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="270" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>588</v>
       </c>
@@ -17992,7 +17992,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="271" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>720</v>
       </c>
@@ -18042,7 +18042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="272" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>726</v>
       </c>
@@ -18092,7 +18092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="273" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>523</v>
       </c>
@@ -18142,7 +18142,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="274" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>526</v>
       </c>
@@ -18192,7 +18192,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="275" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>732</v>
       </c>
@@ -18242,7 +18242,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="276" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>1024</v>
       </c>
@@ -18292,7 +18292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="277" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>1030</v>
       </c>
@@ -18342,7 +18342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="278" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>1036</v>
       </c>
@@ -18392,7 +18392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="279" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>708</v>
       </c>
@@ -18442,7 +18442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="280" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>971</v>
       </c>
@@ -18492,7 +18492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="281" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>1048</v>
       </c>
@@ -18542,7 +18542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="282" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>1128</v>
       </c>
@@ -18592,7 +18592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="283" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
         <v>679</v>
       </c>
@@ -18642,7 +18642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="284" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
         <v>489</v>
       </c>
@@ -18692,7 +18692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="285" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>995</v>
       </c>
@@ -18742,7 +18742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="286" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>518</v>
       </c>
@@ -18792,7 +18792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="287" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
         <v>538</v>
       </c>
@@ -18842,7 +18842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="288" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>833</v>
       </c>
@@ -18892,7 +18892,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="289" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>618</v>
       </c>
@@ -18942,7 +18942,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="290" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>558</v>
       </c>
@@ -18992,7 +18992,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="291" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>561</v>
       </c>
@@ -19042,7 +19042,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="292" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
         <v>562</v>
       </c>
@@ -19092,7 +19092,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="293" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>565</v>
       </c>
@@ -19142,7 +19142,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="294" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>567</v>
       </c>
@@ -19192,7 +19192,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="295" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
         <v>568</v>
       </c>
@@ -19242,7 +19242,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="296" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
         <v>572</v>
       </c>
@@ -19292,7 +19292,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="297" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>618</v>
       </c>
@@ -19342,7 +19342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="298" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>637</v>
       </c>
@@ -19392,7 +19392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="299" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
         <v>577</v>
       </c>
@@ -19442,7 +19442,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="300" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
         <v>580</v>
       </c>
@@ -19492,7 +19492,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="301" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
         <v>637</v>
       </c>
@@ -19542,7 +19542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="302" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
         <v>637</v>
       </c>
@@ -19592,7 +19592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="303" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
         <v>637</v>
       </c>
@@ -19642,7 +19642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="304" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
         <v>838</v>
       </c>
@@ -19692,7 +19692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="305" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
         <v>362</v>
       </c>
@@ -19742,7 +19742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="306" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
         <v>432</v>
       </c>
@@ -19792,7 +19792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="307" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
         <v>593</v>
       </c>
@@ -19842,7 +19842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="308" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
         <v>372</v>
       </c>
@@ -19892,7 +19892,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="309" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
         <v>597</v>
       </c>
@@ -19942,7 +19942,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="310" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
         <v>600</v>
       </c>
@@ -19992,7 +19992,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="311" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
         <v>801</v>
       </c>
@@ -20042,7 +20042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="312" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
         <v>95</v>
       </c>
@@ -20092,7 +20092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="313" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
         <v>95</v>
       </c>
@@ -20142,7 +20142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="314" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
         <v>159</v>
       </c>
@@ -20192,7 +20192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="315" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
         <v>610</v>
       </c>
@@ -20242,7 +20242,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="316" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
         <v>610</v>
       </c>
@@ -20292,7 +20292,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="317" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
         <v>617</v>
       </c>
@@ -20342,7 +20342,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="318" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
         <v>617</v>
       </c>
@@ -20392,7 +20392,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="319" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
         <v>530</v>
       </c>
@@ -20442,7 +20442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="320" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
         <v>660</v>
       </c>
@@ -20492,7 +20492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="321" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
         <v>1093</v>
       </c>
@@ -20542,7 +20542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="322" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
         <v>623</v>
       </c>
@@ -20592,7 +20592,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="323" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
         <v>626</v>
       </c>
@@ -20642,7 +20642,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="324" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
         <v>627</v>
       </c>
@@ -20692,7 +20692,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="325" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
         <v>627</v>
       </c>
@@ -20742,7 +20742,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="326" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
         <v>632</v>
       </c>
@@ -20792,7 +20792,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="327" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
         <v>1093</v>
       </c>
@@ -20842,7 +20842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="328" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
         <v>139</v>
       </c>
@@ -20892,7 +20892,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="329" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
         <v>183</v>
       </c>
@@ -20942,7 +20942,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="330" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
         <v>811</v>
       </c>
@@ -20992,7 +20992,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="331" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
         <v>389</v>
       </c>
@@ -21042,7 +21042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="332" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
         <v>389</v>
       </c>
@@ -21092,7 +21092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="333" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
         <v>742</v>
       </c>
@@ -21142,7 +21142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="334" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
         <v>742</v>
       </c>
@@ -21192,7 +21192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="335" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
         <v>645</v>
       </c>
@@ -21242,7 +21242,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="336" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
         <v>648</v>
       </c>
@@ -21292,7 +21292,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="337" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
         <v>648</v>
       </c>
@@ -21342,7 +21342,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="338" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
         <v>652</v>
       </c>
@@ -21392,7 +21392,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="339" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
         <v>652</v>
       </c>
@@ -21442,7 +21442,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="340" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
         <v>844</v>
       </c>
@@ -21492,7 +21492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="341" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
         <v>905</v>
       </c>
@@ -21542,7 +21542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="342" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
         <v>907</v>
       </c>
@@ -21592,7 +21592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="343" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
         <v>953</v>
       </c>
@@ -21642,7 +21642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="344" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
         <v>155</v>
       </c>
@@ -21692,7 +21692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="345" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
         <v>663</v>
       </c>
@@ -21742,7 +21742,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="346" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
         <v>663</v>
       </c>
@@ -21792,7 +21792,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="347" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
         <v>667</v>
       </c>
@@ -21842,7 +21842,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="348" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
         <v>668</v>
       </c>
@@ -21892,7 +21892,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="349" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
         <v>671</v>
       </c>
@@ -21942,7 +21942,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="350" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
         <v>672</v>
       </c>
@@ -21992,7 +21992,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="351" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
         <v>324</v>
       </c>
@@ -22042,7 +22042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="352" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
         <v>324</v>
       </c>
@@ -22092,7 +22092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="353" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
         <v>273</v>
       </c>
@@ -22142,7 +22142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="354" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
         <v>738</v>
       </c>
@@ -22192,7 +22192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="355" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
         <v>884</v>
       </c>
@@ -22242,7 +22242,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="356" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
         <v>584</v>
       </c>
@@ -22292,7 +22292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="357" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
         <v>587</v>
       </c>
@@ -22342,7 +22342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="358" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
         <v>690</v>
       </c>
@@ -22392,7 +22392,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="359" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
         <v>694</v>
       </c>
@@ -22442,7 +22442,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="360" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
         <v>695</v>
       </c>
@@ -22492,7 +22492,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="361" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
         <v>601</v>
       </c>
@@ -22542,7 +22542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="362" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
         <v>774</v>
       </c>
@@ -22592,7 +22592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="363" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
         <v>848</v>
       </c>
@@ -22642,7 +22642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="364" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
         <v>879</v>
       </c>
@@ -22692,7 +22692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="365" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
         <v>945</v>
       </c>
@@ -22742,7 +22742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="366" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
         <v>949</v>
       </c>
@@ -22792,7 +22792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="367" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
         <v>61</v>
       </c>
@@ -22842,7 +22842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="368" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
         <v>1116</v>
       </c>
@@ -22892,7 +22892,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="369" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
         <v>259</v>
       </c>
@@ -22942,7 +22942,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="370" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
         <v>259</v>
       </c>
@@ -22992,7 +22992,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="371" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
         <v>534</v>
       </c>
@@ -23042,7 +23042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="372" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
         <v>680</v>
       </c>
@@ -23092,7 +23092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="373" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
         <v>916</v>
       </c>
@@ -23142,7 +23142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="374" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
         <v>1108</v>
       </c>
@@ -23192,7 +23192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="375" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
         <v>1185</v>
       </c>
@@ -23242,7 +23242,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="376" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
         <v>822</v>
       </c>
@@ -23292,7 +23292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="377" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
         <v>350</v>
       </c>
@@ -23342,7 +23342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="378" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
         <v>878</v>
       </c>
@@ -23392,7 +23392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="379" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
         <v>896</v>
       </c>
@@ -23442,7 +23442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="380" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
         <v>1044</v>
       </c>
@@ -23492,7 +23492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="381" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
         <v>1123</v>
       </c>
@@ -23542,7 +23542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="382" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
         <v>346</v>
       </c>
@@ -23592,7 +23592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="383" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
         <v>367</v>
       </c>
@@ -23642,7 +23642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="384" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
         <v>406</v>
       </c>
@@ -23692,7 +23692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="385" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
         <v>557</v>
       </c>
@@ -23742,7 +23742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="386" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
         <v>697</v>
       </c>
@@ -23792,7 +23792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="387" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
         <v>747</v>
       </c>
@@ -23842,7 +23842,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="388" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
         <v>747</v>
       </c>
@@ -23892,7 +23892,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="389" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
         <v>753</v>
       </c>
@@ -23942,7 +23942,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="390" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
         <v>755</v>
       </c>
@@ -23992,7 +23992,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="391" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
         <v>756</v>
       </c>
@@ -24042,7 +24042,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="392" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
         <v>758</v>
       </c>
@@ -24092,7 +24092,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="393" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
         <v>797</v>
       </c>
@@ -24142,7 +24142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="394" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
         <v>302</v>
       </c>
@@ -24192,7 +24192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="395" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
         <v>413</v>
       </c>
@@ -24242,7 +24242,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="396" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
         <v>765</v>
       </c>
@@ -24292,7 +24292,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="397" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
         <v>768</v>
       </c>
@@ -24342,7 +24342,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="398" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
         <v>770</v>
       </c>
@@ -24392,7 +24392,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="399" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
         <v>466</v>
       </c>
@@ -24442,7 +24442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="400" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
         <v>470</v>
       </c>
@@ -24492,7 +24492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="401" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
         <v>596</v>
       </c>
@@ -24542,7 +24542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="402" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
         <v>866</v>
       </c>
@@ -24592,7 +24592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="403" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
         <v>924</v>
       </c>
@@ -24642,7 +24642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="404" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
         <v>928</v>
       </c>
@@ -24692,7 +24692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="405" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
         <v>1062</v>
       </c>
@@ -24742,7 +24742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="406" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
         <v>1066</v>
       </c>
@@ -24792,7 +24792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="407" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
         <v>1089</v>
       </c>
@@ -24842,7 +24842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="408" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
         <v>789</v>
       </c>
@@ -24892,7 +24892,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="409" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
         <v>792</v>
       </c>
@@ -24942,7 +24942,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="410" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
         <v>1104</v>
       </c>
@@ -24992,7 +24992,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="411" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
         <v>89</v>
       </c>
@@ -25042,7 +25042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="412" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
         <v>89</v>
       </c>
@@ -25092,7 +25092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="413" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
         <v>178</v>
       </c>
@@ -25142,7 +25142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="414" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
         <v>293</v>
       </c>
@@ -25192,7 +25192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="415" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
         <v>392</v>
       </c>
@@ -25242,7 +25242,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="416" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
         <v>392</v>
       </c>
@@ -25292,7 +25292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="417" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
         <v>397</v>
       </c>
@@ -25342,7 +25342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="418" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
         <v>398</v>
       </c>
@@ -25392,7 +25392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="419" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
         <v>545</v>
       </c>
@@ -25442,7 +25442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="420" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
         <v>609</v>
       </c>
@@ -25492,7 +25492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="421" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
         <v>635</v>
       </c>
@@ -25542,7 +25542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="422" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
         <v>685</v>
       </c>
@@ -25592,7 +25592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="423" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
         <v>689</v>
       </c>
@@ -25642,7 +25642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="424" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
         <v>823</v>
       </c>
@@ -25692,7 +25692,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="425" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
         <v>823</v>
       </c>
@@ -25742,7 +25742,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="426" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
         <v>826</v>
       </c>
@@ -25792,7 +25792,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="427" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
         <v>827</v>
       </c>
@@ -25842,7 +25842,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="428" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
         <v>830</v>
       </c>
@@ -25892,7 +25892,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="429" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
         <v>831</v>
       </c>
@@ -25942,7 +25942,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="430" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
         <v>764</v>
       </c>
@@ -25992,7 +25992,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="431" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
         <v>874</v>
       </c>
@@ -26042,7 +26042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="432" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
         <v>920</v>
       </c>
@@ -26092,7 +26092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="433" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
         <v>1120</v>
       </c>
@@ -26142,7 +26142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="434" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
         <v>1142</v>
       </c>
@@ -26192,7 +26192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="435" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
         <v>1146</v>
       </c>
@@ -26242,7 +26242,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="436" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
         <v>1156</v>
       </c>
@@ -26292,7 +26292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="437" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
         <v>107</v>
       </c>
@@ -26342,7 +26342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="438" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
         <v>849</v>
       </c>
@@ -26392,7 +26392,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="439" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
         <v>851</v>
       </c>
@@ -26442,7 +26442,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="440" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
         <v>853</v>
       </c>
@@ -26492,7 +26492,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="441" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
         <v>855</v>
       </c>
@@ -26542,7 +26542,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="442" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
         <v>113</v>
       </c>
@@ -26592,7 +26592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="443" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
         <v>126</v>
       </c>
@@ -26642,7 +26642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="444" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
         <v>633</v>
       </c>
@@ -26692,7 +26692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="445" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
         <v>862</v>
       </c>
@@ -26742,7 +26742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="446" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
         <v>205</v>
       </c>
@@ -26792,7 +26792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="447" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
         <v>867</v>
       </c>
@@ -26842,7 +26842,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="448" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
         <v>870</v>
       </c>
@@ -26892,7 +26892,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="449" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
         <v>206</v>
       </c>
@@ -26942,7 +26942,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="450" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
         <v>235</v>
       </c>
@@ -26992,7 +26992,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="451" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
         <v>235</v>
       </c>
@@ -27042,7 +27042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="452" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
         <v>249</v>
       </c>
@@ -27092,7 +27092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="453" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
         <v>250</v>
       </c>
@@ -27142,7 +27142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="454" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
         <v>249</v>
       </c>
@@ -27192,7 +27192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="455" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
         <v>250</v>
       </c>
@@ -27242,7 +27242,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="456" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
         <v>885</v>
       </c>
@@ -27292,7 +27292,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="457" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
         <v>298</v>
       </c>
@@ -27342,7 +27342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="458" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
         <v>641</v>
       </c>
@@ -27392,7 +27392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="459" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
         <v>644</v>
       </c>
@@ -27442,7 +27442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="460" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
         <v>900</v>
       </c>
@@ -27492,7 +27492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="461" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
         <v>966</v>
       </c>
@@ -27542,7 +27542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="462" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
         <v>967</v>
       </c>
@@ -27592,7 +27592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="463" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
         <v>980</v>
       </c>
@@ -27642,7 +27642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="464" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
         <v>901</v>
       </c>
@@ -27692,7 +27692,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="465" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
         <v>903</v>
       </c>
@@ -27742,7 +27742,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="466" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
         <v>981</v>
       </c>
@@ -27792,7 +27792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="467" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
         <v>229</v>
       </c>
@@ -27842,7 +27842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="468" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
         <v>909</v>
       </c>
@@ -27892,7 +27892,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="469" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
         <v>912</v>
       </c>
@@ -27942,7 +27942,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="470" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
         <v>459</v>
       </c>
@@ -27992,7 +27992,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="471" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
         <v>471</v>
       </c>
@@ -28042,7 +28042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="472" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
         <v>592</v>
       </c>
@@ -28092,7 +28092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="473" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
         <v>787</v>
       </c>
@@ -28142,7 +28142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="474" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
         <v>788</v>
       </c>
@@ -28192,7 +28192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="475" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
         <v>225</v>
       </c>
@@ -28242,7 +28242,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="476" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
         <v>317</v>
       </c>
@@ -28292,7 +28292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="477" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
         <v>317</v>
       </c>
@@ -28342,7 +28342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="478" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
         <v>383</v>
       </c>
@@ -28392,7 +28392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="479" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
         <v>391</v>
       </c>
@@ -28442,7 +28442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="480" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
         <v>551</v>
       </c>
@@ -28492,7 +28492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="481" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
         <v>935</v>
       </c>
@@ -28542,7 +28542,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="482" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
         <v>935</v>
       </c>
@@ -28592,7 +28592,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="483" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
         <v>935</v>
       </c>
@@ -28642,7 +28642,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="484" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
         <v>935</v>
       </c>
@@ -28692,7 +28692,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="485" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
         <v>940</v>
       </c>
@@ -28742,7 +28742,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="486" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
         <v>605</v>
       </c>
@@ -28792,7 +28792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="487" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
         <v>746</v>
       </c>
@@ -28842,7 +28842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="488" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
         <v>818</v>
       </c>
@@ -28892,7 +28892,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="489" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
         <v>892</v>
       </c>
@@ -28942,7 +28942,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="490" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
         <v>1058</v>
       </c>
@@ -28992,7 +28992,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="491" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
         <v>24</v>
       </c>
@@ -29042,7 +29042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="492" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
         <v>955</v>
       </c>
@@ -29092,7 +29092,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="493" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
         <v>958</v>
       </c>
@@ -29142,7 +29142,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="494" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
         <v>959</v>
       </c>
@@ -29192,7 +29192,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="495" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
         <v>219</v>
       </c>
@@ -29242,7 +29242,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="496" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
         <v>287</v>
       </c>
@@ -29292,7 +29292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="497" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
         <v>447</v>
       </c>
@@ -29342,7 +29342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="498" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
         <v>448</v>
       </c>
@@ -29392,7 +29392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="499" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
         <v>449</v>
       </c>
@@ -29442,7 +29442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="500" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
         <v>450</v>
       </c>
@@ -29492,7 +29492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="501" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
         <v>451</v>
       </c>
@@ -29542,7 +29542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="502" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
         <v>452</v>
       </c>
@@ -29592,7 +29592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="503" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
         <v>453</v>
       </c>
@@ -29642,7 +29642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="504" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
         <v>501</v>
       </c>
@@ -29692,7 +29692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="505" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
         <v>622</v>
       </c>
@@ -29742,7 +29742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="506" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
         <v>982</v>
       </c>
@@ -29792,7 +29792,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="507" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
         <v>984</v>
       </c>
@@ -29842,7 +29842,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="508" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
         <v>986</v>
       </c>
@@ -29892,7 +29892,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="509" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
         <v>989</v>
       </c>
@@ -29942,7 +29942,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="510" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
         <v>991</v>
       </c>
@@ -29992,7 +29992,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="511" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
         <v>952</v>
       </c>
@@ -30042,7 +30042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="512" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
         <v>1026</v>
       </c>
@@ -30092,7 +30092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="513" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
         <v>1134</v>
       </c>
@@ -30142,7 +30142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="514" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
         <v>1138</v>
       </c>
@@ -30192,7 +30192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="515" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
         <v>40</v>
       </c>
@@ -30242,7 +30242,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="516" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
         <v>514</v>
       </c>
@@ -30292,7 +30292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="517" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
         <v>662</v>
       </c>
@@ -30342,7 +30342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="518" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
         <v>722</v>
       </c>
@@ -30392,7 +30392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="519" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
         <v>728</v>
       </c>
@@ -30442,7 +30442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="520" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
         <v>840</v>
       </c>
@@ -30492,7 +30492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="521" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
         <v>973</v>
       </c>
@@ -30542,7 +30542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="522" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
         <v>1038</v>
       </c>
@@ -30592,7 +30592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="523" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
         <v>32</v>
       </c>
@@ -30642,7 +30642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="524" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
         <v>508</v>
       </c>
@@ -30692,7 +30692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="525" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
         <v>508</v>
       </c>
@@ -30742,7 +30742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="526" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
         <v>1032</v>
       </c>
@@ -30792,7 +30792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="527" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
         <v>141</v>
       </c>
@@ -30842,7 +30842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="528" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
         <v>187</v>
       </c>
@@ -30892,7 +30892,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="529" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
         <v>353</v>
       </c>
@@ -30942,7 +30942,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="530" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
         <v>366</v>
       </c>
@@ -30992,7 +30992,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="531" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A531" t="s">
         <v>428</v>
       </c>
@@ -31042,7 +31042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="532" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
         <v>462</v>
       </c>
@@ -31092,7 +31092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="533" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
         <v>734</v>
       </c>
@@ -31142,7 +31142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="534" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
         <v>375</v>
       </c>
@@ -31192,7 +31192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="535" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
         <v>409</v>
       </c>
@@ -31242,7 +31242,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="536" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
         <v>416</v>
       </c>
@@ -31292,7 +31292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="537" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
         <v>476</v>
       </c>
@@ -31342,7 +31342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="538" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
         <v>576</v>
       </c>
@@ -31392,7 +31392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="539" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
         <v>934</v>
       </c>
@@ -31442,7 +31442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="540" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
         <v>263</v>
       </c>
@@ -31492,7 +31492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="541" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
         <v>1049</v>
       </c>
@@ -31542,7 +31542,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="542" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
         <v>1052</v>
       </c>
@@ -31592,7 +31592,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="543" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
         <v>541</v>
       </c>
@@ -31642,7 +31642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="544" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
         <v>193</v>
       </c>
@@ -31692,7 +31692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="545" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
         <v>193</v>
       </c>
@@ -31742,7 +31742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="546" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
         <v>477</v>
       </c>
@@ -31792,7 +31792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="547" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
         <v>477</v>
       </c>
@@ -31842,7 +31842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="548" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
         <v>480</v>
       </c>
@@ -31892,7 +31892,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="549" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
         <v>480</v>
       </c>
@@ -31942,7 +31942,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="550" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
         <v>1067</v>
       </c>
@@ -31992,7 +31992,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="551" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
         <v>1067</v>
       </c>
@@ -32042,7 +32042,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="552" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
         <v>1067</v>
       </c>
@@ -32092,7 +32092,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="553" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
         <v>1067</v>
       </c>
@@ -32142,7 +32142,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="554" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
         <v>1067</v>
       </c>
@@ -32192,7 +32192,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="555" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A555" t="s">
         <v>1067</v>
       </c>
@@ -32242,7 +32242,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="556" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A556" t="s">
         <v>1079</v>
       </c>
@@ -32292,7 +32292,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="557" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A557" t="s">
         <v>1079</v>
       </c>
@@ -32342,7 +32342,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="558" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A558" t="s">
         <v>1079</v>
       </c>
@@ -32392,7 +32392,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="559" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A559" t="s">
         <v>1080</v>
       </c>
@@ -32442,7 +32442,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="560" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A560" t="s">
         <v>1083</v>
       </c>
@@ -32492,7 +32492,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="561" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A561" t="s">
         <v>1084</v>
       </c>
@@ -32542,7 +32542,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="562" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
         <v>483</v>
       </c>
@@ -32592,7 +32592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="563" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
         <v>483</v>
       </c>
@@ -32642,7 +32642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="564" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
         <v>699</v>
       </c>
@@ -32692,7 +32692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="565" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
         <v>701</v>
       </c>
@@ -32742,7 +32742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="566" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
         <v>703</v>
       </c>
@@ -32792,7 +32792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="567" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A567" t="s">
         <v>1095</v>
       </c>
@@ -32842,7 +32842,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="568" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A568" t="s">
         <v>1095</v>
       </c>
@@ -32892,7 +32892,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="569" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A569" t="s">
         <v>1100</v>
       </c>
@@ -32942,7 +32942,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="570" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A570" t="s">
         <v>1100</v>
       </c>
@@ -32992,7 +32992,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="571" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
         <v>998</v>
       </c>
@@ -33042,7 +33042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="572" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
         <v>1000</v>
       </c>
@@ -33092,7 +33092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="573" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A573" t="s">
         <v>1002</v>
       </c>
@@ -33142,7 +33142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="574" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A574" t="s">
         <v>1164</v>
       </c>
@@ -33192,7 +33192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="575" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A575" t="s">
         <v>1109</v>
       </c>
@@ -33242,7 +33242,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="576" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A576" t="s">
         <v>1112</v>
       </c>
@@ -33292,7 +33292,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="577" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A577" t="s">
         <v>1166</v>
       </c>
@@ -33342,7 +33342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="578" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A578" t="s">
         <v>1168</v>
       </c>
@@ -33392,7 +33392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="579" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A579" t="s">
         <v>491</v>
       </c>
@@ -33442,7 +33442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="580" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A580" t="s">
         <v>494</v>
       </c>
@@ -33492,7 +33492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="581" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A581" t="s">
         <v>1121</v>
       </c>
@@ -33542,7 +33542,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="582" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A582" t="s">
         <v>710</v>
       </c>
@@ -33592,7 +33592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="583" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A583" t="s">
         <v>715</v>
       </c>
@@ -33642,7 +33642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="584" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A584" t="s">
         <v>997</v>
       </c>
@@ -33692,7 +33692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="585" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A585" t="s">
         <v>1004</v>
       </c>
@@ -33742,7 +33742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="586" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A586" t="s">
         <v>1006</v>
       </c>
@@ -33792,7 +33792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="587" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A587" t="s">
         <v>1014</v>
       </c>
@@ -33842,7 +33842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="588" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A588" t="s">
         <v>1016</v>
       </c>
@@ -33892,7 +33892,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="589" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A589" t="s">
         <v>1016</v>
       </c>
@@ -33942,7 +33942,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="590" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="590" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A590" t="s">
         <v>1016</v>
       </c>
@@ -33992,7 +33992,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="591" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="591" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A591" t="s">
         <v>1016</v>
       </c>
@@ -34042,7 +34042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="592" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A592" t="s">
         <v>1130</v>
       </c>
@@ -34092,7 +34092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="593" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="593" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A593" t="s">
         <v>1176</v>
       </c>
@@ -34142,7 +34142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="594" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="594" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A594" t="s">
         <v>1147</v>
       </c>
@@ -34192,7 +34192,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="595" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="595" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A595" t="s">
         <v>1149</v>
       </c>
@@ -34242,7 +34242,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="596" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="596" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A596" t="s">
         <v>1152</v>
       </c>
@@ -34292,7 +34292,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="597" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="597" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A597" t="s">
         <v>1183</v>
       </c>
@@ -34342,7 +34342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="598" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="598" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A598" t="s">
         <v>1187</v>
       </c>
@@ -34392,7 +34392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="599" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="599" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A599" t="s">
         <v>1157</v>
       </c>
@@ -34442,7 +34442,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="600" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="600" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A600" t="s">
         <v>1157</v>
       </c>
@@ -34492,7 +34492,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="601" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="601" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A601" t="s">
         <v>1157</v>
       </c>
@@ -34542,7 +34542,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="602" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="602" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A602" t="s">
         <v>1157</v>
       </c>
@@ -34592,7 +34592,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="603" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="603" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A603" t="s">
         <v>1157</v>
       </c>
@@ -34642,7 +34642,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="604" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="604" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A604" t="s">
         <v>1157</v>
       </c>
@@ -34692,7 +34692,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="605" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="605" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A605" t="s">
         <v>1189</v>
       </c>
@@ -34742,7 +34742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="606" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="606" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A606" t="s">
         <v>1191</v>
       </c>
@@ -34792,7 +34792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="607" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="607" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A607" t="s">
         <v>1191</v>
       </c>
@@ -34842,7 +34842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="608" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="608" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A608" t="s">
         <v>803</v>
       </c>
@@ -34892,7 +34892,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="609" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="609" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A609" t="s">
         <v>1008</v>
       </c>
@@ -34942,7 +34942,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="610" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="610" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A610" t="s">
         <v>1010</v>
       </c>
@@ -34992,7 +34992,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="611" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="611" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A611" t="s">
         <v>1178</v>
       </c>
@@ -35042,7 +35042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="612" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="612" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A612" t="s">
         <v>492</v>
       </c>
@@ -35092,7 +35092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="613" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="613" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A613" t="s">
         <v>711</v>
       </c>
@@ -35142,7 +35142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="614" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="614" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A614" t="s">
         <v>713</v>
       </c>
@@ -35192,7 +35192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="615" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="615" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A615" t="s">
         <v>1012</v>
       </c>
@@ -35242,7 +35242,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="616" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="616" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A616" t="s">
         <v>1170</v>
       </c>
@@ -35292,7 +35292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="617" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="617" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A617" t="s">
         <v>1170</v>
       </c>
@@ -35342,7 +35342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="618" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="618" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A618" t="s">
         <v>1173</v>
       </c>
@@ -35392,7 +35392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="619" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="619" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A619" t="s">
         <v>1173</v>
       </c>
@@ -35442,7 +35442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="620" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="620" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A620" t="s">
         <v>1180</v>
       </c>
@@ -35492,7 +35492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="621" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="621" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A621" t="s">
         <v>1180</v>
       </c>
@@ -35546,7 +35546,7 @@
   <autoFilter ref="A1:P621" xr:uid="{6A7ECD2C-6F5B-4E4D-962E-4B55F2FEEDC6}">
     <filterColumn colId="15">
       <filters>
-        <filter val="Y"/>
+        <filter val="N"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P621">

--- a/all_generations_pokemon_families.xlsx
+++ b/all_generations_pokemon_families.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3c6863eb3d429a98/Documents/GitHub/pokefirered-expansion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="823" documentId="8_{3DE7B663-32D8-4B09-ACF8-07A7237E0E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C181B9F9-BB70-491F-A447-42283E9B0E19}"/>
+  <xr:revisionPtr revIDLastSave="853" documentId="8_{3DE7B663-32D8-4B09-ACF8-07A7237E0E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3FDBB079-66C5-4EA4-B129-B35A15CD45C5}"/>
   <bookViews>
     <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{913F818F-7E2F-42B8-8FB9-B28A63806581}"/>
   </bookViews>

--- a/all_generations_pokemon_families.xlsx
+++ b/all_generations_pokemon_families.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3c6863eb3d429a98/Documents/GitHub/pokefirered-expansion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="853" documentId="8_{3DE7B663-32D8-4B09-ACF8-07A7237E0E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3FDBB079-66C5-4EA4-B129-B35A15CD45C5}"/>
+  <xr:revisionPtr revIDLastSave="889" documentId="8_{3DE7B663-32D8-4B09-ACF8-07A7237E0E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60FDAA18-FFB2-44B4-9137-D01E1BBD1DDC}"/>
   <bookViews>
     <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{913F818F-7E2F-42B8-8FB9-B28A63806581}"/>
   </bookViews>

--- a/all_generations_pokemon_families.xlsx
+++ b/all_generations_pokemon_families.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3c6863eb3d429a98/Documents/GitHub/pokefirered-expansion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="889" documentId="8_{3DE7B663-32D8-4B09-ACF8-07A7237E0E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60FDAA18-FFB2-44B4-9137-D01E1BBD1DDC}"/>
+  <xr:revisionPtr revIDLastSave="903" documentId="8_{3DE7B663-32D8-4B09-ACF8-07A7237E0E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C143B821-1A07-4C49-9FEA-1095ABF7CE86}"/>
   <bookViews>
     <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{913F818F-7E2F-42B8-8FB9-B28A63806581}"/>
   </bookViews>
@@ -5042,7 +5042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="12" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>136</v>
       </c>
@@ -5142,7 +5142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>49</v>
       </c>
@@ -5192,7 +5192,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>52</v>
       </c>
@@ -5242,7 +5242,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>54</v>
       </c>
@@ -5442,7 +5442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>62</v>
       </c>
@@ -5492,7 +5492,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>65</v>
       </c>
@@ -5542,7 +5542,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>62</v>
       </c>
@@ -5592,7 +5592,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>62</v>
       </c>
@@ -5642,7 +5642,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>65</v>
       </c>
@@ -5692,7 +5692,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>71</v>
       </c>
@@ -5742,7 +5742,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>74</v>
       </c>
@@ -5792,7 +5792,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>75</v>
       </c>
@@ -5842,7 +5842,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>78</v>
       </c>
@@ -6192,7 +6192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="35" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>101</v>
       </c>
@@ -6242,7 +6242,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="36" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>108</v>
       </c>
@@ -6892,7 +6892,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>122</v>
       </c>
@@ -6942,7 +6942,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>126</v>
       </c>
@@ -6992,7 +6992,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>130</v>
       </c>
@@ -7042,7 +7042,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>133</v>
       </c>
@@ -7092,7 +7092,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>135</v>
       </c>
@@ -7292,7 +7292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>142</v>
       </c>
@@ -7342,7 +7342,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>145</v>
       </c>
@@ -7392,7 +7392,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>145</v>
       </c>
@@ -7442,7 +7442,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>150</v>
       </c>
@@ -7492,7 +7492,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>151</v>
       </c>
@@ -7742,7 +7742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>160</v>
       </c>
@@ -7792,7 +7792,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>163</v>
       </c>
@@ -7842,7 +7842,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>160</v>
       </c>
@@ -7892,7 +7892,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>163</v>
       </c>
@@ -7942,7 +7942,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>166</v>
       </c>
@@ -7992,7 +7992,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>169</v>
       </c>
@@ -8042,7 +8042,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>166</v>
       </c>
@@ -8092,7 +8092,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>169</v>
       </c>
@@ -8142,7 +8142,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>166</v>
       </c>
@@ -8192,7 +8192,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>174</v>
       </c>
@@ -8542,7 +8542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="82" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>581</v>
       </c>
@@ -9542,7 +9542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="102" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>1143</v>
       </c>
@@ -9592,7 +9592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="103" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>863</v>
       </c>
@@ -9992,7 +9992,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>239</v>
       </c>
@@ -10042,7 +10042,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>242</v>
       </c>
@@ -10092,7 +10092,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>239</v>
       </c>
@@ -10142,7 +10142,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>242</v>
       </c>
@@ -10792,7 +10792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>264</v>
       </c>
@@ -10842,7 +10842,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>264</v>
       </c>
@@ -10892,7 +10892,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>269</v>
       </c>
@@ -11042,7 +11042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>274</v>
       </c>
@@ -11092,7 +11092,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="133" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>277</v>
       </c>
@@ -11142,7 +11142,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="134" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>278</v>
       </c>
@@ -11192,7 +11192,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="135" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>281</v>
       </c>
@@ -11242,7 +11242,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="136" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>278</v>
       </c>
@@ -11292,7 +11292,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="137" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>281</v>
       </c>
@@ -11842,7 +11842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="148" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>303</v>
       </c>
@@ -11892,7 +11892,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="149" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>306</v>
       </c>
@@ -12592,7 +12592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="163" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>325</v>
       </c>
@@ -12642,7 +12642,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="164" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>325</v>
       </c>
@@ -12692,7 +12692,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="165" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>325</v>
       </c>
@@ -12742,7 +12742,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="166" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>333</v>
       </c>
@@ -12792,7 +12792,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="167" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>334</v>
       </c>
@@ -12842,7 +12842,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="168" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>335</v>
       </c>
@@ -12892,7 +12892,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="169" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>336</v>
       </c>
@@ -12942,7 +12942,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="170" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>341</v>
       </c>
@@ -13142,7 +13142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="174" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>346</v>
       </c>
@@ -13342,7 +13342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="178" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>354</v>
       </c>
@@ -13392,7 +13392,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="179" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>354</v>
       </c>
@@ -13442,7 +13442,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="180" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>359</v>
       </c>
@@ -13492,7 +13492,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="181" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>361</v>
       </c>
@@ -13542,7 +13542,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="182" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>1113</v>
       </c>
@@ -13842,7 +13842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="188" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>376</v>
       </c>
@@ -13892,7 +13892,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="189" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>379</v>
       </c>
@@ -14142,7 +14142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="194" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>1139</v>
       </c>
@@ -14442,7 +14442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="200" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>342</v>
       </c>
@@ -14492,7 +14492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="201" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>399</v>
       </c>
@@ -14542,7 +14542,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="202" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>402</v>
       </c>
@@ -14592,7 +14592,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="203" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>342</v>
       </c>
@@ -14892,7 +14892,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="209" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>417</v>
       </c>
@@ -14942,7 +14942,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="210" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>419</v>
       </c>
@@ -14992,7 +14992,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="211" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>419</v>
       </c>
@@ -15042,7 +15042,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="212" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>419</v>
       </c>
@@ -15092,7 +15092,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="213" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>419</v>
       </c>
@@ -15142,7 +15142,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="214" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>424</v>
       </c>
@@ -15192,7 +15192,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="215" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>427</v>
       </c>
@@ -16142,7 +16142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="234" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>104</v>
       </c>
@@ -16192,7 +16192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="235" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>111</v>
       </c>
@@ -16242,7 +16242,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="236" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>454</v>
       </c>
@@ -18092,7 +18092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="273" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>523</v>
       </c>
@@ -18142,7 +18142,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="274" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>526</v>
       </c>
@@ -18942,7 +18942,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="290" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>558</v>
       </c>
@@ -18992,7 +18992,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="291" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>561</v>
       </c>
@@ -19042,7 +19042,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="292" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
         <v>562</v>
       </c>
@@ -19092,7 +19092,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="293" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>565</v>
       </c>
@@ -19142,7 +19142,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="294" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>567</v>
       </c>
@@ -19192,7 +19192,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="295" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
         <v>568</v>
       </c>
@@ -19242,7 +19242,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="296" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
         <v>572</v>
       </c>
@@ -19392,7 +19392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="299" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
         <v>577</v>
       </c>
@@ -19442,7 +19442,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="300" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
         <v>580</v>
       </c>
@@ -19892,7 +19892,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="309" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
         <v>597</v>
       </c>
@@ -19942,7 +19942,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="310" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
         <v>600</v>
       </c>
@@ -20192,7 +20192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="315" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
         <v>610</v>
       </c>
@@ -20242,7 +20242,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="316" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
         <v>610</v>
       </c>
@@ -20292,7 +20292,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="317" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
         <v>617</v>
       </c>
@@ -20342,7 +20342,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="318" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
         <v>617</v>
       </c>
@@ -20542,7 +20542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="322" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
         <v>623</v>
       </c>
@@ -20592,7 +20592,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="323" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
         <v>626</v>
       </c>
@@ -20642,7 +20642,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="324" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
         <v>627</v>
       </c>
@@ -20692,7 +20692,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="325" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
         <v>627</v>
       </c>
@@ -20742,7 +20742,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="326" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
         <v>632</v>
       </c>
@@ -20842,7 +20842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="328" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
         <v>139</v>
       </c>
@@ -21192,7 +21192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="335" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
         <v>645</v>
       </c>
@@ -21242,7 +21242,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="336" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
         <v>648</v>
       </c>
@@ -21292,7 +21292,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="337" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
         <v>648</v>
       </c>
@@ -21342,7 +21342,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="338" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
         <v>652</v>
       </c>
@@ -21392,7 +21392,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="339" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
         <v>652</v>
       </c>
@@ -21692,7 +21692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="345" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
         <v>663</v>
       </c>
@@ -21742,7 +21742,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="346" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
         <v>663</v>
       </c>
@@ -21792,7 +21792,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="347" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
         <v>667</v>
       </c>
@@ -21842,7 +21842,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="348" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
         <v>668</v>
       </c>
@@ -21892,7 +21892,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="349" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
         <v>671</v>
       </c>
@@ -21942,7 +21942,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="350" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
         <v>672</v>
       </c>
@@ -22292,7 +22292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="357" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
         <v>587</v>
       </c>
@@ -22342,7 +22342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="358" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
         <v>690</v>
       </c>
@@ -22392,7 +22392,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="359" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
         <v>694</v>
       </c>
@@ -22442,7 +22442,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="360" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
         <v>695</v>
       </c>
@@ -22842,7 +22842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="368" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
         <v>1116</v>
       </c>
@@ -23542,7 +23542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="382" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
         <v>346</v>
       </c>
@@ -23792,7 +23792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="387" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
         <v>747</v>
       </c>
@@ -23842,7 +23842,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="388" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
         <v>747</v>
       </c>
@@ -23892,7 +23892,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="389" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
         <v>753</v>
       </c>
@@ -23942,7 +23942,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="390" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
         <v>755</v>
       </c>
@@ -23992,7 +23992,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="391" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
         <v>756</v>
       </c>
@@ -24042,7 +24042,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="392" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
         <v>758</v>
       </c>
@@ -24242,7 +24242,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="396" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
         <v>765</v>
       </c>
@@ -24292,7 +24292,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="397" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
         <v>768</v>
       </c>
@@ -24342,7 +24342,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="398" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
         <v>770</v>
       </c>
@@ -24542,7 +24542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="402" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
         <v>866</v>
       </c>
@@ -24842,7 +24842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="408" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
         <v>789</v>
       </c>
@@ -24892,7 +24892,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="409" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
         <v>792</v>
       </c>
@@ -25642,7 +25642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="424" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
         <v>823</v>
       </c>
@@ -25692,7 +25692,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="425" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
         <v>823</v>
       </c>
@@ -25742,7 +25742,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="426" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
         <v>826</v>
       </c>
@@ -25792,7 +25792,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="427" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
         <v>827</v>
       </c>
@@ -25842,7 +25842,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="428" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
         <v>830</v>
       </c>
@@ -25892,7 +25892,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="429" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
         <v>831</v>
       </c>
@@ -26142,7 +26142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="434" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
         <v>1142</v>
       </c>
@@ -26192,7 +26192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="435" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
         <v>1146</v>
       </c>
@@ -26292,7 +26292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="437" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
         <v>107</v>
       </c>
@@ -26342,7 +26342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="438" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
         <v>849</v>
       </c>
@@ -26392,7 +26392,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="439" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
         <v>851</v>
       </c>
@@ -26442,7 +26442,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="440" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
         <v>853</v>
       </c>
@@ -26492,7 +26492,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="441" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
         <v>855</v>
       </c>
@@ -26542,7 +26542,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="442" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
         <v>113</v>
       </c>
@@ -26792,7 +26792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="447" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
         <v>867</v>
       </c>
@@ -26842,7 +26842,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="448" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
         <v>870</v>
       </c>
@@ -27142,7 +27142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="454" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
         <v>249</v>
       </c>
@@ -27192,7 +27192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="455" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
         <v>250</v>
       </c>
@@ -27242,7 +27242,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="456" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
         <v>885</v>
       </c>
@@ -27642,7 +27642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="464" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
         <v>901</v>
       </c>
@@ -27692,7 +27692,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="465" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
         <v>903</v>
       </c>
@@ -27842,7 +27842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="468" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
         <v>909</v>
       </c>
@@ -27892,7 +27892,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="469" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
         <v>912</v>
       </c>
@@ -28492,7 +28492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="481" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
         <v>935</v>
       </c>
@@ -28542,7 +28542,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="482" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
         <v>935</v>
       </c>
@@ -28592,7 +28592,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="483" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
         <v>935</v>
       </c>
@@ -28642,7 +28642,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="484" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
         <v>935</v>
       </c>
@@ -28692,7 +28692,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="485" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
         <v>940</v>
       </c>
@@ -29042,7 +29042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="492" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
         <v>955</v>
       </c>
@@ -29092,7 +29092,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="493" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
         <v>958</v>
       </c>
@@ -29142,7 +29142,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="494" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
         <v>959</v>
       </c>
@@ -29742,7 +29742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="506" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
         <v>982</v>
       </c>
@@ -29792,7 +29792,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="507" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
         <v>984</v>
       </c>
@@ -29842,7 +29842,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="508" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
         <v>986</v>
       </c>
@@ -29892,7 +29892,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="509" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
         <v>989</v>
       </c>
@@ -29942,7 +29942,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="510" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
         <v>991</v>
       </c>
@@ -30792,7 +30792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="527" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
         <v>141</v>
       </c>
@@ -31492,7 +31492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="541" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
         <v>1049</v>
       </c>
@@ -31542,7 +31542,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="542" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
         <v>1052</v>
       </c>
@@ -31942,7 +31942,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="550" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
         <v>1067</v>
       </c>
@@ -31992,7 +31992,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="551" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
         <v>1067</v>
       </c>
@@ -32042,7 +32042,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="552" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
         <v>1067</v>
       </c>
@@ -32092,7 +32092,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="553" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
         <v>1067</v>
       </c>
@@ -32142,7 +32142,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="554" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
         <v>1067</v>
       </c>
@@ -32192,7 +32192,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="555" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A555" t="s">
         <v>1067</v>
       </c>
@@ -32242,7 +32242,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="556" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A556" t="s">
         <v>1079</v>
       </c>
@@ -32292,7 +32292,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="557" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A557" t="s">
         <v>1079</v>
       </c>
@@ -32342,7 +32342,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="558" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A558" t="s">
         <v>1079</v>
       </c>
@@ -32392,7 +32392,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="559" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A559" t="s">
         <v>1080</v>
       </c>
@@ -32442,7 +32442,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="560" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A560" t="s">
         <v>1083</v>
       </c>
@@ -32492,7 +32492,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="561" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A561" t="s">
         <v>1084</v>
       </c>
@@ -32792,7 +32792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="567" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A567" t="s">
         <v>1095</v>
       </c>
@@ -32842,7 +32842,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="568" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A568" t="s">
         <v>1095</v>
       </c>
@@ -32892,7 +32892,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="569" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A569" t="s">
         <v>1100</v>
       </c>
@@ -32942,7 +32942,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="570" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A570" t="s">
         <v>1100</v>
       </c>
@@ -33192,7 +33192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="575" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A575" t="s">
         <v>1109</v>
       </c>
@@ -33242,7 +33242,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="576" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A576" t="s">
         <v>1112</v>
       </c>
@@ -33492,7 +33492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="581" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A581" t="s">
         <v>1121</v>
       </c>
@@ -34142,7 +34142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="594" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="594" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A594" t="s">
         <v>1147</v>
       </c>
@@ -34192,7 +34192,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="595" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="595" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A595" t="s">
         <v>1149</v>
       </c>
@@ -34242,7 +34242,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="596" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="596" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A596" t="s">
         <v>1152</v>
       </c>
@@ -34392,7 +34392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="599" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="599" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A599" t="s">
         <v>1157</v>
       </c>
@@ -34442,7 +34442,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="600" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="600" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A600" t="s">
         <v>1157</v>
       </c>
@@ -34492,7 +34492,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="601" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="601" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A601" t="s">
         <v>1157</v>
       </c>
@@ -34542,7 +34542,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="602" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="602" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A602" t="s">
         <v>1157</v>
       </c>
@@ -34592,7 +34592,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="603" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="603" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A603" t="s">
         <v>1157</v>
       </c>
@@ -34642,7 +34642,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="604" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="604" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A604" t="s">
         <v>1157</v>
       </c>
@@ -35544,9 +35544,14 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:P621" xr:uid="{6A7ECD2C-6F5B-4E4D-962E-4B55F2FEEDC6}">
+    <filterColumn colId="9">
+      <filters>
+        <filter val="TYPE_POISON"/>
+      </filters>
+    </filterColumn>
     <filterColumn colId="15">
       <filters>
-        <filter val="N"/>
+        <filter val="Y"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P621">

--- a/all_generations_pokemon_families.xlsx
+++ b/all_generations_pokemon_families.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3c6863eb3d429a98/Documents/GitHub/pokefirered-expansion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="903" documentId="8_{3DE7B663-32D8-4B09-ACF8-07A7237E0E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C143B821-1A07-4C49-9FEA-1095ABF7CE86}"/>
+  <xr:revisionPtr revIDLastSave="911" documentId="8_{3DE7B663-32D8-4B09-ACF8-07A7237E0E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C352AAC-F15E-4A9F-A033-83CC755FFAC0}"/>
   <bookViews>
     <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{913F818F-7E2F-42B8-8FB9-B28A63806581}"/>
   </bookViews>
@@ -5042,7 +5042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>136</v>
       </c>
@@ -6192,7 +6192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>101</v>
       </c>
@@ -6242,7 +6242,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>108</v>
       </c>
@@ -8542,7 +8542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>581</v>
       </c>
@@ -9142,7 +9142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="94" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>942</v>
       </c>
@@ -9192,7 +9192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="95" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>946</v>
       </c>
@@ -9542,7 +9542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>1143</v>
       </c>
@@ -9592,7 +9592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>863</v>
       </c>
@@ -10492,7 +10492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="121" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>288</v>
       </c>
@@ -13542,7 +13542,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="182" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>1113</v>
       </c>
@@ -14142,7 +14142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="194" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>1139</v>
       </c>
@@ -14442,7 +14442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="200" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>342</v>
       </c>
@@ -14592,7 +14592,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="203" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>342</v>
       </c>
@@ -15442,7 +15442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="220" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>1101</v>
       </c>
@@ -16142,7 +16142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="234" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>104</v>
       </c>
@@ -16192,7 +16192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="235" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>111</v>
       </c>
@@ -17642,7 +17642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="264" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>291</v>
       </c>
@@ -17692,7 +17692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="265" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>291</v>
       </c>
@@ -19792,7 +19792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="307" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
         <v>593</v>
       </c>
@@ -20842,7 +20842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="328" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
         <v>139</v>
       </c>
@@ -22292,7 +22292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="357" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
         <v>587</v>
       </c>
@@ -22692,7 +22692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="365" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
         <v>945</v>
       </c>
@@ -22742,7 +22742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="366" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
         <v>949</v>
       </c>
@@ -22842,7 +22842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="368" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
         <v>1116</v>
       </c>
@@ -23492,7 +23492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="381" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
         <v>1123</v>
       </c>
@@ -23542,7 +23542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="382" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
         <v>346</v>
       </c>
@@ -24492,7 +24492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="401" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
         <v>596</v>
       </c>
@@ -24542,7 +24542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="402" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
         <v>866</v>
       </c>
@@ -24942,7 +24942,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="410" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
         <v>1104</v>
       </c>
@@ -25142,7 +25142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="414" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
         <v>293</v>
       </c>
@@ -26142,7 +26142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="434" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
         <v>1142</v>
       </c>
@@ -26192,7 +26192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="435" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
         <v>1146</v>
       </c>
@@ -26292,7 +26292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="437" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
         <v>107</v>
       </c>
@@ -26542,7 +26542,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="442" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
         <v>113</v>
       </c>
@@ -27142,7 +27142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="454" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
         <v>249</v>
       </c>
@@ -27192,7 +27192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="455" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
         <v>250</v>
       </c>
@@ -29992,7 +29992,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="511" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
         <v>952</v>
       </c>
@@ -30792,7 +30792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="527" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
         <v>141</v>
       </c>
@@ -35442,7 +35442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="620" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="620" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A620" t="s">
         <v>1180</v>
       </c>
@@ -35492,7 +35492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="621" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="621" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A621" t="s">
         <v>1180</v>
       </c>
@@ -35546,7 +35546,7 @@
   <autoFilter ref="A1:P621" xr:uid="{6A7ECD2C-6F5B-4E4D-962E-4B55F2FEEDC6}">
     <filterColumn colId="9">
       <filters>
-        <filter val="TYPE_POISON"/>
+        <filter val="TYPE_GHOST"/>
       </filters>
     </filterColumn>
     <filterColumn colId="15">

--- a/all_generations_pokemon_families.xlsx
+++ b/all_generations_pokemon_families.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3c6863eb3d429a98/Documents/GitHub/pokefirered-expansion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="911" documentId="8_{3DE7B663-32D8-4B09-ACF8-07A7237E0E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C352AAC-F15E-4A9F-A033-83CC755FFAC0}"/>
+  <xr:revisionPtr revIDLastSave="917" documentId="8_{3DE7B663-32D8-4B09-ACF8-07A7237E0E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63F96B43-E45C-4805-B998-1B4CFBE6DD77}"/>
   <bookViews>
     <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{913F818F-7E2F-42B8-8FB9-B28A63806581}"/>
   </bookViews>
@@ -6042,7 +6042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="32" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>653</v>
       </c>
@@ -7542,7 +7542,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="62" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>122</v>
       </c>
@@ -9142,7 +9142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>942</v>
       </c>
@@ -9192,7 +9192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>946</v>
       </c>
@@ -9942,7 +9942,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="110" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>875</v>
       </c>
@@ -10242,7 +10242,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="116" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>26</v>
       </c>
@@ -10292,7 +10292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="117" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>502</v>
       </c>
@@ -10342,7 +10342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="118" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>1027</v>
       </c>
@@ -10492,7 +10492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>288</v>
       </c>
@@ -10692,7 +10692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="125" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>723</v>
       </c>
@@ -15442,7 +15442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="220" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>1101</v>
       </c>
@@ -15542,7 +15542,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="222" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>189</v>
       </c>
@@ -15592,7 +15592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="223" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>189</v>
       </c>
@@ -16292,7 +16292,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="237" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>410</v>
       </c>
@@ -17192,7 +17192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="255" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>656</v>
       </c>
@@ -17392,7 +17392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="259" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>30</v>
       </c>
@@ -17642,7 +17642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="264" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>291</v>
       </c>
@@ -17692,7 +17692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="265" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>291</v>
       </c>
@@ -17792,7 +17792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="267" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>505</v>
       </c>
@@ -17842,7 +17842,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="268" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>505</v>
       </c>
@@ -18042,7 +18042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="272" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>726</v>
       </c>
@@ -18292,7 +18292,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="277" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>1030</v>
       </c>
@@ -19792,7 +19792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="307" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
         <v>593</v>
       </c>
@@ -22042,7 +22042,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="352" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
         <v>324</v>
       </c>
@@ -22642,7 +22642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="364" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
         <v>879</v>
       </c>
@@ -22692,7 +22692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="365" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
         <v>945</v>
       </c>
@@ -22742,7 +22742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="366" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
         <v>949</v>
       </c>
@@ -23342,7 +23342,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="378" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
         <v>878</v>
       </c>
@@ -23492,7 +23492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="381" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
         <v>1123</v>
       </c>
@@ -24192,7 +24192,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="395" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
         <v>413</v>
       </c>
@@ -24492,7 +24492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="401" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
         <v>596</v>
       </c>
@@ -24942,7 +24942,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="410" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
         <v>1104</v>
       </c>
@@ -25142,7 +25142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="414" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
         <v>293</v>
       </c>
@@ -26592,7 +26592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="443" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
         <v>126</v>
       </c>
@@ -29392,7 +29392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="499" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
         <v>449</v>
       </c>
@@ -29992,7 +29992,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="511" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
         <v>952</v>
       </c>
@@ -30392,7 +30392,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="519" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
         <v>728</v>
       </c>
@@ -30592,7 +30592,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="523" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
         <v>32</v>
       </c>
@@ -30642,7 +30642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="524" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
         <v>508</v>
       </c>
@@ -30692,7 +30692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="525" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
         <v>508</v>
       </c>
@@ -30742,7 +30742,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="526" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
         <v>1032</v>
       </c>
@@ -31242,7 +31242,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="536" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
         <v>416</v>
       </c>
@@ -31642,7 +31642,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="544" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
         <v>193</v>
       </c>
@@ -31692,7 +31692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="545" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
         <v>193</v>
       </c>
@@ -32542,7 +32542,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="562" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
         <v>483</v>
       </c>
@@ -32692,7 +32692,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="565" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
         <v>701</v>
       </c>
@@ -34092,7 +34092,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="593" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="593" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A593" t="s">
         <v>1176</v>
       </c>
@@ -35142,7 +35142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="614" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="614" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A614" t="s">
         <v>713</v>
       </c>
@@ -35442,7 +35442,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="620" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="620" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A620" t="s">
         <v>1180</v>
       </c>
@@ -35492,7 +35492,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="621" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="621" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A621" t="s">
         <v>1180</v>
       </c>
@@ -35546,7 +35546,7 @@
   <autoFilter ref="A1:P621" xr:uid="{6A7ECD2C-6F5B-4E4D-962E-4B55F2FEEDC6}">
     <filterColumn colId="9">
       <filters>
-        <filter val="TYPE_GHOST"/>
+        <filter val="TYPE_FIRE"/>
       </filters>
     </filterColumn>
     <filterColumn colId="15">

--- a/all_generations_pokemon_families.xlsx
+++ b/all_generations_pokemon_families.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3c6863eb3d429a98/Documents/GitHub/pokefirered-expansion/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Austin\Documents\PokemonDecompBuild\pokefirered-expansion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="917" documentId="8_{3DE7B663-32D8-4B09-ACF8-07A7237E0E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63F96B43-E45C-4805-B998-1B4CFBE6DD77}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73F2262A-E5B3-4185-A537-AAA20E3A2DD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{913F818F-7E2F-42B8-8FB9-B28A63806581}"/>
   </bookViews>
@@ -4157,10 +4157,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -4992,7 +4988,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="11" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>573</v>
       </c>
@@ -6042,7 +6038,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>653</v>
       </c>
@@ -6492,7 +6488,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="41" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>1090</v>
       </c>
@@ -6592,7 +6588,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="43" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>857</v>
       </c>
@@ -7542,7 +7538,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>122</v>
       </c>
@@ -7692,7 +7688,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="65" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>220</v>
       </c>
@@ -8742,7 +8738,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="86" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>793</v>
       </c>
@@ -9942,7 +9938,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>875</v>
       </c>
@@ -10242,7 +10238,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>26</v>
       </c>
@@ -10292,7 +10288,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>502</v>
       </c>
@@ -10342,7 +10338,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>1027</v>
       </c>
@@ -10642,7 +10638,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="124" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>717</v>
       </c>
@@ -10692,7 +10688,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>723</v>
       </c>
@@ -11642,7 +11638,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="144" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>15</v>
       </c>
@@ -11692,7 +11688,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="145" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>496</v>
       </c>
@@ -11742,7 +11738,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="146" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>1021</v>
       </c>
@@ -12242,7 +12238,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="156" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>313</v>
       </c>
@@ -12292,7 +12288,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="157" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>313</v>
       </c>
@@ -14192,7 +14188,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="195" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>1153</v>
       </c>
@@ -14292,7 +14288,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="197" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>893</v>
       </c>
@@ -15542,7 +15538,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="222" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>189</v>
       </c>
@@ -15592,7 +15588,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="223" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>189</v>
       </c>
@@ -16292,7 +16288,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="237" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>410</v>
       </c>
@@ -16742,7 +16738,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="246" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>223</v>
       </c>
@@ -17192,7 +17188,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="255" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>656</v>
       </c>
@@ -17242,7 +17238,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="256" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>860</v>
       </c>
@@ -17342,7 +17338,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="258" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>22</v>
       </c>
@@ -17392,7 +17388,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="259" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>30</v>
       </c>
@@ -17742,7 +17738,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="266" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>499</v>
       </c>
@@ -17792,7 +17788,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="267" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>505</v>
       </c>
@@ -17842,7 +17838,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="268" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>505</v>
       </c>
@@ -17992,7 +17988,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="271" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>720</v>
       </c>
@@ -18042,7 +18038,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="272" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>726</v>
       </c>
@@ -18242,7 +18238,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="276" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>1024</v>
       </c>
@@ -18292,7 +18288,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="277" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>1030</v>
       </c>
@@ -19692,7 +19688,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="305" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
         <v>362</v>
       </c>
@@ -20492,7 +20488,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="321" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
         <v>1093</v>
       </c>
@@ -20792,7 +20788,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="327" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
         <v>1093</v>
       </c>
@@ -21592,7 +21588,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="343" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
         <v>953</v>
       </c>
@@ -22042,7 +22038,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="352" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
         <v>324</v>
       </c>
@@ -22642,7 +22638,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="364" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
         <v>879</v>
       </c>
@@ -23342,7 +23338,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="378" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
         <v>878</v>
       </c>
@@ -23392,7 +23388,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="379" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
         <v>896</v>
       </c>
@@ -24092,7 +24088,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="393" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
         <v>797</v>
       </c>
@@ -24192,7 +24188,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="395" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
         <v>413</v>
       </c>
@@ -26242,7 +26238,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="436" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
         <v>1156</v>
       </c>
@@ -26592,7 +26588,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="443" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
         <v>126</v>
       </c>
@@ -26692,7 +26688,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="445" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
         <v>862</v>
       </c>
@@ -28192,7 +28188,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="475" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
         <v>225</v>
       </c>
@@ -28242,7 +28238,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="476" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
         <v>317</v>
       </c>
@@ -28292,7 +28288,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="477" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
         <v>317</v>
       </c>
@@ -28992,7 +28988,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="491" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
         <v>24</v>
       </c>
@@ -29392,7 +29388,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="499" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
         <v>449</v>
       </c>
@@ -29542,7 +29538,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="502" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
         <v>452</v>
       </c>
@@ -29642,7 +29638,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="504" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
         <v>501</v>
       </c>
@@ -30042,7 +30038,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="512" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
         <v>1026</v>
       </c>
@@ -30342,7 +30338,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="518" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
         <v>722</v>
       </c>
@@ -30392,7 +30388,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="519" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
         <v>728</v>
       </c>
@@ -30592,7 +30588,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="523" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
         <v>32</v>
       </c>
@@ -30642,7 +30638,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="524" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
         <v>508</v>
       </c>
@@ -30692,7 +30688,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="525" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
         <v>508</v>
       </c>
@@ -30742,7 +30738,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="526" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
         <v>1032</v>
       </c>
@@ -30942,7 +30938,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="530" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
         <v>366</v>
       </c>
@@ -31242,7 +31238,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="536" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
         <v>416</v>
       </c>
@@ -31342,7 +31338,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="538" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
         <v>576</v>
       </c>
@@ -31642,7 +31638,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="544" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
         <v>193</v>
       </c>
@@ -31692,7 +31688,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="545" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
         <v>193</v>
       </c>
@@ -32542,7 +32538,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="562" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
         <v>483</v>
       </c>
@@ -32692,7 +32688,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="565" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
         <v>701</v>
       </c>
@@ -34092,7 +34088,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="593" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="593" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A593" t="s">
         <v>1176</v>
       </c>
@@ -34742,7 +34738,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="606" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="606" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A606" t="s">
         <v>1191</v>
       </c>
@@ -34792,7 +34788,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="607" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="607" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A607" t="s">
         <v>1191</v>
       </c>
@@ -35142,7 +35138,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="614" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="614" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A614" t="s">
         <v>713</v>
       </c>
@@ -35546,7 +35542,7 @@
   <autoFilter ref="A1:P621" xr:uid="{6A7ECD2C-6F5B-4E4D-962E-4B55F2FEEDC6}">
     <filterColumn colId="9">
       <filters>
-        <filter val="TYPE_FIRE"/>
+        <filter val="TYPE_GRASS"/>
       </filters>
     </filterColumn>
     <filterColumn colId="15">

--- a/all_generations_pokemon_families.xlsx
+++ b/all_generations_pokemon_families.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Austin\Documents\PokemonDecompBuild\pokefirered-expansion\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\apetronack\Documents\Projects\pokefirered-expansion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73F2262A-E5B3-4185-A537-AAA20E3A2DD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45660C4E-9CAB-49D2-90D4-FC7E8D0F9FBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{913F818F-7E2F-42B8-8FB9-B28A63806581}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{913F818F-7E2F-42B8-8FB9-B28A63806581}"/>
   </bookViews>
   <sheets>
     <sheet name="all_generations_pokemon_familie" sheetId="1" r:id="rId1"/>
@@ -4988,7 +4988,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>573</v>
       </c>
@@ -6488,7 +6488,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>1090</v>
       </c>
@@ -6588,7 +6588,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>857</v>
       </c>
@@ -7688,7 +7688,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>220</v>
       </c>
@@ -8738,7 +8738,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>793</v>
       </c>
@@ -10638,7 +10638,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>717</v>
       </c>
@@ -11638,7 +11638,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="144" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>15</v>
       </c>
@@ -11688,7 +11688,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="145" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>496</v>
       </c>
@@ -11738,7 +11738,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="146" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>1021</v>
       </c>
@@ -12238,7 +12238,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="156" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>313</v>
       </c>
@@ -12288,7 +12288,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="157" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>313</v>
       </c>
@@ -14188,7 +14188,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="195" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>1153</v>
       </c>
@@ -14288,7 +14288,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="197" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>893</v>
       </c>
@@ -16738,7 +16738,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="246" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>223</v>
       </c>
@@ -17238,7 +17238,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="256" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>860</v>
       </c>
@@ -17388,7 +17388,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="259" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>30</v>
       </c>
@@ -17438,7 +17438,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="260" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>38</v>
       </c>
@@ -17488,7 +17488,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="261" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>213</v>
       </c>
@@ -17538,7 +17538,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="262" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>217</v>
       </c>
@@ -17588,7 +17588,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="263" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>217</v>
       </c>
@@ -17638,7 +17638,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="264" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>291</v>
       </c>
@@ -17688,7 +17688,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="265" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>291</v>
       </c>
@@ -17788,7 +17788,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="267" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>505</v>
       </c>
@@ -17838,7 +17838,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="268" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>505</v>
       </c>
@@ -17888,7 +17888,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="269" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>512</v>
       </c>
@@ -17938,7 +17938,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="270" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>588</v>
       </c>
@@ -18038,7 +18038,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="272" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>726</v>
       </c>
@@ -18188,7 +18188,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="275" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>732</v>
       </c>
@@ -18288,7 +18288,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="277" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>1030</v>
       </c>
@@ -18338,7 +18338,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="278" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>1036</v>
       </c>
@@ -18388,7 +18388,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="279" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>708</v>
       </c>
@@ -18438,7 +18438,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="280" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>971</v>
       </c>
@@ -18488,7 +18488,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="281" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>1048</v>
       </c>
@@ -18538,7 +18538,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="282" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>1128</v>
       </c>
@@ -18588,7 +18588,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="283" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
         <v>679</v>
       </c>
@@ -18638,7 +18638,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="284" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
         <v>489</v>
       </c>
@@ -18688,7 +18688,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="285" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>995</v>
       </c>
@@ -18738,7 +18738,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="286" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>518</v>
       </c>
@@ -18788,7 +18788,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="287" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
         <v>538</v>
       </c>
@@ -18838,7 +18838,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="288" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>833</v>
       </c>
@@ -18888,7 +18888,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="289" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>618</v>
       </c>
@@ -19288,7 +19288,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="297" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>618</v>
       </c>
@@ -19338,7 +19338,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="298" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>637</v>
       </c>
@@ -19488,7 +19488,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="301" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
         <v>637</v>
       </c>
@@ -19538,7 +19538,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="302" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
         <v>637</v>
       </c>
@@ -19588,7 +19588,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="303" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
         <v>637</v>
       </c>
@@ -19638,7 +19638,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="304" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
         <v>838</v>
       </c>
@@ -19738,7 +19738,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="306" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
         <v>432</v>
       </c>
@@ -19788,7 +19788,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="307" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
         <v>593</v>
       </c>
@@ -19838,7 +19838,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="308" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
         <v>372</v>
       </c>
@@ -19988,7 +19988,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="311" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
         <v>801</v>
       </c>
@@ -20038,7 +20038,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="312" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
         <v>95</v>
       </c>
@@ -20088,7 +20088,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="313" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
         <v>95</v>
       </c>
@@ -20138,7 +20138,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="314" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
         <v>159</v>
       </c>
@@ -20388,7 +20388,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="319" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
         <v>530</v>
       </c>
@@ -20438,7 +20438,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="320" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
         <v>660</v>
       </c>
@@ -20838,7 +20838,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="328" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
         <v>139</v>
       </c>
@@ -20888,7 +20888,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="329" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
         <v>183</v>
       </c>
@@ -20938,7 +20938,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="330" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
         <v>811</v>
       </c>
@@ -20988,7 +20988,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="331" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
         <v>389</v>
       </c>
@@ -21038,7 +21038,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="332" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
         <v>389</v>
       </c>
@@ -21088,7 +21088,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="333" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
         <v>742</v>
       </c>
@@ -21138,7 +21138,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="334" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
         <v>742</v>
       </c>
@@ -21438,7 +21438,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="340" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
         <v>844</v>
       </c>
@@ -21488,7 +21488,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="341" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
         <v>905</v>
       </c>
@@ -21538,7 +21538,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="342" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
         <v>907</v>
       </c>
@@ -21638,7 +21638,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="344" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
         <v>155</v>
       </c>
@@ -21988,7 +21988,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="351" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
         <v>324</v>
       </c>
@@ -22038,7 +22038,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="352" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
         <v>324</v>
       </c>
@@ -22088,7 +22088,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="353" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
         <v>273</v>
       </c>
@@ -22138,7 +22138,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="354" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
         <v>738</v>
       </c>
@@ -22188,7 +22188,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="355" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
         <v>884</v>
       </c>
@@ -22238,7 +22238,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="356" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
         <v>584</v>
       </c>
@@ -22288,7 +22288,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="357" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
         <v>587</v>
       </c>
@@ -22488,7 +22488,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="361" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
         <v>601</v>
       </c>
@@ -22538,7 +22538,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="362" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
         <v>774</v>
       </c>
@@ -22588,7 +22588,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="363" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
         <v>848</v>
       </c>
@@ -22638,7 +22638,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="364" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
         <v>879</v>
       </c>
@@ -22688,7 +22688,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="365" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
         <v>945</v>
       </c>
@@ -22738,7 +22738,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="366" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
         <v>949</v>
       </c>
@@ -22788,7 +22788,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="367" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
         <v>61</v>
       </c>
@@ -22838,7 +22838,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="368" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
         <v>1116</v>
       </c>
@@ -22888,7 +22888,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="369" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
         <v>259</v>
       </c>
@@ -22938,7 +22938,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="370" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
         <v>259</v>
       </c>
@@ -22988,7 +22988,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="371" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
         <v>534</v>
       </c>
@@ -23038,7 +23038,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="372" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
         <v>680</v>
       </c>
@@ -23088,7 +23088,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="373" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
         <v>916</v>
       </c>
@@ -23138,7 +23138,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="374" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
         <v>1108</v>
       </c>
@@ -23188,7 +23188,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="375" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
         <v>1185</v>
       </c>
@@ -23238,7 +23238,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="376" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
         <v>822</v>
       </c>
@@ -23288,7 +23288,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="377" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
         <v>350</v>
       </c>
@@ -23338,7 +23338,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="378" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
         <v>878</v>
       </c>
@@ -23438,7 +23438,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="380" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
         <v>1044</v>
       </c>
@@ -23488,7 +23488,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="381" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
         <v>1123</v>
       </c>
@@ -23538,7 +23538,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="382" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
         <v>346</v>
       </c>
@@ -23588,7 +23588,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="383" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
         <v>367</v>
       </c>
@@ -23638,7 +23638,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="384" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
         <v>406</v>
       </c>
@@ -23688,7 +23688,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="385" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
         <v>557</v>
       </c>
@@ -23738,7 +23738,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="386" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
         <v>697</v>
       </c>
@@ -24138,7 +24138,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="394" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
         <v>302</v>
       </c>
@@ -24188,7 +24188,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="395" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
         <v>413</v>
       </c>
@@ -24388,7 +24388,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="399" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
         <v>466</v>
       </c>
@@ -24438,7 +24438,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="400" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
         <v>470</v>
       </c>
@@ -24488,7 +24488,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="401" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
         <v>596</v>
       </c>
@@ -24538,7 +24538,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="402" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
         <v>866</v>
       </c>
@@ -24588,7 +24588,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="403" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
         <v>924</v>
       </c>
@@ -24638,7 +24638,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="404" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
         <v>928</v>
       </c>
@@ -24688,7 +24688,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="405" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
         <v>1062</v>
       </c>
@@ -24738,7 +24738,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="406" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
         <v>1066</v>
       </c>
@@ -24788,7 +24788,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="407" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
         <v>1089</v>
       </c>
@@ -24938,7 +24938,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="410" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
         <v>1104</v>
       </c>
@@ -24988,7 +24988,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="411" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
         <v>89</v>
       </c>
@@ -25038,7 +25038,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="412" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
         <v>89</v>
       </c>
@@ -25088,7 +25088,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="413" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
         <v>178</v>
       </c>
@@ -25138,7 +25138,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="414" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
         <v>293</v>
       </c>
@@ -25188,7 +25188,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="415" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
         <v>392</v>
       </c>
@@ -25238,7 +25238,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="416" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
         <v>392</v>
       </c>
@@ -25288,7 +25288,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="417" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
         <v>397</v>
       </c>
@@ -25338,7 +25338,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="418" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
         <v>398</v>
       </c>
@@ -25388,7 +25388,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="419" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
         <v>545</v>
       </c>
@@ -25438,7 +25438,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="420" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
         <v>609</v>
       </c>
@@ -25488,7 +25488,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="421" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
         <v>635</v>
       </c>
@@ -25538,7 +25538,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="422" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
         <v>685</v>
       </c>
@@ -25588,7 +25588,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="423" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
         <v>689</v>
       </c>
@@ -25938,7 +25938,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="430" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
         <v>764</v>
       </c>
@@ -25988,7 +25988,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="431" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
         <v>874</v>
       </c>
@@ -26038,7 +26038,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="432" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
         <v>920</v>
       </c>
@@ -26088,7 +26088,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="433" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
         <v>1120</v>
       </c>
@@ -26138,7 +26138,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="434" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
         <v>1142</v>
       </c>
@@ -26188,7 +26188,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="435" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
         <v>1146</v>
       </c>
@@ -26288,7 +26288,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="437" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
         <v>107</v>
       </c>
@@ -26538,7 +26538,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="442" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
         <v>113</v>
       </c>
@@ -26588,7 +26588,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="443" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
         <v>126</v>
       </c>
@@ -26638,7 +26638,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="444" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
         <v>633</v>
       </c>
@@ -26738,7 +26738,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="446" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
         <v>205</v>
       </c>
@@ -26888,7 +26888,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="449" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
         <v>206</v>
       </c>
@@ -26938,7 +26938,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="450" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
         <v>235</v>
       </c>
@@ -26988,7 +26988,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="451" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
         <v>235</v>
       </c>
@@ -27038,7 +27038,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="452" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
         <v>249</v>
       </c>
@@ -27088,7 +27088,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="453" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
         <v>250</v>
       </c>
@@ -27138,7 +27138,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="454" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
         <v>249</v>
       </c>
@@ -27188,7 +27188,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="455" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
         <v>250</v>
       </c>
@@ -27288,7 +27288,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="457" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
         <v>298</v>
       </c>
@@ -27338,7 +27338,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="458" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
         <v>641</v>
       </c>
@@ -27388,7 +27388,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="459" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
         <v>644</v>
       </c>
@@ -27438,7 +27438,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="460" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
         <v>900</v>
       </c>
@@ -27488,7 +27488,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="461" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
         <v>966</v>
       </c>
@@ -27538,7 +27538,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="462" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
         <v>967</v>
       </c>
@@ -27588,7 +27588,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="463" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
         <v>980</v>
       </c>
@@ -27738,7 +27738,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="466" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
         <v>981</v>
       </c>
@@ -27788,7 +27788,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="467" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
         <v>229</v>
       </c>
@@ -27938,7 +27938,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="470" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
         <v>459</v>
       </c>
@@ -27988,7 +27988,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="471" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
         <v>471</v>
       </c>
@@ -28038,7 +28038,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="472" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
         <v>592</v>
       </c>
@@ -28088,7 +28088,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="473" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
         <v>787</v>
       </c>
@@ -28138,7 +28138,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="474" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
         <v>788</v>
       </c>
@@ -28338,7 +28338,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="478" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
         <v>383</v>
       </c>
@@ -28388,7 +28388,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="479" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
         <v>391</v>
       </c>
@@ -28438,7 +28438,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="480" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
         <v>551</v>
       </c>
@@ -28738,7 +28738,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="486" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
         <v>605</v>
       </c>
@@ -28788,7 +28788,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="487" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
         <v>746</v>
       </c>
@@ -28838,7 +28838,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="488" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
         <v>818</v>
       </c>
@@ -28888,7 +28888,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="489" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
         <v>892</v>
       </c>
@@ -28938,7 +28938,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="490" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
         <v>1058</v>
       </c>
@@ -29188,7 +29188,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="495" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
         <v>219</v>
       </c>
@@ -29238,7 +29238,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="496" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
         <v>287</v>
       </c>
@@ -29288,7 +29288,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="497" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
         <v>447</v>
       </c>
@@ -29338,7 +29338,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="498" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
         <v>448</v>
       </c>
@@ -29388,7 +29388,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="499" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
         <v>449</v>
       </c>
@@ -29438,7 +29438,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="500" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
         <v>450</v>
       </c>
@@ -29488,7 +29488,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="501" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
         <v>451</v>
       </c>
@@ -29588,7 +29588,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="503" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
         <v>453</v>
       </c>
@@ -29688,7 +29688,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="505" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
         <v>622</v>
       </c>
@@ -29988,7 +29988,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="511" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
         <v>952</v>
       </c>
@@ -30088,7 +30088,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="513" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
         <v>1134</v>
       </c>
@@ -30138,7 +30138,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="514" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
         <v>1138</v>
       </c>
@@ -30188,7 +30188,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="515" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
         <v>40</v>
       </c>
@@ -30238,7 +30238,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="516" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
         <v>514</v>
       </c>
@@ -30288,7 +30288,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="517" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
         <v>662</v>
       </c>
@@ -30388,7 +30388,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="519" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
         <v>728</v>
       </c>
@@ -30438,7 +30438,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="520" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
         <v>840</v>
       </c>
@@ -30488,7 +30488,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="521" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
         <v>973</v>
       </c>
@@ -30538,7 +30538,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="522" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
         <v>1038</v>
       </c>
@@ -30588,7 +30588,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="523" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
         <v>32</v>
       </c>
@@ -30638,7 +30638,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="524" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
         <v>508</v>
       </c>
@@ -30688,7 +30688,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="525" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
         <v>508</v>
       </c>
@@ -30738,7 +30738,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="526" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
         <v>1032</v>
       </c>
@@ -30788,7 +30788,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="527" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
         <v>141</v>
       </c>
@@ -30838,7 +30838,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="528" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
         <v>187</v>
       </c>
@@ -30888,7 +30888,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="529" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
         <v>353</v>
       </c>
@@ -30988,7 +30988,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="531" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A531" t="s">
         <v>428</v>
       </c>
@@ -31038,7 +31038,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="532" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
         <v>462</v>
       </c>
@@ -31088,7 +31088,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="533" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
         <v>734</v>
       </c>
@@ -31138,7 +31138,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="534" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
         <v>375</v>
       </c>
@@ -31188,7 +31188,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="535" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
         <v>409</v>
       </c>
@@ -31238,7 +31238,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="536" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
         <v>416</v>
       </c>
@@ -31288,7 +31288,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="537" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
         <v>476</v>
       </c>
@@ -31388,7 +31388,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="539" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
         <v>934</v>
       </c>
@@ -31438,7 +31438,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="540" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
         <v>263</v>
       </c>
@@ -31588,7 +31588,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="543" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
         <v>541</v>
       </c>
@@ -31638,7 +31638,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="544" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
         <v>193</v>
       </c>
@@ -31688,7 +31688,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="545" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
         <v>193</v>
       </c>
@@ -31738,7 +31738,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="546" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
         <v>477</v>
       </c>
@@ -31788,7 +31788,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="547" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
         <v>477</v>
       </c>
@@ -31838,7 +31838,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="548" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
         <v>480</v>
       </c>
@@ -31888,7 +31888,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="549" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
         <v>480</v>
       </c>
@@ -32538,7 +32538,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="562" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
         <v>483</v>
       </c>
@@ -32588,7 +32588,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="563" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
         <v>483</v>
       </c>
@@ -32638,7 +32638,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="564" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
         <v>699</v>
       </c>
@@ -32688,7 +32688,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="565" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
         <v>701</v>
       </c>
@@ -32738,7 +32738,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="566" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
         <v>703</v>
       </c>
@@ -32988,7 +32988,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="571" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
         <v>998</v>
       </c>
@@ -33038,7 +33038,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="572" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
         <v>1000</v>
       </c>
@@ -33088,7 +33088,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="573" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A573" t="s">
         <v>1002</v>
       </c>
@@ -33138,7 +33138,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="574" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A574" t="s">
         <v>1164</v>
       </c>
@@ -33288,7 +33288,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="577" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A577" t="s">
         <v>1166</v>
       </c>
@@ -33338,7 +33338,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="578" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A578" t="s">
         <v>1168</v>
       </c>
@@ -33388,7 +33388,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="579" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A579" t="s">
         <v>491</v>
       </c>
@@ -33438,7 +33438,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="580" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A580" t="s">
         <v>494</v>
       </c>
@@ -33538,7 +33538,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="582" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A582" t="s">
         <v>710</v>
       </c>
@@ -33588,7 +33588,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="583" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A583" t="s">
         <v>715</v>
       </c>
@@ -33638,7 +33638,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="584" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A584" t="s">
         <v>997</v>
       </c>
@@ -33688,7 +33688,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="585" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A585" t="s">
         <v>1004</v>
       </c>
@@ -33738,7 +33738,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="586" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A586" t="s">
         <v>1006</v>
       </c>
@@ -33788,7 +33788,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="587" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A587" t="s">
         <v>1014</v>
       </c>
@@ -33838,7 +33838,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="588" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A588" t="s">
         <v>1016</v>
       </c>
@@ -33888,7 +33888,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="589" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A589" t="s">
         <v>1016</v>
       </c>
@@ -33938,7 +33938,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="590" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="590" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A590" t="s">
         <v>1016</v>
       </c>
@@ -33988,7 +33988,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="591" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="591" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A591" t="s">
         <v>1016</v>
       </c>
@@ -34038,7 +34038,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="592" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A592" t="s">
         <v>1130</v>
       </c>
@@ -34088,7 +34088,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="593" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="593" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A593" t="s">
         <v>1176</v>
       </c>
@@ -34288,7 +34288,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="597" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="597" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A597" t="s">
         <v>1183</v>
       </c>
@@ -34338,7 +34338,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="598" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="598" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A598" t="s">
         <v>1187</v>
       </c>
@@ -34688,7 +34688,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="605" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="605" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A605" t="s">
         <v>1189</v>
       </c>
@@ -34838,7 +34838,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="608" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="608" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A608" t="s">
         <v>803</v>
       </c>
@@ -34888,7 +34888,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="609" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="609" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A609" t="s">
         <v>1008</v>
       </c>
@@ -34938,7 +34938,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="610" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="610" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A610" t="s">
         <v>1010</v>
       </c>
@@ -34988,7 +34988,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="611" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="611" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A611" t="s">
         <v>1178</v>
       </c>
@@ -35038,7 +35038,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="612" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="612" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A612" t="s">
         <v>492</v>
       </c>
@@ -35088,7 +35088,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="613" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="613" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A613" t="s">
         <v>711</v>
       </c>
@@ -35138,7 +35138,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="614" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="614" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A614" t="s">
         <v>713</v>
       </c>
@@ -35188,7 +35188,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="615" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="615" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A615" t="s">
         <v>1012</v>
       </c>
@@ -35238,7 +35238,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="616" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="616" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A616" t="s">
         <v>1170</v>
       </c>
@@ -35288,7 +35288,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="617" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="617" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A617" t="s">
         <v>1170</v>
       </c>
@@ -35338,7 +35338,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="618" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="618" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A618" t="s">
         <v>1173</v>
       </c>
@@ -35388,7 +35388,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="619" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="619" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A619" t="s">
         <v>1173</v>
       </c>
@@ -35438,7 +35438,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="620" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="620" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A620" t="s">
         <v>1180</v>
       </c>
@@ -35488,7 +35488,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="621" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="621" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A621" t="s">
         <v>1180</v>
       </c>
@@ -35540,10 +35540,10 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:P621" xr:uid="{6A7ECD2C-6F5B-4E4D-962E-4B55F2FEEDC6}">
-    <filterColumn colId="9">
-      <filters>
-        <filter val="TYPE_GRASS"/>
-      </filters>
+    <filterColumn colId="8">
+      <customFilters>
+        <customFilter operator="greaterThan" val="400"/>
+      </customFilters>
     </filterColumn>
     <filterColumn colId="15">
       <filters>

--- a/all_generations_pokemon_families.xlsx
+++ b/all_generations_pokemon_families.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\apetronack\Documents\Projects\pokefirered-expansion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45660C4E-9CAB-49D2-90D4-FC7E8D0F9FBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EBE7E01-8550-484B-BFAD-D853392BDD24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{913F818F-7E2F-42B8-8FB9-B28A63806581}"/>
   </bookViews>

--- a/all_generations_pokemon_families.xlsx
+++ b/all_generations_pokemon_families.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\apetronack\Documents\Projects\pokefirered-expansion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EBE7E01-8550-484B-BFAD-D853392BDD24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{640D09F9-2BEB-4A1E-ABBB-ACCC28723074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{913F818F-7E2F-42B8-8FB9-B28A63806581}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{913F818F-7E2F-42B8-8FB9-B28A63806581}"/>
   </bookViews>
   <sheets>
     <sheet name="all_generations_pokemon_familie" sheetId="1" r:id="rId1"/>
@@ -17338,7 +17338,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="258" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>22</v>
       </c>
@@ -17388,7 +17388,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="259" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>30</v>
       </c>
@@ -17488,7 +17488,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="261" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>213</v>
       </c>
@@ -17538,7 +17538,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="262" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>217</v>
       </c>
@@ -17588,7 +17588,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="263" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>217</v>
       </c>
@@ -17638,7 +17638,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="264" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>291</v>
       </c>
@@ -17688,7 +17688,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="265" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>291</v>
       </c>
@@ -17738,7 +17738,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="266" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>499</v>
       </c>
@@ -17788,7 +17788,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="267" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>505</v>
       </c>
@@ -17838,7 +17838,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="268" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>505</v>
       </c>
@@ -17938,7 +17938,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="270" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>588</v>
       </c>
@@ -17988,7 +17988,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="271" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>720</v>
       </c>
@@ -18038,7 +18038,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="272" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>726</v>
       </c>
@@ -18238,7 +18238,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="276" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>1024</v>
       </c>
@@ -18288,7 +18288,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="277" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>1030</v>
       </c>
@@ -18388,7 +18388,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="279" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>708</v>
       </c>
@@ -18438,7 +18438,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="280" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>971</v>
       </c>
@@ -18488,7 +18488,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="281" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>1048</v>
       </c>
@@ -18538,7 +18538,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="282" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>1128</v>
       </c>
@@ -18638,7 +18638,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="284" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
         <v>489</v>
       </c>
@@ -18688,7 +18688,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="285" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>995</v>
       </c>
@@ -18738,7 +18738,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="286" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>518</v>
       </c>
@@ -18788,7 +18788,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="287" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
         <v>538</v>
       </c>
@@ -18838,7 +18838,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="288" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>833</v>
       </c>
@@ -18888,7 +18888,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="289" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>618</v>
       </c>
@@ -19288,7 +19288,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="297" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>618</v>
       </c>
@@ -19338,7 +19338,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="298" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>637</v>
       </c>
@@ -19488,7 +19488,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="301" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
         <v>637</v>
       </c>
@@ -19538,7 +19538,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="302" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
         <v>637</v>
       </c>
@@ -19588,7 +19588,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="303" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
         <v>637</v>
       </c>
@@ -19638,7 +19638,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="304" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
         <v>838</v>
       </c>
@@ -19688,7 +19688,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="305" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
         <v>362</v>
       </c>
@@ -19738,7 +19738,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="306" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
         <v>432</v>
       </c>
@@ -19788,7 +19788,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="307" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
         <v>593</v>
       </c>
@@ -19988,7 +19988,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="311" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
         <v>801</v>
       </c>
@@ -20038,7 +20038,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="312" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
         <v>95</v>
       </c>
@@ -20088,7 +20088,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="313" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
         <v>95</v>
       </c>
@@ -20138,7 +20138,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="314" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
         <v>159</v>
       </c>
@@ -20388,7 +20388,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="319" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
         <v>530</v>
       </c>
@@ -20438,7 +20438,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="320" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
         <v>660</v>
       </c>
@@ -20488,7 +20488,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="321" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
         <v>1093</v>
       </c>
@@ -20788,7 +20788,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="327" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
         <v>1093</v>
       </c>
@@ -20838,7 +20838,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="328" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
         <v>139</v>
       </c>
@@ -20888,7 +20888,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="329" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
         <v>183</v>
       </c>
@@ -20938,7 +20938,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="330" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
         <v>811</v>
       </c>
@@ -20988,7 +20988,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="331" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
         <v>389</v>
       </c>
@@ -21038,7 +21038,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="332" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
         <v>389</v>
       </c>
@@ -21088,7 +21088,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="333" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
         <v>742</v>
       </c>
@@ -21138,7 +21138,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="334" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
         <v>742</v>
       </c>
@@ -21438,7 +21438,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="340" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
         <v>844</v>
       </c>
@@ -21488,7 +21488,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="341" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
         <v>905</v>
       </c>
@@ -21538,7 +21538,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="342" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
         <v>907</v>
       </c>
@@ -21588,7 +21588,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="343" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
         <v>953</v>
       </c>
@@ -21638,7 +21638,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="344" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
         <v>155</v>
       </c>
@@ -21988,7 +21988,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="351" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
         <v>324</v>
       </c>
@@ -22038,7 +22038,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="352" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
         <v>324</v>
       </c>
@@ -22088,7 +22088,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="353" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
         <v>273</v>
       </c>
@@ -22138,7 +22138,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="354" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
         <v>738</v>
       </c>
@@ -22188,7 +22188,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="355" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
         <v>884</v>
       </c>
@@ -22288,7 +22288,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="357" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
         <v>587</v>
       </c>
@@ -22488,7 +22488,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="361" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
         <v>601</v>
       </c>
@@ -22538,7 +22538,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="362" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
         <v>774</v>
       </c>
@@ -22588,7 +22588,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="363" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
         <v>848</v>
       </c>
@@ -22638,7 +22638,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="364" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
         <v>879</v>
       </c>
@@ -22688,7 +22688,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="365" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
         <v>945</v>
       </c>
@@ -22738,7 +22738,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="366" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
         <v>949</v>
       </c>
@@ -22788,7 +22788,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="367" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
         <v>61</v>
       </c>
@@ -22838,7 +22838,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="368" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
         <v>1116</v>
       </c>
@@ -22888,7 +22888,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="369" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
         <v>259</v>
       </c>
@@ -22938,7 +22938,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="370" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
         <v>259</v>
       </c>
@@ -23038,7 +23038,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="372" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
         <v>680</v>
       </c>
@@ -23138,7 +23138,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="374" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
         <v>1108</v>
       </c>
@@ -23238,7 +23238,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="376" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
         <v>822</v>
       </c>
@@ -23288,7 +23288,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="377" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
         <v>350</v>
       </c>
@@ -23338,7 +23338,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="378" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
         <v>878</v>
       </c>
@@ -23388,7 +23388,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="379" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
         <v>896</v>
       </c>
@@ -23438,7 +23438,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="380" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
         <v>1044</v>
       </c>
@@ -23488,7 +23488,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="381" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
         <v>1123</v>
       </c>
@@ -23538,7 +23538,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="382" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
         <v>346</v>
       </c>
@@ -23588,7 +23588,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="383" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
         <v>367</v>
       </c>
@@ -23638,7 +23638,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="384" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
         <v>406</v>
       </c>
@@ -23738,7 +23738,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="386" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
         <v>697</v>
       </c>
@@ -24088,7 +24088,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="393" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
         <v>797</v>
       </c>
@@ -24138,7 +24138,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="394" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
         <v>302</v>
       </c>
@@ -24188,7 +24188,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="395" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
         <v>413</v>
       </c>
@@ -24388,7 +24388,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="399" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
         <v>466</v>
       </c>
@@ -24438,7 +24438,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="400" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
         <v>470</v>
       </c>
@@ -24488,7 +24488,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="401" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
         <v>596</v>
       </c>
@@ -24538,7 +24538,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="402" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
         <v>866</v>
       </c>
@@ -24588,7 +24588,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="403" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
         <v>924</v>
       </c>
@@ -24638,7 +24638,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="404" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
         <v>928</v>
       </c>
@@ -24688,7 +24688,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="405" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
         <v>1062</v>
       </c>
@@ -24738,7 +24738,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="406" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
         <v>1066</v>
       </c>
@@ -24938,7 +24938,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="410" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
         <v>1104</v>
       </c>
@@ -24988,7 +24988,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="411" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
         <v>89</v>
       </c>
@@ -25038,7 +25038,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="412" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
         <v>89</v>
       </c>
@@ -25138,7 +25138,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="414" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
         <v>293</v>
       </c>
@@ -25188,7 +25188,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="415" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
         <v>392</v>
       </c>
@@ -25238,7 +25238,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="416" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
         <v>392</v>
       </c>
@@ -25288,7 +25288,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="417" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
         <v>397</v>
       </c>
@@ -25338,7 +25338,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="418" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
         <v>398</v>
       </c>
@@ -25388,7 +25388,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="419" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
         <v>545</v>
       </c>
@@ -25438,7 +25438,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="420" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
         <v>609</v>
       </c>
@@ -25488,7 +25488,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="421" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
         <v>635</v>
       </c>
@@ -25538,7 +25538,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="422" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
         <v>685</v>
       </c>
@@ -25588,7 +25588,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="423" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
         <v>689</v>
       </c>
@@ -26038,7 +26038,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="432" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
         <v>920</v>
       </c>
@@ -26088,7 +26088,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="433" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
         <v>1120</v>
       </c>
@@ -26138,7 +26138,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="434" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
         <v>1142</v>
       </c>
@@ -26188,7 +26188,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="435" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
         <v>1146</v>
       </c>
@@ -26238,7 +26238,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="436" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
         <v>1156</v>
       </c>
@@ -26288,7 +26288,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="437" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
         <v>107</v>
       </c>
@@ -26538,7 +26538,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="442" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
         <v>113</v>
       </c>
@@ -26588,7 +26588,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="443" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
         <v>126</v>
       </c>
@@ -26638,7 +26638,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="444" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
         <v>633</v>
       </c>
@@ -26688,7 +26688,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="445" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
         <v>862</v>
       </c>
@@ -26938,7 +26938,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="450" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
         <v>235</v>
       </c>
@@ -26988,7 +26988,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="451" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
         <v>235</v>
       </c>
@@ -27138,7 +27138,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="454" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
         <v>249</v>
       </c>
@@ -27188,7 +27188,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="455" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
         <v>250</v>
       </c>
@@ -27288,7 +27288,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="457" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
         <v>298</v>
       </c>
@@ -27338,7 +27338,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="458" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
         <v>641</v>
       </c>
@@ -27388,7 +27388,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="459" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
         <v>644</v>
       </c>
@@ -27438,7 +27438,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="460" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
         <v>900</v>
       </c>
@@ -27488,7 +27488,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="461" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
         <v>966</v>
       </c>
@@ -27538,7 +27538,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="462" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
         <v>967</v>
       </c>
@@ -27938,7 +27938,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="470" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
         <v>459</v>
       </c>
@@ -27988,7 +27988,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="471" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
         <v>471</v>
       </c>
@@ -28038,7 +28038,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="472" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
         <v>592</v>
       </c>
@@ -28088,7 +28088,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="473" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
         <v>787</v>
       </c>
@@ -28138,7 +28138,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="474" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
         <v>788</v>
       </c>
@@ -28188,7 +28188,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="475" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
         <v>225</v>
       </c>
@@ -28238,7 +28238,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="476" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
         <v>317</v>
       </c>
@@ -28288,7 +28288,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="477" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
         <v>317</v>
       </c>
@@ -28388,7 +28388,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="479" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
         <v>391</v>
       </c>
@@ -28438,7 +28438,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="480" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
         <v>551</v>
       </c>
@@ -28738,7 +28738,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="486" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
         <v>605</v>
       </c>
@@ -28788,7 +28788,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="487" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
         <v>746</v>
       </c>
@@ -28838,7 +28838,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="488" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
         <v>818</v>
       </c>
@@ -28888,7 +28888,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="489" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
         <v>892</v>
       </c>
@@ -28938,7 +28938,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="490" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
         <v>1058</v>
       </c>
@@ -28988,7 +28988,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="491" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
         <v>24</v>
       </c>
@@ -29188,7 +29188,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="495" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
         <v>219</v>
       </c>
@@ -29338,7 +29338,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="498" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
         <v>448</v>
       </c>
@@ -29388,7 +29388,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="499" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
         <v>449</v>
       </c>
@@ -29438,7 +29438,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="500" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
         <v>450</v>
       </c>
@@ -29488,7 +29488,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="501" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
         <v>451</v>
       </c>
@@ -29538,7 +29538,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="502" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
         <v>452</v>
       </c>
@@ -29588,7 +29588,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="503" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
         <v>453</v>
       </c>
@@ -29638,7 +29638,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="504" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
         <v>501</v>
       </c>
@@ -29688,7 +29688,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="505" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
         <v>622</v>
       </c>
@@ -29988,7 +29988,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="511" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
         <v>952</v>
       </c>
@@ -30038,7 +30038,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="512" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
         <v>1026</v>
       </c>
@@ -30088,7 +30088,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="513" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
         <v>1134</v>
       </c>
@@ -30138,7 +30138,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="514" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
         <v>1138</v>
       </c>
@@ -30288,7 +30288,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="517" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
         <v>662</v>
       </c>
@@ -30338,7 +30338,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="518" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
         <v>722</v>
       </c>
@@ -30388,7 +30388,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="519" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
         <v>728</v>
       </c>
@@ -30438,7 +30438,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="520" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
         <v>840</v>
       </c>
@@ -30488,7 +30488,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="521" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
         <v>973</v>
       </c>
@@ -30588,7 +30588,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="523" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
         <v>32</v>
       </c>
@@ -30638,7 +30638,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="524" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
         <v>508</v>
       </c>
@@ -30688,7 +30688,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="525" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
         <v>508</v>
       </c>
@@ -30738,7 +30738,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="526" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
         <v>1032</v>
       </c>
@@ -30788,7 +30788,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="527" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
         <v>141</v>
       </c>
@@ -30838,7 +30838,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="528" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
         <v>187</v>
       </c>
@@ -30888,7 +30888,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="529" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
         <v>353</v>
       </c>
@@ -30938,7 +30938,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="530" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
         <v>366</v>
       </c>
@@ -31038,7 +31038,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="532" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
         <v>462</v>
       </c>
@@ -31188,7 +31188,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="535" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
         <v>409</v>
       </c>
@@ -31238,7 +31238,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="536" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
         <v>416</v>
       </c>
@@ -31288,7 +31288,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="537" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
         <v>476</v>
       </c>
@@ -31338,7 +31338,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="538" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
         <v>576</v>
       </c>
@@ -31438,7 +31438,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="540" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
         <v>263</v>
       </c>
@@ -31588,7 +31588,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="543" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
         <v>541</v>
       </c>
@@ -31638,7 +31638,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="544" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
         <v>193</v>
       </c>
@@ -31688,7 +31688,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="545" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
         <v>193</v>
       </c>
@@ -31738,7 +31738,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="546" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
         <v>477</v>
       </c>
@@ -31788,7 +31788,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="547" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
         <v>477</v>
       </c>
@@ -31838,7 +31838,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="548" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
         <v>480</v>
       </c>
@@ -31888,7 +31888,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="549" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
         <v>480</v>
       </c>
@@ -32538,7 +32538,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="562" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
         <v>483</v>
       </c>
@@ -32588,7 +32588,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="563" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
         <v>483</v>
       </c>
@@ -32638,7 +32638,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="564" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
         <v>699</v>
       </c>
@@ -32688,7 +32688,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="565" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
         <v>701</v>
       </c>
@@ -32988,7 +32988,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="571" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
         <v>998</v>
       </c>
@@ -33038,7 +33038,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="572" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
         <v>1000</v>
       </c>
@@ -33088,7 +33088,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="573" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A573" t="s">
         <v>1002</v>
       </c>
@@ -33138,7 +33138,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="574" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A574" t="s">
         <v>1164</v>
       </c>
@@ -33288,7 +33288,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="577" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A577" t="s">
         <v>1166</v>
       </c>
@@ -33338,7 +33338,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="578" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A578" t="s">
         <v>1168</v>
       </c>
@@ -33388,7 +33388,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="579" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A579" t="s">
         <v>491</v>
       </c>
@@ -33438,7 +33438,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="580" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A580" t="s">
         <v>494</v>
       </c>
@@ -33538,7 +33538,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="582" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A582" t="s">
         <v>710</v>
       </c>
@@ -33588,7 +33588,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="583" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A583" t="s">
         <v>715</v>
       </c>
@@ -33638,7 +33638,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="584" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A584" t="s">
         <v>997</v>
       </c>
@@ -33688,7 +33688,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="585" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A585" t="s">
         <v>1004</v>
       </c>
@@ -33738,7 +33738,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="586" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A586" t="s">
         <v>1006</v>
       </c>
@@ -33788,7 +33788,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="587" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A587" t="s">
         <v>1014</v>
       </c>
@@ -33838,7 +33838,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="588" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A588" t="s">
         <v>1016</v>
       </c>
@@ -33888,7 +33888,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="589" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A589" t="s">
         <v>1016</v>
       </c>
@@ -33938,7 +33938,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="590" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="590" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A590" t="s">
         <v>1016</v>
       </c>
@@ -33988,7 +33988,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="591" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="591" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A591" t="s">
         <v>1016</v>
       </c>
@@ -34038,7 +34038,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="592" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A592" t="s">
         <v>1130</v>
       </c>
@@ -34088,7 +34088,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="593" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="593" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A593" t="s">
         <v>1176</v>
       </c>
@@ -34288,7 +34288,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="597" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="597" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A597" t="s">
         <v>1183</v>
       </c>
@@ -34688,7 +34688,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="605" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="605" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A605" t="s">
         <v>1189</v>
       </c>
@@ -34738,7 +34738,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="606" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="606" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A606" t="s">
         <v>1191</v>
       </c>
@@ -34788,7 +34788,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="607" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="607" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A607" t="s">
         <v>1191</v>
       </c>
@@ -34838,7 +34838,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="608" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="608" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A608" t="s">
         <v>803</v>
       </c>
@@ -34938,7 +34938,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="610" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="610" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A610" t="s">
         <v>1010</v>
       </c>
@@ -34988,7 +34988,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="611" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="611" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A611" t="s">
         <v>1178</v>
       </c>
@@ -35038,7 +35038,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="612" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="612" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A612" t="s">
         <v>492</v>
       </c>
@@ -35088,7 +35088,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="613" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="613" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A613" t="s">
         <v>711</v>
       </c>
@@ -35138,7 +35138,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="614" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="614" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A614" t="s">
         <v>713</v>
       </c>
@@ -35188,7 +35188,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="615" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="615" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A615" t="s">
         <v>1012</v>
       </c>
@@ -35238,7 +35238,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="616" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="616" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A616" t="s">
         <v>1170</v>
       </c>
@@ -35288,7 +35288,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="617" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="617" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A617" t="s">
         <v>1170</v>
       </c>
@@ -35438,7 +35438,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="620" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="620" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A620" t="s">
         <v>1180</v>
       </c>
@@ -35488,7 +35488,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="621" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="621" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A621" t="s">
         <v>1180</v>
       </c>
@@ -35544,6 +35544,11 @@
       <customFilters>
         <customFilter operator="greaterThan" val="400"/>
       </customFilters>
+    </filterColumn>
+    <filterColumn colId="9">
+      <filters>
+        <filter val="TYPE_WATER"/>
+      </filters>
     </filterColumn>
     <filterColumn colId="15">
       <filters>

--- a/all_generations_pokemon_families.xlsx
+++ b/all_generations_pokemon_families.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\apetronack\Documents\Projects\pokefirered-expansion\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Austin\Documents\PokemonDecompBuild\pokefirered-expansion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{640D09F9-2BEB-4A1E-ABBB-ACCC28723074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DC3E173-CD0D-4AE9-91D1-60A79C85DC6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{913F818F-7E2F-42B8-8FB9-B28A63806581}"/>
+    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{913F818F-7E2F-42B8-8FB9-B28A63806581}"/>
   </bookViews>
   <sheets>
     <sheet name="all_generations_pokemon_familie" sheetId="1" r:id="rId1"/>
@@ -4638,7 +4638,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="4" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>929</v>
       </c>
@@ -4688,7 +4688,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="5" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>929</v>
       </c>
@@ -6388,7 +6388,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>759</v>
       </c>
@@ -7638,7 +7638,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="64" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>197</v>
       </c>
@@ -8338,7 +8338,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="78" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>369</v>
       </c>
@@ -8488,7 +8488,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="81" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>581</v>
       </c>
@@ -8688,7 +8688,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="85" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>775</v>
       </c>
@@ -9838,7 +9838,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="108" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>284</v>
       </c>
@@ -10188,7 +10188,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="115" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>913</v>
       </c>
@@ -10738,7 +10738,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="126" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>729</v>
       </c>
@@ -10988,7 +10988,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="131" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>34</v>
       </c>
@@ -11338,7 +11338,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="138" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>509</v>
       </c>
@@ -11388,7 +11388,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="139" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>1033</v>
       </c>
@@ -11438,7 +11438,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="140" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>245</v>
       </c>
@@ -11488,7 +11488,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="141" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>245</v>
       </c>
@@ -11788,7 +11788,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="147" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>175</v>
       </c>
@@ -13688,7 +13688,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="185" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>531</v>
       </c>
@@ -14038,7 +14038,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="192" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>1086</v>
       </c>
@@ -14238,7 +14238,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="196" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>226</v>
       </c>
@@ -14638,7 +14638,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="204" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>380</v>
       </c>
@@ -14688,7 +14688,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="205" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>762</v>
       </c>
@@ -15238,7 +15238,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="216" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>555</v>
       </c>
@@ -15288,7 +15288,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="217" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>674</v>
       </c>
@@ -15338,7 +15338,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="218" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>974</v>
       </c>
@@ -15388,7 +15388,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="219" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>974</v>
       </c>
@@ -16388,7 +16388,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="239" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>778</v>
       </c>
@@ -16538,7 +16538,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="242" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>200</v>
       </c>
@@ -16588,7 +16588,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="243" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>200</v>
       </c>
@@ -17288,7 +17288,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="257" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>871</v>
       </c>
@@ -35540,11 +35540,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:P621" xr:uid="{6A7ECD2C-6F5B-4E4D-962E-4B55F2FEEDC6}">
-    <filterColumn colId="8">
-      <customFilters>
-        <customFilter operator="greaterThan" val="400"/>
-      </customFilters>
-    </filterColumn>
     <filterColumn colId="9">
       <filters>
         <filter val="TYPE_WATER"/>

--- a/all_generations_pokemon_families.xlsx
+++ b/all_generations_pokemon_families.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\apetronack\Documents\Projects\pokefirered-expansion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D960E841-7FA1-44BA-950B-9B05A023D678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{8F5A88A5-85B3-4260-B9DF-7B6D611872F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{CFD33D56-DCEE-4C8F-A281-92D9AA7B5F95}"/>
   </bookViews>
@@ -4301,7 +4301,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>41</v>
       </c>
@@ -4403,7 +4403,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>706</v>
       </c>
@@ -4439,7 +4439,7 @@
         <v>88</v>
       </c>
       <c r="L5" t="s">
-        <v>180</v>
+        <v>44</v>
       </c>
       <c r="M5" t="s">
         <v>708</v>
@@ -4454,7 +4454,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>847</v>
       </c>
@@ -4607,7 +4607,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>46</v>
       </c>
@@ -4811,7 +4811,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>522</v>
       </c>
@@ -4862,7 +4862,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>128</v>
       </c>
@@ -4913,7 +4913,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>473</v>
       </c>
@@ -5015,7 +5015,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>666</v>
       </c>
@@ -5066,7 +5066,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>670</v>
       </c>
@@ -5117,7 +5117,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>956</v>
       </c>
@@ -5168,7 +5168,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>962</v>
       </c>
@@ -5219,7 +5219,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>55</v>
       </c>
@@ -5576,7 +5576,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>592</v>
       </c>
@@ -5627,7 +5627,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>596</v>
       </c>
@@ -5663,7 +5663,7 @@
         <v>91</v>
       </c>
       <c r="L29" t="s">
-        <v>180</v>
+        <v>19</v>
       </c>
       <c r="M29" t="s">
         <v>598</v>
@@ -5729,7 +5729,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>698</v>
       </c>
@@ -5780,7 +5780,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>97</v>
       </c>
@@ -5831,7 +5831,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>104</v>
       </c>
@@ -5882,7 +5882,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>485</v>
       </c>
@@ -5933,7 +5933,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>686</v>
       </c>
@@ -5984,7 +5984,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>735</v>
       </c>
@@ -6086,7 +6086,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>996</v>
       </c>
@@ -6137,7 +6137,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>970</v>
       </c>
@@ -6341,7 +6341,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>709</v>
       </c>
@@ -6377,7 +6377,7 @@
         <v>88</v>
       </c>
       <c r="L43" t="s">
-        <v>180</v>
+        <v>44</v>
       </c>
       <c r="M43" t="s">
         <v>710</v>
@@ -6392,7 +6392,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>723</v>
       </c>
@@ -6494,7 +6494,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>169</v>
       </c>
@@ -6545,7 +6545,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>477</v>
       </c>
@@ -6596,7 +6596,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>552</v>
       </c>
@@ -6647,7 +6647,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>26</v>
       </c>
@@ -6698,7 +6698,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>79</v>
       </c>
@@ -6749,7 +6749,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>115</v>
       </c>
@@ -6800,7 +6800,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>208</v>
       </c>
@@ -6851,7 +6851,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>336</v>
       </c>
@@ -6902,7 +6902,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>93</v>
       </c>
@@ -7004,7 +7004,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>143</v>
       </c>
@@ -7106,7 +7106,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>186</v>
       </c>
@@ -7157,7 +7157,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>218</v>
       </c>
@@ -7208,7 +7208,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>218</v>
       </c>
@@ -7259,7 +7259,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>218</v>
       </c>
@@ -7310,7 +7310,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>218</v>
       </c>
@@ -7361,7 +7361,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>394</v>
       </c>
@@ -7412,7 +7412,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>444</v>
       </c>
@@ -7514,7 +7514,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>528</v>
       </c>
@@ -7565,7 +7565,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>528</v>
       </c>
@@ -7616,7 +7616,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>528</v>
       </c>
@@ -7667,7 +7667,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>528</v>
       </c>
@@ -7820,7 +7820,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>636</v>
       </c>
@@ -7871,7 +7871,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>670</v>
       </c>
@@ -7922,7 +7922,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>702</v>
       </c>
@@ -8009,7 +8009,7 @@
         <v>17</v>
       </c>
       <c r="L75" t="s">
-        <v>720</v>
+        <v>19</v>
       </c>
       <c r="M75" t="s">
         <v>721</v>
@@ -8024,7 +8024,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>729</v>
       </c>
@@ -8111,7 +8111,7 @@
         <v>171</v>
       </c>
       <c r="L77" t="s">
-        <v>720</v>
+        <v>19</v>
       </c>
       <c r="M77" t="s">
         <v>743</v>
@@ -8177,7 +8177,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>761</v>
       </c>
@@ -8228,7 +8228,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>765</v>
       </c>
@@ -8264,7 +8264,7 @@
         <v>81</v>
       </c>
       <c r="L80" t="s">
-        <v>180</v>
+        <v>19</v>
       </c>
       <c r="M80" t="s">
         <v>767</v>
@@ -8279,7 +8279,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>805</v>
       </c>
@@ -8381,7 +8381,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>835</v>
       </c>
@@ -8432,7 +8432,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>859</v>
       </c>
@@ -8483,7 +8483,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>863</v>
       </c>
@@ -8585,7 +8585,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>879</v>
       </c>
@@ -8636,7 +8636,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>885</v>
       </c>
@@ -8738,7 +8738,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>909</v>
       </c>
@@ -8789,7 +8789,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>1021</v>
       </c>
@@ -8840,7 +8840,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>1029</v>
       </c>
@@ -8891,7 +8891,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>1045</v>
       </c>
@@ -8978,7 +8978,7 @@
         <v>18</v>
       </c>
       <c r="L94" t="s">
-        <v>720</v>
+        <v>19</v>
       </c>
       <c r="M94" t="s">
         <v>783</v>
@@ -8993,7 +8993,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>265</v>
       </c>
@@ -9029,7 +9029,7 @@
         <v>36</v>
       </c>
       <c r="L95" t="s">
-        <v>180</v>
+        <v>731</v>
       </c>
       <c r="M95" t="s">
         <v>267</v>
@@ -9044,7 +9044,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>147</v>
       </c>
@@ -9197,7 +9197,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>202</v>
       </c>
@@ -9299,7 +9299,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>502</v>
       </c>
@@ -9401,7 +9401,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>793</v>
       </c>
@@ -9488,7 +9488,7 @@
         <v>36</v>
       </c>
       <c r="L104" t="s">
-        <v>720</v>
+        <v>19</v>
       </c>
       <c r="M104" t="s">
         <v>833</v>
@@ -9503,7 +9503,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>460</v>
       </c>
@@ -9554,7 +9554,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>944</v>
       </c>
@@ -9605,7 +9605,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>196</v>
       </c>
@@ -9656,7 +9656,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>269</v>
       </c>
@@ -9707,7 +9707,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>251</v>
       </c>
@@ -9758,7 +9758,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>648</v>
       </c>
@@ -9809,7 +9809,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>654</v>
       </c>
@@ -9860,7 +9860,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>660</v>
       </c>
@@ -9911,7 +9911,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>815</v>
       </c>
@@ -10013,7 +10013,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>34</v>
       </c>
@@ -10064,7 +10064,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>467</v>
       </c>
@@ -10115,7 +10115,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>950</v>
       </c>
@@ -10166,7 +10166,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>233</v>
       </c>
@@ -10217,7 +10217,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>233</v>
       </c>
@@ -10268,7 +10268,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>233</v>
       </c>
@@ -10319,7 +10319,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>233</v>
       </c>
@@ -10370,7 +10370,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>233</v>
       </c>
@@ -10421,7 +10421,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>233</v>
       </c>
@@ -10472,7 +10472,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>15</v>
       </c>
@@ -10523,7 +10523,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>454</v>
       </c>
@@ -10574,7 +10574,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>938</v>
       </c>
@@ -10676,7 +10676,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>165</v>
       </c>
@@ -10727,7 +10727,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>300</v>
       </c>
@@ -10778,7 +10778,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>343</v>
       </c>
@@ -10829,7 +10829,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="131" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>498</v>
       </c>
@@ -10880,7 +10880,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>110</v>
       </c>
@@ -10931,7 +10931,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="133" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>242</v>
       </c>
@@ -11084,7 +11084,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="136" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>294</v>
       </c>
@@ -11120,7 +11120,7 @@
         <v>88</v>
       </c>
       <c r="L136" t="s">
-        <v>180</v>
+        <v>731</v>
       </c>
       <c r="M136" t="s">
         <v>296</v>
@@ -11135,7 +11135,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="137" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>294</v>
       </c>
@@ -11171,7 +11171,7 @@
         <v>88</v>
       </c>
       <c r="L137" t="s">
-        <v>180</v>
+        <v>731</v>
       </c>
       <c r="M137" t="s">
         <v>297</v>
@@ -11186,7 +11186,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="138" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>396</v>
       </c>
@@ -11237,7 +11237,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>396</v>
       </c>
@@ -11288,7 +11288,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="140" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>396</v>
       </c>
@@ -11339,7 +11339,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="141" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>396</v>
       </c>
@@ -11390,7 +11390,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="142" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>396</v>
       </c>
@@ -11441,7 +11441,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="143" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>396</v>
       </c>
@@ -11492,7 +11492,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="144" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>396</v>
       </c>
@@ -11747,7 +11747,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="149" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>280</v>
       </c>
@@ -11798,7 +11798,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="150" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>1017</v>
       </c>
@@ -11849,7 +11849,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="151" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>288</v>
       </c>
@@ -11900,7 +11900,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="152" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>288</v>
       </c>
@@ -11951,7 +11951,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="153" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>288</v>
       </c>
@@ -12002,7 +12002,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="154" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>288</v>
       </c>
@@ -12053,7 +12053,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="155" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>489</v>
       </c>
@@ -12089,7 +12089,7 @@
         <v>81</v>
       </c>
       <c r="L155" t="s">
-        <v>180</v>
+        <v>19</v>
       </c>
       <c r="M155" t="s">
         <v>491</v>
@@ -12206,7 +12206,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="158" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>616</v>
       </c>
@@ -12242,7 +12242,7 @@
         <v>28</v>
       </c>
       <c r="L158" t="s">
-        <v>180</v>
+        <v>44</v>
       </c>
       <c r="M158" t="s">
         <v>618</v>
@@ -12257,7 +12257,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="159" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>620</v>
       </c>
@@ -12308,7 +12308,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="160" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>755</v>
       </c>
@@ -12344,7 +12344,7 @@
         <v>185</v>
       </c>
       <c r="L160" t="s">
-        <v>180</v>
+        <v>19</v>
       </c>
       <c r="M160" t="s">
         <v>757</v>
@@ -12359,7 +12359,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="161" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>799</v>
       </c>
@@ -12461,7 +12461,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="163" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>992</v>
       </c>
@@ -12512,7 +12512,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="164" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>1037</v>
       </c>
@@ -12548,7 +12548,7 @@
         <v>91</v>
       </c>
       <c r="L164" t="s">
-        <v>180</v>
+        <v>44</v>
       </c>
       <c r="M164" t="s">
         <v>1039</v>
@@ -12563,7 +12563,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="165" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>1041</v>
       </c>
@@ -12599,7 +12599,7 @@
         <v>43</v>
       </c>
       <c r="L165" t="s">
-        <v>180</v>
+        <v>112</v>
       </c>
       <c r="M165" t="s">
         <v>1043</v>
@@ -12665,7 +12665,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="167" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>1055</v>
       </c>
@@ -12701,7 +12701,7 @@
         <v>95</v>
       </c>
       <c r="L167" t="s">
-        <v>180</v>
+        <v>19</v>
       </c>
       <c r="M167" t="s">
         <v>1057</v>
@@ -12716,7 +12716,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="168" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>214</v>
       </c>
@@ -12752,7 +12752,7 @@
         <v>18</v>
       </c>
       <c r="L168" t="s">
-        <v>180</v>
+        <v>44</v>
       </c>
       <c r="M168" t="s">
         <v>216</v>
@@ -12767,7 +12767,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="169" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>811</v>
       </c>
@@ -12818,7 +12818,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="170" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>347</v>
       </c>
@@ -12854,7 +12854,7 @@
         <v>36</v>
       </c>
       <c r="L170" t="s">
-        <v>180</v>
+        <v>731</v>
       </c>
       <c r="M170" t="s">
         <v>349</v>
@@ -12869,7 +12869,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="171" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>313</v>
       </c>
@@ -12971,7 +12971,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="173" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>689</v>
       </c>
@@ -13073,7 +13073,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="175" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>808</v>
       </c>
@@ -13124,7 +13124,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="176" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>959</v>
       </c>
@@ -13175,7 +13175,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="177" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>318</v>
       </c>
@@ -13211,7 +13211,7 @@
         <v>185</v>
       </c>
       <c r="L177" t="s">
-        <v>180</v>
+        <v>731</v>
       </c>
       <c r="M177" t="s">
         <v>320</v>
@@ -13226,7 +13226,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="178" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>508</v>
       </c>
@@ -13277,7 +13277,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="179" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>891</v>
       </c>
@@ -13328,7 +13328,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="180" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>891</v>
       </c>
@@ -13415,7 +13415,7 @@
         <v>33</v>
       </c>
       <c r="L181" t="s">
-        <v>720</v>
+        <v>19</v>
       </c>
       <c r="M181" t="s">
         <v>1009</v>
@@ -13430,7 +13430,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="182" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>59</v>
       </c>
@@ -13481,7 +13481,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="183" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>178</v>
       </c>
@@ -13517,7 +13517,7 @@
         <v>28</v>
       </c>
       <c r="L183" t="s">
-        <v>180</v>
+        <v>731</v>
       </c>
       <c r="M183" t="s">
         <v>181</v>
@@ -13532,7 +13532,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="184" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>178</v>
       </c>
@@ -13568,7 +13568,7 @@
         <v>28</v>
       </c>
       <c r="L184" t="s">
-        <v>180</v>
+        <v>731</v>
       </c>
       <c r="M184" t="s">
         <v>182</v>
@@ -13583,7 +13583,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="185" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>178</v>
       </c>
@@ -13619,7 +13619,7 @@
         <v>185</v>
       </c>
       <c r="L185" t="s">
-        <v>180</v>
+        <v>731</v>
       </c>
       <c r="M185" t="s">
         <v>184</v>
@@ -13634,7 +13634,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="186" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>976</v>
       </c>
@@ -13685,7 +13685,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="187" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>980</v>
       </c>
@@ -13736,7 +13736,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="188" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>423</v>
       </c>
@@ -13787,7 +13787,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="189" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>427</v>
       </c>
@@ -13838,7 +13838,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="190" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>839</v>
       </c>
@@ -13889,7 +13889,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="191" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>843</v>
       </c>
@@ -13940,7 +13940,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="192" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>367</v>
       </c>
@@ -14042,7 +14042,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="194" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>733</v>
       </c>
@@ -14093,7 +14093,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="195" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>973</v>
       </c>
@@ -14144,7 +14144,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="196" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>100</v>
       </c>
@@ -14195,7 +14195,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="197" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>107</v>
       </c>
@@ -14246,7 +14246,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="198" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>374</v>
       </c>
@@ -14297,7 +14297,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="199" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>505</v>
       </c>
@@ -14348,7 +14348,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="200" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>738</v>
       </c>
@@ -14603,7 +14603,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="205" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>48</v>
       </c>
@@ -14654,7 +14654,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="206" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>275</v>
       </c>
@@ -14705,7 +14705,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="207" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>189</v>
       </c>
@@ -14756,7 +14756,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="208" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>189</v>
       </c>
@@ -14858,7 +14858,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="210" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>211</v>
       </c>
@@ -14909,7 +14909,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="211" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>222</v>
       </c>
@@ -14960,7 +14960,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="212" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>222</v>
       </c>
@@ -15011,7 +15011,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="213" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>222</v>
       </c>
@@ -15062,7 +15062,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="214" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>222</v>
       </c>
@@ -15113,7 +15113,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="215" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>415</v>
       </c>
@@ -15368,7 +15368,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="220" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>199</v>
       </c>
@@ -15419,7 +15419,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="221" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>199</v>
       </c>
@@ -15470,7 +15470,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="222" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>777</v>
       </c>
@@ -15557,7 +15557,7 @@
         <v>36</v>
       </c>
       <c r="L223" t="s">
-        <v>720</v>
+        <v>19</v>
       </c>
       <c r="M223" t="s">
         <v>791</v>
@@ -15572,7 +15572,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="224" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>30</v>
       </c>
@@ -15623,7 +15623,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="225" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>38</v>
       </c>
@@ -15674,7 +15674,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="226" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>205</v>
       </c>
@@ -15725,7 +15725,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="227" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>205</v>
       </c>
@@ -15776,7 +15776,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="228" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>272</v>
       </c>
@@ -15827,7 +15827,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="229" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>272</v>
       </c>
@@ -15878,7 +15878,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="230" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>22</v>
       </c>
@@ -15929,7 +15929,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="231" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>457</v>
       </c>
@@ -15980,7 +15980,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="232" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>463</v>
       </c>
@@ -16031,7 +16031,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="233" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>463</v>
       </c>
@@ -16082,7 +16082,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="234" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>470</v>
       </c>
@@ -16133,7 +16133,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="235" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>535</v>
       </c>
@@ -16235,7 +16235,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="237" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>651</v>
       </c>
@@ -16286,7 +16286,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="238" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>657</v>
       </c>
@@ -16337,7 +16337,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="239" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>663</v>
       </c>
@@ -16490,7 +16490,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="242" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>941</v>
       </c>
@@ -16541,7 +16541,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="243" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>947</v>
       </c>
@@ -16592,7 +16592,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="244" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>953</v>
       </c>
@@ -16949,7 +16949,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="251" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>639</v>
       </c>
@@ -17000,7 +17000,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="252" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>888</v>
       </c>
@@ -17051,7 +17051,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="253" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>965</v>
       </c>
@@ -17102,7 +17102,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="254" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>1032</v>
       </c>
@@ -17306,7 +17306,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="258" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>447</v>
       </c>
@@ -17663,7 +17663,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="265" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>912</v>
       </c>
@@ -17867,7 +17867,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="269" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>476</v>
       </c>
@@ -17918,7 +17918,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="270" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>493</v>
       </c>
@@ -18020,7 +18020,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="272" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>753</v>
       </c>
@@ -18173,7 +18173,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="275" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>559</v>
       </c>
@@ -18224,7 +18224,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="276" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>576</v>
       </c>
@@ -18275,7 +18275,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="277" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>576</v>
       </c>
@@ -18326,7 +18326,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="278" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>576</v>
       </c>
@@ -18377,7 +18377,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="279" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>576</v>
       </c>
@@ -18428,7 +18428,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="280" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>758</v>
       </c>
@@ -18464,7 +18464,7 @@
         <v>185</v>
       </c>
       <c r="L280" t="s">
-        <v>180</v>
+        <v>19</v>
       </c>
       <c r="M280" t="s">
         <v>759</v>
@@ -18530,7 +18530,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="282" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>539</v>
       </c>
@@ -18581,7 +18581,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="283" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
         <v>339</v>
       </c>
@@ -18683,7 +18683,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="285" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>726</v>
       </c>
@@ -18887,7 +18887,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="289" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>480</v>
       </c>
@@ -18938,7 +18938,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="290" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>705</v>
       </c>
@@ -18989,7 +18989,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="291" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>89</v>
       </c>
@@ -19040,7 +19040,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="292" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
         <v>89</v>
       </c>
@@ -19091,7 +19091,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="293" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>150</v>
       </c>
@@ -19244,7 +19244,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="296" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
         <v>488</v>
       </c>
@@ -19346,7 +19346,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="298" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>999</v>
       </c>
@@ -19397,7 +19397,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="299" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
         <v>999</v>
       </c>
@@ -19703,7 +19703,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="305" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
         <v>173</v>
       </c>
@@ -19958,7 +19958,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="310" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
         <v>351</v>
       </c>
@@ -20009,7 +20009,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="311" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
         <v>595</v>
       </c>
@@ -20162,7 +20162,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="314" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
         <v>351</v>
       </c>
@@ -20213,7 +20213,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="315" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
         <v>351</v>
       </c>
@@ -20264,7 +20264,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="316" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
         <v>673</v>
       </c>
@@ -20315,7 +20315,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="317" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
         <v>673</v>
       </c>
@@ -20366,7 +20366,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="318" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
         <v>764</v>
       </c>
@@ -20417,7 +20417,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="319" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
         <v>823</v>
       </c>
@@ -20468,7 +20468,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="320" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
         <v>825</v>
       </c>
@@ -20519,7 +20519,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="321" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
         <v>870</v>
       </c>
@@ -20555,7 +20555,7 @@
         <v>33</v>
       </c>
       <c r="L321" t="s">
-        <v>180</v>
+        <v>112</v>
       </c>
       <c r="M321" t="s">
         <v>25</v>
@@ -20723,7 +20723,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="325" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
         <v>146</v>
       </c>
@@ -20774,7 +20774,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="326" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
         <v>303</v>
       </c>
@@ -20825,7 +20825,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="327" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
         <v>303</v>
       </c>
@@ -20876,7 +20876,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="328" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
         <v>254</v>
       </c>
@@ -20978,7 +20978,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="330" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
         <v>669</v>
       </c>
@@ -21029,7 +21029,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="331" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
         <v>802</v>
       </c>
@@ -21080,7 +21080,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="332" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
         <v>114</v>
       </c>
@@ -21182,7 +21182,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="334" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
         <v>532</v>
       </c>
@@ -21233,7 +21233,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="335" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
         <v>534</v>
       </c>
@@ -21284,7 +21284,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="336" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
         <v>547</v>
       </c>
@@ -21335,7 +21335,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="337" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
         <v>701</v>
       </c>
@@ -21437,7 +21437,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="339" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
         <v>768</v>
       </c>
@@ -21473,7 +21473,7 @@
         <v>81</v>
       </c>
       <c r="L339" t="s">
-        <v>180</v>
+        <v>19</v>
       </c>
       <c r="M339" t="s">
         <v>25</v>
@@ -21539,7 +21539,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="341" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
         <v>797</v>
       </c>
@@ -21590,7 +21590,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="342" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
         <v>862</v>
       </c>
@@ -21641,7 +21641,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="343" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
         <v>866</v>
       </c>
@@ -21794,7 +21794,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="346" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
         <v>61</v>
       </c>
@@ -21845,7 +21845,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="347" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
         <v>1020</v>
       </c>
@@ -21896,7 +21896,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="348" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
         <v>292</v>
       </c>
@@ -21947,7 +21947,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="349" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
         <v>292</v>
       </c>
@@ -22049,7 +22049,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="351" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
         <v>492</v>
       </c>
@@ -22085,7 +22085,7 @@
         <v>81</v>
       </c>
       <c r="L351" t="s">
-        <v>180</v>
+        <v>19</v>
       </c>
       <c r="M351" t="s">
         <v>25</v>
@@ -22100,7 +22100,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="352" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
         <v>614</v>
       </c>
@@ -22136,7 +22136,7 @@
         <v>33</v>
       </c>
       <c r="L352" t="s">
-        <v>180</v>
+        <v>731</v>
       </c>
       <c r="M352" t="s">
         <v>25</v>
@@ -22238,7 +22238,7 @@
         <v>67</v>
       </c>
       <c r="L354" t="s">
-        <v>720</v>
+        <v>19</v>
       </c>
       <c r="M354" t="s">
         <v>25</v>
@@ -22253,7 +22253,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="355" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
         <v>1011</v>
       </c>
@@ -22304,7 +22304,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="356" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
         <v>1087</v>
       </c>
@@ -22442,7 +22442,7 @@
         <v>171</v>
       </c>
       <c r="L358" t="s">
-        <v>720</v>
+        <v>19</v>
       </c>
       <c r="M358" t="s">
         <v>25</v>
@@ -22508,7 +22508,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="360" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
         <v>321</v>
       </c>
@@ -22544,7 +22544,7 @@
         <v>185</v>
       </c>
       <c r="L360" t="s">
-        <v>180</v>
+        <v>731</v>
       </c>
       <c r="M360" t="s">
         <v>322</v>
@@ -22559,7 +22559,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="361" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
         <v>796</v>
       </c>
@@ -22610,7 +22610,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="362" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
         <v>814</v>
       </c>
@@ -22763,7 +22763,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="365" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
         <v>961</v>
       </c>
@@ -22814,7 +22814,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="366" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
         <v>1027</v>
       </c>
@@ -22865,7 +22865,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="367" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
         <v>370</v>
       </c>
@@ -22916,7 +22916,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="368" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
         <v>201</v>
       </c>
@@ -22967,7 +22967,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="369" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
         <v>334</v>
       </c>
@@ -23018,7 +23018,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="370" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
         <v>316</v>
       </c>
@@ -23324,7 +23324,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="376" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
         <v>511</v>
       </c>
@@ -23426,7 +23426,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="378" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
         <v>628</v>
       </c>
@@ -23513,7 +23513,7 @@
         <v>171</v>
       </c>
       <c r="L379" t="s">
-        <v>720</v>
+        <v>19</v>
       </c>
       <c r="M379" t="s">
         <v>25</v>
@@ -23528,7 +23528,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="380" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
         <v>377</v>
       </c>
@@ -23579,7 +23579,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="381" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
         <v>426</v>
       </c>
@@ -23630,7 +23630,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="382" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
         <v>430</v>
       </c>
@@ -23681,7 +23681,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="383" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
         <v>283</v>
       </c>
@@ -23732,7 +23732,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="384" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
         <v>542</v>
       </c>
@@ -23819,7 +23819,7 @@
         <v>18</v>
       </c>
       <c r="L385" t="s">
-        <v>720</v>
+        <v>19</v>
       </c>
       <c r="M385" t="s">
         <v>25</v>
@@ -23834,7 +23834,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="386" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
         <v>842</v>
       </c>
@@ -23885,7 +23885,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="387" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
         <v>846</v>
       </c>
@@ -23936,7 +23936,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="388" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
         <v>979</v>
       </c>
@@ -23987,7 +23987,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="389" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
         <v>983</v>
       </c>
@@ -24038,7 +24038,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="390" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
         <v>995</v>
       </c>
@@ -24125,7 +24125,7 @@
         <v>33</v>
       </c>
       <c r="L391" t="s">
-        <v>720</v>
+        <v>19</v>
       </c>
       <c r="M391" t="s">
         <v>25</v>
@@ -24242,7 +24242,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="394" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
         <v>168</v>
       </c>
@@ -24293,7 +24293,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="395" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
         <v>612</v>
       </c>
@@ -24329,7 +24329,7 @@
         <v>33</v>
       </c>
       <c r="L395" t="s">
-        <v>180</v>
+        <v>731</v>
       </c>
       <c r="M395" t="s">
         <v>25</v>
@@ -24344,7 +24344,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="396" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
         <v>85</v>
       </c>
@@ -24395,7 +24395,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="397" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
         <v>356</v>
       </c>
@@ -24446,7 +24446,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="398" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
         <v>356</v>
       </c>
@@ -24497,7 +24497,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="399" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
         <v>274</v>
       </c>
@@ -24548,7 +24548,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="400" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
         <v>381</v>
       </c>
@@ -24584,7 +24584,7 @@
         <v>43</v>
       </c>
       <c r="L400" t="s">
-        <v>180</v>
+        <v>731</v>
       </c>
       <c r="M400" t="s">
         <v>25</v>
@@ -24596,10 +24596,10 @@
         <v>0</v>
       </c>
       <c r="P400" t="s">
-        <v>1098</v>
-      </c>
-    </row>
-    <row r="401" spans="1:16" x14ac:dyDescent="0.35">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="401" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
         <v>85</v>
       </c>
@@ -24803,7 +24803,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="405" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
         <v>361</v>
       </c>
@@ -24854,7 +24854,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="406" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
         <v>362</v>
       </c>
@@ -24905,7 +24905,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="407" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
         <v>501</v>
       </c>
@@ -25007,7 +25007,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="409" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
         <v>555</v>
       </c>
@@ -25058,7 +25058,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="410" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
         <v>574</v>
       </c>
@@ -25094,7 +25094,7 @@
         <v>171</v>
       </c>
       <c r="L410" t="s">
-        <v>180</v>
+        <v>731</v>
       </c>
       <c r="M410" t="s">
         <v>25</v>
@@ -25211,7 +25211,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="413" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
         <v>619</v>
       </c>
@@ -25247,7 +25247,7 @@
         <v>28</v>
       </c>
       <c r="L413" t="s">
-        <v>180</v>
+        <v>44</v>
       </c>
       <c r="M413" t="s">
         <v>25</v>
@@ -25262,7 +25262,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="414" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
         <v>623</v>
       </c>
@@ -25313,7 +25313,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="415" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
         <v>691</v>
       </c>
@@ -25451,7 +25451,7 @@
         <v>36</v>
       </c>
       <c r="L417" t="s">
-        <v>720</v>
+        <v>19</v>
       </c>
       <c r="M417" t="s">
         <v>25</v>
@@ -25466,7 +25466,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="418" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
         <v>838</v>
       </c>
@@ -25517,7 +25517,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="419" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
         <v>1024</v>
       </c>
@@ -25568,7 +25568,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="420" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
         <v>1044</v>
       </c>
@@ -25604,7 +25604,7 @@
         <v>67</v>
       </c>
       <c r="L420" t="s">
-        <v>180</v>
+        <v>112</v>
       </c>
       <c r="M420" t="s">
         <v>25</v>
@@ -25619,7 +25619,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="421" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
         <v>1048</v>
       </c>
@@ -25670,7 +25670,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="422" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
         <v>1058</v>
       </c>
@@ -25706,7 +25706,7 @@
         <v>95</v>
       </c>
       <c r="L422" t="s">
-        <v>180</v>
+        <v>19</v>
       </c>
       <c r="M422" t="s">
         <v>25</v>
@@ -25721,7 +25721,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="423" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
         <v>103</v>
       </c>
@@ -25772,7 +25772,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="424" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
         <v>109</v>
       </c>
@@ -25823,7 +25823,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="425" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
         <v>119</v>
       </c>
@@ -25925,7 +25925,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="427" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
         <v>572</v>
       </c>
@@ -25976,7 +25976,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="428" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
         <v>780</v>
       </c>
@@ -26078,7 +26078,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="430" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
         <v>194</v>
       </c>
@@ -26180,7 +26180,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="432" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
         <v>195</v>
       </c>
@@ -26231,7 +26231,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="433" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
         <v>225</v>
       </c>
@@ -26282,7 +26282,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="434" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
         <v>225</v>
       </c>
@@ -26333,7 +26333,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="435" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
         <v>238</v>
       </c>
@@ -26384,7 +26384,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="436" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
         <v>240</v>
       </c>
@@ -26435,7 +26435,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="437" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
         <v>238</v>
       </c>
@@ -26486,7 +26486,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="438" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
         <v>240</v>
       </c>
@@ -26537,7 +26537,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="439" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
         <v>279</v>
       </c>
@@ -26639,7 +26639,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="441" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
         <v>581</v>
       </c>
@@ -26690,7 +26690,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="442" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
         <v>583</v>
       </c>
@@ -26792,7 +26792,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="444" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
         <v>818</v>
       </c>
@@ -26843,7 +26843,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="445" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
         <v>882</v>
       </c>
@@ -26894,7 +26894,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="446" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
         <v>883</v>
       </c>
@@ -26945,7 +26945,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="447" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
         <v>897</v>
       </c>
@@ -26996,7 +26996,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="448" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
         <v>898</v>
       </c>
@@ -27047,7 +27047,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="449" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
         <v>217</v>
       </c>
@@ -27098,7 +27098,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="450" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
         <v>431</v>
       </c>
@@ -27134,7 +27134,7 @@
         <v>33</v>
       </c>
       <c r="L450" t="s">
-        <v>180</v>
+        <v>19</v>
       </c>
       <c r="M450" t="s">
         <v>25</v>
@@ -27200,7 +27200,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="452" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
         <v>419</v>
       </c>
@@ -27302,7 +27302,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="454" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
         <v>538</v>
       </c>
@@ -27353,7 +27353,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="455" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
         <v>711</v>
       </c>
@@ -27389,7 +27389,7 @@
         <v>88</v>
       </c>
       <c r="L455" t="s">
-        <v>180</v>
+        <v>44</v>
       </c>
       <c r="M455" t="s">
         <v>25</v>
@@ -27404,7 +27404,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="456" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
         <v>712</v>
       </c>
@@ -27440,7 +27440,7 @@
         <v>171</v>
       </c>
       <c r="L456" t="s">
-        <v>180</v>
+        <v>44</v>
       </c>
       <c r="M456" t="s">
         <v>25</v>
@@ -27455,7 +27455,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="457" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
         <v>350</v>
       </c>
@@ -27491,7 +27491,7 @@
         <v>88</v>
       </c>
       <c r="L457" t="s">
-        <v>180</v>
+        <v>731</v>
       </c>
       <c r="M457" t="s">
         <v>25</v>
@@ -27506,7 +27506,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="458" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
         <v>213</v>
       </c>
@@ -27557,7 +27557,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="459" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
         <v>298</v>
       </c>
@@ -27593,7 +27593,7 @@
         <v>88</v>
       </c>
       <c r="L459" t="s">
-        <v>180</v>
+        <v>731</v>
       </c>
       <c r="M459" t="s">
         <v>297</v>
@@ -27608,7 +27608,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="460" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
         <v>298</v>
       </c>
@@ -27644,7 +27644,7 @@
         <v>299</v>
       </c>
       <c r="L460" t="s">
-        <v>180</v>
+        <v>731</v>
       </c>
       <c r="M460" t="s">
         <v>296</v>
@@ -27659,7 +27659,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="461" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
         <v>355</v>
       </c>
@@ -27710,7 +27710,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="462" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
         <v>507</v>
       </c>
@@ -27761,7 +27761,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="463" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
         <v>551</v>
       </c>
@@ -27914,7 +27914,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="466" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
         <v>677</v>
       </c>
@@ -27965,7 +27965,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="467" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
         <v>740</v>
       </c>
@@ -28016,7 +28016,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="468" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
         <v>810</v>
       </c>
@@ -28322,7 +28322,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="474" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
         <v>975</v>
       </c>
@@ -28373,7 +28373,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="475" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
         <v>406</v>
       </c>
@@ -28424,7 +28424,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="476" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
         <v>407</v>
       </c>
@@ -28475,7 +28475,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="477" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
         <v>408</v>
       </c>
@@ -28526,7 +28526,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="478" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
         <v>268</v>
       </c>
@@ -28562,7 +28562,7 @@
         <v>95</v>
       </c>
       <c r="L478" t="s">
-        <v>180</v>
+        <v>731</v>
       </c>
       <c r="M478" t="s">
         <v>25</v>
@@ -28577,7 +28577,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="479" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
         <v>24</v>
       </c>
@@ -28628,7 +28628,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="480" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
         <v>207</v>
       </c>
@@ -28679,7 +28679,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="481" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
         <v>409</v>
       </c>
@@ -28730,7 +28730,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="482" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
         <v>410</v>
       </c>
@@ -28781,7 +28781,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="483" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
         <v>411</v>
       </c>
@@ -28832,7 +28832,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="484" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
         <v>412</v>
       </c>
@@ -28934,7 +28934,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="486" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
         <v>459</v>
       </c>
@@ -28985,7 +28985,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="487" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
         <v>563</v>
       </c>
@@ -29138,7 +29138,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="490" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
         <v>869</v>
       </c>
@@ -29189,7 +29189,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="491" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
         <v>943</v>
       </c>
@@ -29240,7 +29240,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="492" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
         <v>1035</v>
       </c>
@@ -29291,7 +29291,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="493" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
         <v>1040</v>
       </c>
@@ -29327,7 +29327,7 @@
         <v>91</v>
       </c>
       <c r="L493" t="s">
-        <v>180</v>
+        <v>44</v>
       </c>
       <c r="M493" t="s">
         <v>25</v>
@@ -29342,7 +29342,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="494" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
         <v>40</v>
       </c>
@@ -29393,7 +29393,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="495" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
         <v>472</v>
       </c>
@@ -29444,7 +29444,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="496" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
         <v>599</v>
       </c>
@@ -29480,7 +29480,7 @@
         <v>91</v>
       </c>
       <c r="L496" t="s">
-        <v>180</v>
+        <v>44</v>
       </c>
       <c r="M496" t="s">
         <v>25</v>
@@ -29495,7 +29495,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="497" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
         <v>653</v>
       </c>
@@ -29546,7 +29546,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="498" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
         <v>659</v>
       </c>
@@ -29597,7 +29597,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="499" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
         <v>760</v>
       </c>
@@ -29633,7 +29633,7 @@
         <v>185</v>
       </c>
       <c r="L499" t="s">
-        <v>180</v>
+        <v>19</v>
       </c>
       <c r="M499" t="s">
         <v>25</v>
@@ -29648,7 +29648,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="500" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
         <v>890</v>
       </c>
@@ -29699,7 +29699,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="501" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
         <v>955</v>
       </c>
@@ -29750,7 +29750,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="502" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
         <v>32</v>
       </c>
@@ -29801,7 +29801,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="503" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
         <v>466</v>
       </c>
@@ -29852,7 +29852,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="504" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
         <v>466</v>
       </c>
@@ -29903,7 +29903,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="505" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
         <v>949</v>
       </c>
@@ -29954,7 +29954,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="506" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
         <v>392</v>
       </c>
@@ -29990,7 +29990,7 @@
         <v>95</v>
       </c>
       <c r="L506" t="s">
-        <v>180</v>
+        <v>19</v>
       </c>
       <c r="M506" t="s">
         <v>25</v>
@@ -30005,7 +30005,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="507" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
         <v>131</v>
       </c>
@@ -30056,7 +30056,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="508" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
         <v>176</v>
       </c>
@@ -30107,7 +30107,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="509" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
         <v>324</v>
       </c>
@@ -30143,7 +30143,7 @@
         <v>185</v>
       </c>
       <c r="L509" t="s">
-        <v>180</v>
+        <v>731</v>
       </c>
       <c r="M509" t="s">
         <v>25</v>
@@ -30158,7 +30158,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="510" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
         <v>332</v>
       </c>
@@ -30209,7 +30209,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="511" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
         <v>422</v>
       </c>
@@ -30260,7 +30260,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="512" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
         <v>665</v>
       </c>
@@ -30311,7 +30311,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="513" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
         <v>433</v>
       </c>
@@ -30464,7 +30464,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="516" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
         <v>342</v>
       </c>
@@ -30515,7 +30515,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="517" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
         <v>373</v>
       </c>
@@ -30566,7 +30566,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="518" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
         <v>380</v>
       </c>
@@ -30617,7 +30617,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="519" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
         <v>525</v>
       </c>
@@ -30668,7 +30668,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="520" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
         <v>851</v>
       </c>
@@ -30719,7 +30719,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="521" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
         <v>245</v>
       </c>
@@ -30770,7 +30770,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="522" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
         <v>497</v>
       </c>
@@ -30872,7 +30872,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="524" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
         <v>183</v>
       </c>
@@ -30908,7 +30908,7 @@
         <v>28</v>
       </c>
       <c r="L524" t="s">
-        <v>180</v>
+        <v>731</v>
       </c>
       <c r="M524" t="s">
         <v>184</v>
@@ -30923,7 +30923,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="525" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
         <v>183</v>
       </c>
@@ -30959,7 +30959,7 @@
         <v>185</v>
       </c>
       <c r="L525" t="s">
-        <v>180</v>
+        <v>731</v>
       </c>
       <c r="M525" t="s">
         <v>181</v>
@@ -31025,7 +31025,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="527" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
         <v>435</v>
       </c>
@@ -31076,7 +31076,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="528" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
         <v>438</v>
       </c>
@@ -31127,7 +31127,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="529" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
         <v>441</v>
       </c>
@@ -31178,7 +31178,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="530" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
         <v>435</v>
       </c>
@@ -31229,7 +31229,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="531" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A531" t="s">
         <v>438</v>
       </c>
@@ -31280,7 +31280,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="532" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
         <v>441</v>
       </c>
@@ -31331,7 +31331,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="533" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
         <v>630</v>
       </c>
@@ -31382,7 +31382,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="534" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
         <v>632</v>
       </c>
@@ -31433,7 +31433,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="535" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
         <v>634</v>
       </c>
@@ -31484,7 +31484,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="536" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
         <v>915</v>
       </c>
@@ -31535,7 +31535,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="537" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
         <v>917</v>
       </c>
@@ -31586,7 +31586,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="538" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
         <v>919</v>
       </c>
@@ -31637,7 +31637,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="539" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
         <v>1066</v>
       </c>
@@ -31688,7 +31688,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="540" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
         <v>1068</v>
       </c>
@@ -31739,7 +31739,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="541" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
         <v>1070</v>
       </c>
@@ -31790,7 +31790,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="542" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
         <v>449</v>
       </c>
@@ -31841,7 +31841,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="543" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
         <v>452</v>
       </c>
@@ -31892,7 +31892,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="544" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
         <v>641</v>
       </c>
@@ -31943,7 +31943,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="545" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
         <v>646</v>
       </c>
@@ -32045,7 +32045,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="547" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
         <v>914</v>
       </c>
@@ -32096,7 +32096,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="548" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
         <v>921</v>
       </c>
@@ -32147,7 +32147,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="549" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
         <v>923</v>
       </c>
@@ -32198,7 +32198,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="550" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
         <v>931</v>
       </c>
@@ -32249,7 +32249,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="551" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
         <v>933</v>
       </c>
@@ -32300,7 +32300,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="552" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
         <v>933</v>
       </c>
@@ -32351,7 +32351,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="553" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
         <v>933</v>
       </c>
@@ -32402,7 +32402,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="554" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
         <v>933</v>
       </c>
@@ -32453,7 +32453,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="555" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A555" t="s">
         <v>1034</v>
       </c>
@@ -32504,7 +32504,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="556" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A556" t="s">
         <v>1078</v>
       </c>
@@ -32555,7 +32555,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="557" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A557" t="s">
         <v>1085</v>
       </c>
@@ -32606,7 +32606,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="558" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A558" t="s">
         <v>1089</v>
       </c>
@@ -32657,7 +32657,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="559" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A559" t="s">
         <v>1091</v>
       </c>
@@ -32708,7 +32708,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="560" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A560" t="s">
         <v>1093</v>
       </c>
@@ -32759,7 +32759,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="561" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A561" t="s">
         <v>1093</v>
       </c>
@@ -32810,7 +32810,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="562" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
         <v>728</v>
       </c>
@@ -32861,7 +32861,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="563" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
         <v>925</v>
       </c>
@@ -32912,7 +32912,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="564" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
         <v>927</v>
       </c>
@@ -32963,7 +32963,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="565" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
         <v>1080</v>
       </c>
@@ -33014,7 +33014,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="566" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
         <v>450</v>
       </c>
@@ -33065,7 +33065,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="567" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A567" t="s">
         <v>642</v>
       </c>
@@ -33116,7 +33116,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="568" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A568" t="s">
         <v>644</v>
       </c>
@@ -33167,7 +33167,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="569" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A569" t="s">
         <v>929</v>
       </c>
@@ -33218,7 +33218,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="570" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A570" t="s">
         <v>1072</v>
       </c>
@@ -33320,7 +33320,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="572" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
         <v>1075</v>
       </c>
@@ -33422,7 +33422,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="574" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A574" t="s">
         <v>1082</v>
       </c>
@@ -33526,6 +33526,11 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:P575" xr:uid="{DA2BF836-2FD5-4520-BC72-6D688307FCF3}">
+    <filterColumn colId="11">
+      <filters>
+        <filter val="GROWTH_FLUCTUATING"/>
+      </filters>
+    </filterColumn>
     <filterColumn colId="15">
       <filters>
         <filter val="Y"/>
@@ -33536,5 +33541,6 @@
     <sortCondition ref="I1:I575"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/all_generations_pokemon_families.xlsx
+++ b/all_generations_pokemon_families.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\apetronack\Documents\Projects\pokefirered-expansion\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Austin\Documents\Pokemon and Gameboy\PokemonDecompBuild\pokefirered-expansion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{8F5A88A5-85B3-4260-B9DF-7B6D611872F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47105793-33DB-440F-953C-B4C5E9ED544F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{CFD33D56-DCEE-4C8F-A281-92D9AA7B5F95}"/>
+    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{CFD33D56-DCEE-4C8F-A281-92D9AA7B5F95}"/>
   </bookViews>
   <sheets>
     <sheet name="all_generations_pokemon_familie" sheetId="1" r:id="rId1"/>
@@ -18,12 +18,25 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">all_generations_pokemon_familie!$A$1:$P$575</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4709" uniqueCount="1099">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4709" uniqueCount="1101">
   <si>
     <t>Display Name</t>
   </si>
@@ -3320,6 +3333,12 @@
   </si>
   <si>
     <t>Y</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>R</t>
   </si>
 </sst>
 </file>
@@ -4276,7 +4295,7 @@
         <v>20</v>
       </c>
       <c r="I2">
-        <f>SUM(C2:H2)</f>
+        <f t="shared" ref="I2:I65" si="0">SUM(C2:H2)</f>
         <v>200</v>
       </c>
       <c r="J2" t="s">
@@ -4327,7 +4346,7 @@
         <v>20</v>
       </c>
       <c r="I3">
-        <f>SUM(C3:H3)</f>
+        <f t="shared" si="0"/>
         <v>200</v>
       </c>
       <c r="J3" t="s">
@@ -4378,7 +4397,7 @@
         <v>20</v>
       </c>
       <c r="I4">
-        <f>SUM(C4:H4)</f>
+        <f t="shared" si="0"/>
         <v>200</v>
       </c>
       <c r="J4" t="s">
@@ -4429,7 +4448,7 @@
         <v>35</v>
       </c>
       <c r="I5">
-        <f>SUM(C5:H5)</f>
+        <f t="shared" si="0"/>
         <v>200</v>
       </c>
       <c r="J5" t="s">
@@ -4480,7 +4499,7 @@
         <v>55</v>
       </c>
       <c r="I6">
-        <f>SUM(C6:H6)</f>
+        <f t="shared" si="0"/>
         <v>200</v>
       </c>
       <c r="J6" t="s">
@@ -4531,7 +4550,7 @@
         <v>65</v>
       </c>
       <c r="I7">
-        <f>SUM(C7:H7)</f>
+        <f t="shared" si="0"/>
         <v>220</v>
       </c>
       <c r="J7" t="s">
@@ -4582,7 +4601,7 @@
         <v>65</v>
       </c>
       <c r="I8">
-        <f>SUM(C8:H8)</f>
+        <f t="shared" si="0"/>
         <v>220</v>
       </c>
       <c r="J8" t="s">
@@ -4633,7 +4652,7 @@
         <v>25</v>
       </c>
       <c r="I9">
-        <f>SUM(C9:H9)</f>
+        <f t="shared" si="0"/>
         <v>225</v>
       </c>
       <c r="J9" t="s">
@@ -4684,7 +4703,7 @@
         <v>25</v>
       </c>
       <c r="I10">
-        <f>SUM(C10:H10)</f>
+        <f t="shared" si="0"/>
         <v>225</v>
       </c>
       <c r="J10" t="s">
@@ -4735,7 +4754,7 @@
         <v>25</v>
       </c>
       <c r="I11">
-        <f>SUM(C11:H11)</f>
+        <f t="shared" si="0"/>
         <v>225</v>
       </c>
       <c r="J11" t="s">
@@ -4786,7 +4805,7 @@
         <v>25</v>
       </c>
       <c r="I12">
-        <f>SUM(C12:H12)</f>
+        <f t="shared" si="0"/>
         <v>225</v>
       </c>
       <c r="J12" t="s">
@@ -4837,7 +4856,7 @@
         <v>40</v>
       </c>
       <c r="I13">
-        <f>SUM(C13:H13)</f>
+        <f t="shared" si="0"/>
         <v>240</v>
       </c>
       <c r="J13" t="s">
@@ -4888,7 +4907,7 @@
         <v>40</v>
       </c>
       <c r="I14">
-        <f>SUM(C14:H14)</f>
+        <f t="shared" si="0"/>
         <v>245</v>
       </c>
       <c r="J14" t="s">
@@ -4939,7 +4958,7 @@
         <v>55</v>
       </c>
       <c r="I15">
-        <f>SUM(C15:H15)</f>
+        <f t="shared" si="0"/>
         <v>245</v>
       </c>
       <c r="J15" t="s">
@@ -4990,7 +5009,7 @@
         <v>45</v>
       </c>
       <c r="I16">
-        <f>SUM(C16:H16)</f>
+        <f t="shared" si="0"/>
         <v>250</v>
       </c>
       <c r="J16" t="s">
@@ -5041,7 +5060,7 @@
         <v>30</v>
       </c>
       <c r="I17">
-        <f>SUM(C17:H17)</f>
+        <f t="shared" si="0"/>
         <v>250</v>
       </c>
       <c r="J17" t="s">
@@ -5092,7 +5111,7 @@
         <v>41</v>
       </c>
       <c r="I18">
-        <f>SUM(C18:H18)</f>
+        <f t="shared" si="0"/>
         <v>250</v>
       </c>
       <c r="J18" t="s">
@@ -5143,7 +5162,7 @@
         <v>30</v>
       </c>
       <c r="I19">
-        <f>SUM(C19:H19)</f>
+        <f t="shared" si="0"/>
         <v>250</v>
       </c>
       <c r="J19" t="s">
@@ -5168,7 +5187,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="20" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>962</v>
       </c>
@@ -5194,7 +5213,7 @@
         <v>40</v>
       </c>
       <c r="I20">
-        <f>SUM(C20:H20)</f>
+        <f t="shared" si="0"/>
         <v>250</v>
       </c>
       <c r="J20" t="s">
@@ -5216,7 +5235,7 @@
         <v>15</v>
       </c>
       <c r="P20" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="21" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
@@ -5245,7 +5264,7 @@
         <v>35</v>
       </c>
       <c r="I21">
-        <f>SUM(C21:H21)</f>
+        <f t="shared" si="0"/>
         <v>251</v>
       </c>
       <c r="J21" t="s">
@@ -5296,7 +5315,7 @@
         <v>35</v>
       </c>
       <c r="I22">
-        <f>SUM(C22:H22)</f>
+        <f t="shared" si="0"/>
         <v>253</v>
       </c>
       <c r="J22" t="s">
@@ -5347,7 +5366,7 @@
         <v>35</v>
       </c>
       <c r="I23">
-        <f>SUM(C23:H23)</f>
+        <f t="shared" si="0"/>
         <v>253</v>
       </c>
       <c r="J23" t="s">
@@ -5398,7 +5417,7 @@
         <v>35</v>
       </c>
       <c r="I24">
-        <f>SUM(C24:H24)</f>
+        <f t="shared" si="0"/>
         <v>253</v>
       </c>
       <c r="J24" t="s">
@@ -5449,7 +5468,7 @@
         <v>25</v>
       </c>
       <c r="I25">
-        <f>SUM(C25:H25)</f>
+        <f t="shared" si="0"/>
         <v>255</v>
       </c>
       <c r="J25" t="s">
@@ -5500,7 +5519,7 @@
         <v>55</v>
       </c>
       <c r="I26">
-        <f>SUM(C26:H26)</f>
+        <f t="shared" si="0"/>
         <v>260</v>
       </c>
       <c r="J26" t="s">
@@ -5551,7 +5570,7 @@
         <v>48</v>
       </c>
       <c r="I27">
-        <f>SUM(C27:H27)</f>
+        <f t="shared" si="0"/>
         <v>260</v>
       </c>
       <c r="J27" t="s">
@@ -5576,7 +5595,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="28" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>592</v>
       </c>
@@ -5602,7 +5621,7 @@
         <v>45</v>
       </c>
       <c r="I28">
-        <f>SUM(C28:H28)</f>
+        <f t="shared" si="0"/>
         <v>260</v>
       </c>
       <c r="J28" t="s">
@@ -5624,7 +5643,7 @@
         <v>38</v>
       </c>
       <c r="P28" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="29" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
@@ -5653,7 +5672,7 @@
         <v>30</v>
       </c>
       <c r="I29">
-        <f>SUM(C29:H29)</f>
+        <f t="shared" si="0"/>
         <v>260</v>
       </c>
       <c r="J29" t="s">
@@ -5704,7 +5723,7 @@
         <v>35</v>
       </c>
       <c r="I30">
-        <f>SUM(C30:H30)</f>
+        <f t="shared" si="0"/>
         <v>270</v>
       </c>
       <c r="J30" t="s">
@@ -5755,7 +5774,7 @@
         <v>30</v>
       </c>
       <c r="I31">
-        <f>SUM(C31:H31)</f>
+        <f t="shared" si="0"/>
         <v>270</v>
       </c>
       <c r="J31" t="s">
@@ -5806,7 +5825,7 @@
         <v>40</v>
       </c>
       <c r="I32">
-        <f>SUM(C32:H32)</f>
+        <f t="shared" si="0"/>
         <v>275</v>
       </c>
       <c r="J32" t="s">
@@ -5857,7 +5876,7 @@
         <v>40</v>
       </c>
       <c r="I33">
-        <f>SUM(C33:H33)</f>
+        <f t="shared" si="0"/>
         <v>275</v>
       </c>
       <c r="J33" t="s">
@@ -5908,7 +5927,7 @@
         <v>40</v>
       </c>
       <c r="I34">
-        <f>SUM(C34:H34)</f>
+        <f t="shared" si="0"/>
         <v>275</v>
       </c>
       <c r="J34" t="s">
@@ -5959,7 +5978,7 @@
         <v>70</v>
       </c>
       <c r="I35">
-        <f>SUM(C35:H35)</f>
+        <f t="shared" si="0"/>
         <v>275</v>
       </c>
       <c r="J35" t="s">
@@ -6010,7 +6029,7 @@
         <v>25</v>
       </c>
       <c r="I36">
-        <f>SUM(C36:H36)</f>
+        <f t="shared" si="0"/>
         <v>275</v>
       </c>
       <c r="J36" t="s">
@@ -6061,7 +6080,7 @@
         <v>55</v>
       </c>
       <c r="I37">
-        <f>SUM(C37:H37)</f>
+        <f t="shared" si="0"/>
         <v>275</v>
       </c>
       <c r="J37" t="s">
@@ -6112,7 +6131,7 @@
         <v>53</v>
       </c>
       <c r="I38">
-        <f>SUM(C38:H38)</f>
+        <f t="shared" si="0"/>
         <v>275</v>
       </c>
       <c r="J38" t="s">
@@ -6163,7 +6182,7 @@
         <v>40</v>
       </c>
       <c r="I39">
-        <f>SUM(C39:H39)</f>
+        <f t="shared" si="0"/>
         <v>280</v>
       </c>
       <c r="J39" t="s">
@@ -6214,7 +6233,7 @@
         <v>45</v>
       </c>
       <c r="I40">
-        <f>SUM(C40:H40)</f>
+        <f t="shared" si="0"/>
         <v>285</v>
       </c>
       <c r="J40" t="s">
@@ -6265,7 +6284,7 @@
         <v>55</v>
       </c>
       <c r="I41">
-        <f>SUM(C41:H41)</f>
+        <f t="shared" si="0"/>
         <v>285</v>
       </c>
       <c r="J41" t="s">
@@ -6316,7 +6335,7 @@
         <v>40</v>
       </c>
       <c r="I42">
-        <f>SUM(C42:H42)</f>
+        <f t="shared" si="0"/>
         <v>290</v>
       </c>
       <c r="J42" t="s">
@@ -6367,7 +6386,7 @@
         <v>55</v>
       </c>
       <c r="I43">
-        <f>SUM(C43:H43)</f>
+        <f t="shared" si="0"/>
         <v>290</v>
       </c>
       <c r="J43" t="s">
@@ -6418,7 +6437,7 @@
         <v>40</v>
       </c>
       <c r="I44">
-        <f>SUM(C44:H44)</f>
+        <f t="shared" si="0"/>
         <v>290</v>
       </c>
       <c r="J44" t="s">
@@ -6469,7 +6488,7 @@
         <v>54</v>
       </c>
       <c r="I45">
-        <f>SUM(C45:H45)</f>
+        <f t="shared" si="0"/>
         <v>293</v>
       </c>
       <c r="J45" t="s">
@@ -6520,7 +6539,7 @@
         <v>35</v>
       </c>
       <c r="I46">
-        <f>SUM(C46:H46)</f>
+        <f t="shared" si="0"/>
         <v>295</v>
       </c>
       <c r="J46" t="s">
@@ -6571,7 +6590,7 @@
         <v>60</v>
       </c>
       <c r="I47">
-        <f>SUM(C47:H47)</f>
+        <f t="shared" si="0"/>
         <v>295</v>
       </c>
       <c r="J47" t="s">
@@ -6622,7 +6641,7 @@
         <v>40</v>
       </c>
       <c r="I48">
-        <f>SUM(C48:H48)</f>
+        <f t="shared" si="0"/>
         <v>295</v>
       </c>
       <c r="J48" t="s">
@@ -6673,7 +6692,7 @@
         <v>50</v>
       </c>
       <c r="I49">
-        <f>SUM(C49:H49)</f>
+        <f t="shared" si="0"/>
         <v>299</v>
       </c>
       <c r="J49" t="s">
@@ -6724,7 +6743,7 @@
         <v>40</v>
       </c>
       <c r="I50">
-        <f>SUM(C50:H50)</f>
+        <f t="shared" si="0"/>
         <v>300</v>
       </c>
       <c r="J50" t="s">
@@ -6775,7 +6794,7 @@
         <v>65</v>
       </c>
       <c r="I51">
-        <f>SUM(C51:H51)</f>
+        <f t="shared" si="0"/>
         <v>300</v>
       </c>
       <c r="J51" t="s">
@@ -6826,7 +6845,7 @@
         <v>30</v>
       </c>
       <c r="I52">
-        <f>SUM(C52:H52)</f>
+        <f t="shared" si="0"/>
         <v>300</v>
       </c>
       <c r="J52" t="s">
@@ -6877,7 +6896,7 @@
         <v>25</v>
       </c>
       <c r="I53">
-        <f>SUM(C53:H53)</f>
+        <f t="shared" si="0"/>
         <v>300</v>
       </c>
       <c r="J53" t="s">
@@ -6928,7 +6947,7 @@
         <v>35</v>
       </c>
       <c r="I54">
-        <f>SUM(C54:H54)</f>
+        <f t="shared" si="0"/>
         <v>300</v>
       </c>
       <c r="J54" t="s">
@@ -6979,7 +6998,7 @@
         <v>65</v>
       </c>
       <c r="I55">
-        <f>SUM(C55:H55)</f>
+        <f t="shared" si="0"/>
         <v>300</v>
       </c>
       <c r="J55" t="s">
@@ -7030,7 +7049,7 @@
         <v>60</v>
       </c>
       <c r="I56">
-        <f>SUM(C56:H56)</f>
+        <f t="shared" si="0"/>
         <v>300</v>
       </c>
       <c r="J56" t="s">
@@ -7081,7 +7100,7 @@
         <v>40</v>
       </c>
       <c r="I57">
-        <f>SUM(C57:H57)</f>
+        <f t="shared" si="0"/>
         <v>300</v>
       </c>
       <c r="J57" t="s">
@@ -7132,7 +7151,7 @@
         <v>40</v>
       </c>
       <c r="I58">
-        <f>SUM(C58:H58)</f>
+        <f t="shared" si="0"/>
         <v>300</v>
       </c>
       <c r="J58" t="s">
@@ -7183,7 +7202,7 @@
         <v>30</v>
       </c>
       <c r="I59">
-        <f>SUM(C59:H59)</f>
+        <f t="shared" si="0"/>
         <v>300</v>
       </c>
       <c r="J59" t="s">
@@ -7234,7 +7253,7 @@
         <v>30</v>
       </c>
       <c r="I60">
-        <f>SUM(C60:H60)</f>
+        <f t="shared" si="0"/>
         <v>300</v>
       </c>
       <c r="J60" t="s">
@@ -7285,7 +7304,7 @@
         <v>30</v>
       </c>
       <c r="I61">
-        <f>SUM(C61:H61)</f>
+        <f t="shared" si="0"/>
         <v>300</v>
       </c>
       <c r="J61" t="s">
@@ -7336,7 +7355,7 @@
         <v>30</v>
       </c>
       <c r="I62">
-        <f>SUM(C62:H62)</f>
+        <f t="shared" si="0"/>
         <v>300</v>
       </c>
       <c r="J62" t="s">
@@ -7387,7 +7406,7 @@
         <v>50</v>
       </c>
       <c r="I63">
-        <f>SUM(C63:H63)</f>
+        <f t="shared" si="0"/>
         <v>300</v>
       </c>
       <c r="J63" t="s">
@@ -7438,7 +7457,7 @@
         <v>50</v>
       </c>
       <c r="I64">
-        <f>SUM(C64:H64)</f>
+        <f t="shared" si="0"/>
         <v>300</v>
       </c>
       <c r="J64" t="s">
@@ -7489,7 +7508,7 @@
         <v>80</v>
       </c>
       <c r="I65">
-        <f>SUM(C65:H65)</f>
+        <f t="shared" si="0"/>
         <v>300</v>
       </c>
       <c r="J65" t="s">
@@ -7540,7 +7559,7 @@
         <v>55</v>
       </c>
       <c r="I66">
-        <f>SUM(C66:H66)</f>
+        <f t="shared" ref="I66:I129" si="1">SUM(C66:H66)</f>
         <v>300</v>
       </c>
       <c r="J66" t="s">
@@ -7591,7 +7610,7 @@
         <v>55</v>
       </c>
       <c r="I67">
-        <f>SUM(C67:H67)</f>
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
       <c r="J67" t="s">
@@ -7642,7 +7661,7 @@
         <v>55</v>
       </c>
       <c r="I68">
-        <f>SUM(C68:H68)</f>
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
       <c r="J68" t="s">
@@ -7693,7 +7712,7 @@
         <v>55</v>
       </c>
       <c r="I69">
-        <f>SUM(C69:H69)</f>
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
       <c r="J69" t="s">
@@ -7744,7 +7763,7 @@
         <v>40</v>
       </c>
       <c r="I70">
-        <f>SUM(C70:H70)</f>
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
       <c r="J70" t="s">
@@ -7795,7 +7814,7 @@
         <v>35</v>
       </c>
       <c r="I71">
-        <f>SUM(C71:H71)</f>
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
       <c r="J71" t="s">
@@ -7846,7 +7865,7 @@
         <v>50</v>
       </c>
       <c r="I72">
-        <f>SUM(C72:H72)</f>
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
       <c r="J72" t="s">
@@ -7897,7 +7916,7 @@
         <v>60</v>
       </c>
       <c r="I73">
-        <f>SUM(C73:H73)</f>
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
       <c r="J73" t="s">
@@ -7948,7 +7967,7 @@
         <v>30</v>
       </c>
       <c r="I74">
-        <f>SUM(C74:H74)</f>
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
       <c r="J74" t="s">
@@ -7973,7 +7992,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>718</v>
       </c>
@@ -7999,7 +8018,7 @@
         <v>60</v>
       </c>
       <c r="I75">
-        <f>SUM(C75:H75)</f>
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
       <c r="J75" t="s">
@@ -8050,7 +8069,7 @@
         <v>40</v>
       </c>
       <c r="I76">
-        <f>SUM(C76:H76)</f>
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
       <c r="J76" t="s">
@@ -8075,7 +8094,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>741</v>
       </c>
@@ -8101,7 +8120,7 @@
         <v>50</v>
       </c>
       <c r="I77">
-        <f>SUM(C77:H77)</f>
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
       <c r="J77" t="s">
@@ -8152,7 +8171,7 @@
         <v>50</v>
       </c>
       <c r="I78">
-        <f>SUM(C78:H78)</f>
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
       <c r="J78" t="s">
@@ -8203,7 +8222,7 @@
         <v>55</v>
       </c>
       <c r="I79">
-        <f>SUM(C79:H79)</f>
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
       <c r="J79" t="s">
@@ -8254,7 +8273,7 @@
         <v>40</v>
       </c>
       <c r="I80">
-        <f>SUM(C80:H80)</f>
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
       <c r="J80" t="s">
@@ -8305,7 +8324,7 @@
         <v>45</v>
       </c>
       <c r="I81">
-        <f>SUM(C81:H81)</f>
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
       <c r="J81" t="s">
@@ -8356,7 +8375,7 @@
         <v>45</v>
       </c>
       <c r="I82">
-        <f>SUM(C82:H82)</f>
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
       <c r="J82" t="s">
@@ -8407,7 +8426,7 @@
         <v>70</v>
       </c>
       <c r="I83">
-        <f>SUM(C83:H83)</f>
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
       <c r="J83" t="s">
@@ -8458,7 +8477,7 @@
         <v>35</v>
       </c>
       <c r="I84">
-        <f>SUM(C84:H84)</f>
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
       <c r="J84" t="s">
@@ -8509,7 +8528,7 @@
         <v>90</v>
       </c>
       <c r="I85">
-        <f>SUM(C85:H85)</f>
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
       <c r="J85" t="s">
@@ -8560,7 +8579,7 @@
         <v>60</v>
       </c>
       <c r="I86">
-        <f>SUM(C86:H86)</f>
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
       <c r="J86" t="s">
@@ -8611,7 +8630,7 @@
         <v>50</v>
       </c>
       <c r="I87">
-        <f>SUM(C87:H87)</f>
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
       <c r="J87" t="s">
@@ -8662,7 +8681,7 @@
         <v>55</v>
       </c>
       <c r="I88">
-        <f>SUM(C88:H88)</f>
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
       <c r="J88" t="s">
@@ -8713,7 +8732,7 @@
         <v>30</v>
       </c>
       <c r="I89">
-        <f>SUM(C89:H89)</f>
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
       <c r="J89" t="s">
@@ -8764,7 +8783,7 @@
         <v>60</v>
       </c>
       <c r="I90">
-        <f>SUM(C90:H90)</f>
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
       <c r="J90" t="s">
@@ -8815,7 +8834,7 @@
         <v>86</v>
       </c>
       <c r="I91">
-        <f>SUM(C91:H91)</f>
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
       <c r="J91" t="s">
@@ -8866,7 +8885,7 @@
         <v>45</v>
       </c>
       <c r="I92">
-        <f>SUM(C92:H92)</f>
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
       <c r="J92" t="s">
@@ -8917,7 +8936,7 @@
         <v>40</v>
       </c>
       <c r="I93">
-        <f>SUM(C93:H93)</f>
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
       <c r="J93" t="s">
@@ -8942,7 +8961,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>781</v>
       </c>
@@ -8968,7 +8987,7 @@
         <v>53</v>
       </c>
       <c r="I94">
-        <f>SUM(C94:H94)</f>
+        <f t="shared" si="1"/>
         <v>302</v>
       </c>
       <c r="J94" t="s">
@@ -9019,7 +9038,7 @@
         <v>25</v>
       </c>
       <c r="I95">
-        <f>SUM(C95:H95)</f>
+        <f t="shared" si="1"/>
         <v>305</v>
       </c>
       <c r="J95" t="s">
@@ -9070,7 +9089,7 @@
         <v>55</v>
       </c>
       <c r="I96">
-        <f>SUM(C96:H96)</f>
+        <f t="shared" si="1"/>
         <v>305</v>
       </c>
       <c r="J96" t="s">
@@ -9121,7 +9140,7 @@
         <v>55</v>
       </c>
       <c r="I97">
-        <f>SUM(C97:H97)</f>
+        <f t="shared" si="1"/>
         <v>305</v>
       </c>
       <c r="J97" t="s">
@@ -9172,7 +9191,7 @@
         <v>55</v>
       </c>
       <c r="I98">
-        <f>SUM(C98:H98)</f>
+        <f t="shared" si="1"/>
         <v>305</v>
       </c>
       <c r="J98" t="s">
@@ -9223,7 +9242,7 @@
         <v>35</v>
       </c>
       <c r="I99">
-        <f>SUM(C99:H99)</f>
+        <f t="shared" si="1"/>
         <v>305</v>
       </c>
       <c r="J99" t="s">
@@ -9274,7 +9293,7 @@
         <v>65</v>
       </c>
       <c r="I100">
-        <f>SUM(C100:H100)</f>
+        <f t="shared" si="1"/>
         <v>305</v>
       </c>
       <c r="J100" t="s">
@@ -9325,7 +9344,7 @@
         <v>55</v>
       </c>
       <c r="I101">
-        <f>SUM(C101:H101)</f>
+        <f t="shared" si="1"/>
         <v>305</v>
       </c>
       <c r="J101" t="s">
@@ -9376,7 +9395,7 @@
         <v>20</v>
       </c>
       <c r="I102">
-        <f>SUM(C102:H102)</f>
+        <f t="shared" si="1"/>
         <v>305</v>
       </c>
       <c r="J102" t="s">
@@ -9427,7 +9446,7 @@
         <v>45</v>
       </c>
       <c r="I103">
-        <f>SUM(C103:H103)</f>
+        <f t="shared" si="1"/>
         <v>305</v>
       </c>
       <c r="J103" t="s">
@@ -9452,7 +9471,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>831</v>
       </c>
@@ -9478,7 +9497,7 @@
         <v>35</v>
       </c>
       <c r="I104">
-        <f>SUM(C104:H104)</f>
+        <f t="shared" si="1"/>
         <v>308</v>
       </c>
       <c r="J104" t="s">
@@ -9529,7 +9548,7 @@
         <v>50</v>
       </c>
       <c r="I105">
-        <f>SUM(C105:H105)</f>
+        <f t="shared" si="1"/>
         <v>309</v>
       </c>
       <c r="J105" t="s">
@@ -9580,7 +9599,7 @@
         <v>44</v>
       </c>
       <c r="I106">
-        <f>SUM(C106:H106)</f>
+        <f t="shared" si="1"/>
         <v>309</v>
       </c>
       <c r="J106" t="s">
@@ -9631,7 +9650,7 @@
         <v>55</v>
       </c>
       <c r="I107">
-        <f>SUM(C107:H107)</f>
+        <f t="shared" si="1"/>
         <v>310</v>
       </c>
       <c r="J107" t="s">
@@ -9682,7 +9701,7 @@
         <v>35</v>
       </c>
       <c r="I108">
-        <f>SUM(C108:H108)</f>
+        <f t="shared" si="1"/>
         <v>310</v>
       </c>
       <c r="J108" t="s">
@@ -9733,7 +9752,7 @@
         <v>35</v>
       </c>
       <c r="I109">
-        <f>SUM(C109:H109)</f>
+        <f t="shared" si="1"/>
         <v>310</v>
       </c>
       <c r="J109" t="s">
@@ -9784,7 +9803,7 @@
         <v>55</v>
       </c>
       <c r="I110">
-        <f>SUM(C110:H110)</f>
+        <f t="shared" si="1"/>
         <v>310</v>
       </c>
       <c r="J110" t="s">
@@ -9835,7 +9854,7 @@
         <v>50</v>
       </c>
       <c r="I111">
-        <f>SUM(C111:H111)</f>
+        <f t="shared" si="1"/>
         <v>310</v>
       </c>
       <c r="J111" t="s">
@@ -9886,7 +9905,7 @@
         <v>50</v>
       </c>
       <c r="I112">
-        <f>SUM(C112:H112)</f>
+        <f t="shared" si="1"/>
         <v>310</v>
       </c>
       <c r="J112" t="s">
@@ -9937,7 +9956,7 @@
         <v>75</v>
       </c>
       <c r="I113">
-        <f>SUM(C113:H113)</f>
+        <f t="shared" si="1"/>
         <v>310</v>
       </c>
       <c r="J113" t="s">
@@ -9988,7 +10007,7 @@
         <v>37</v>
       </c>
       <c r="I114">
-        <f>SUM(C114:H114)</f>
+        <f t="shared" si="1"/>
         <v>310</v>
       </c>
       <c r="J114" t="s">
@@ -10039,7 +10058,7 @@
         <v>64</v>
       </c>
       <c r="I115">
-        <f>SUM(C115:H115)</f>
+        <f t="shared" si="1"/>
         <v>314</v>
       </c>
       <c r="J115" t="s">
@@ -10090,7 +10109,7 @@
         <v>48</v>
       </c>
       <c r="I116">
-        <f>SUM(C116:H116)</f>
+        <f t="shared" si="1"/>
         <v>314</v>
       </c>
       <c r="J116" t="s">
@@ -10141,7 +10160,7 @@
         <v>56</v>
       </c>
       <c r="I117">
-        <f>SUM(C117:H117)</f>
+        <f t="shared" si="1"/>
         <v>314</v>
       </c>
       <c r="J117" t="s">
@@ -10192,7 +10211,7 @@
         <v>40</v>
       </c>
       <c r="I118">
-        <f>SUM(C118:H118)</f>
+        <f t="shared" si="1"/>
         <v>315</v>
       </c>
       <c r="J118" t="s">
@@ -10243,7 +10262,7 @@
         <v>40</v>
       </c>
       <c r="I119">
-        <f>SUM(C119:H119)</f>
+        <f t="shared" si="1"/>
         <v>315</v>
       </c>
       <c r="J119" t="s">
@@ -10294,7 +10313,7 @@
         <v>40</v>
       </c>
       <c r="I120">
-        <f>SUM(C120:H120)</f>
+        <f t="shared" si="1"/>
         <v>315</v>
       </c>
       <c r="J120" t="s">
@@ -10345,7 +10364,7 @@
         <v>40</v>
       </c>
       <c r="I121">
-        <f>SUM(C121:H121)</f>
+        <f t="shared" si="1"/>
         <v>315</v>
       </c>
       <c r="J121" t="s">
@@ -10396,7 +10415,7 @@
         <v>40</v>
       </c>
       <c r="I122">
-        <f>SUM(C122:H122)</f>
+        <f t="shared" si="1"/>
         <v>315</v>
       </c>
       <c r="J122" t="s">
@@ -10447,7 +10466,7 @@
         <v>40</v>
       </c>
       <c r="I123">
-        <f>SUM(C123:H123)</f>
+        <f t="shared" si="1"/>
         <v>315</v>
       </c>
       <c r="J123" t="s">
@@ -10498,7 +10517,7 @@
         <v>65</v>
       </c>
       <c r="I124">
-        <f>SUM(C124:H124)</f>
+        <f t="shared" si="1"/>
         <v>318</v>
       </c>
       <c r="J124" t="s">
@@ -10549,7 +10568,7 @@
         <v>65</v>
       </c>
       <c r="I125">
-        <f>SUM(C125:H125)</f>
+        <f t="shared" si="1"/>
         <v>318</v>
       </c>
       <c r="J125" t="s">
@@ -10600,7 +10619,7 @@
         <v>55</v>
       </c>
       <c r="I126">
-        <f>SUM(C126:H126)</f>
+        <f t="shared" si="1"/>
         <v>318</v>
       </c>
       <c r="J126" t="s">
@@ -10651,7 +10670,7 @@
         <v>65</v>
       </c>
       <c r="I127">
-        <f>SUM(C127:H127)</f>
+        <f t="shared" si="1"/>
         <v>320</v>
       </c>
       <c r="J127" t="s">
@@ -10702,7 +10721,7 @@
         <v>50</v>
       </c>
       <c r="I128">
-        <f>SUM(C128:H128)</f>
+        <f t="shared" si="1"/>
         <v>320</v>
       </c>
       <c r="J128" t="s">
@@ -10753,7 +10772,7 @@
         <v>50</v>
       </c>
       <c r="I129">
-        <f>SUM(C129:H129)</f>
+        <f t="shared" si="1"/>
         <v>320</v>
       </c>
       <c r="J129" t="s">
@@ -10804,7 +10823,7 @@
         <v>50</v>
       </c>
       <c r="I130">
-        <f>SUM(C130:H130)</f>
+        <f t="shared" ref="I130:I193" si="2">SUM(C130:H130)</f>
         <v>320</v>
       </c>
       <c r="J130" t="s">
@@ -10855,7 +10874,7 @@
         <v>45</v>
       </c>
       <c r="I131">
-        <f>SUM(C131:H131)</f>
+        <f t="shared" si="2"/>
         <v>320</v>
       </c>
       <c r="J131" t="s">
@@ -10906,7 +10925,7 @@
         <v>65</v>
       </c>
       <c r="I132">
-        <f>SUM(C132:H132)</f>
+        <f t="shared" si="2"/>
         <v>323</v>
       </c>
       <c r="J132" t="s">
@@ -10957,7 +10976,7 @@
         <v>55</v>
       </c>
       <c r="I133">
-        <f>SUM(C133:H133)</f>
+        <f t="shared" si="2"/>
         <v>325</v>
       </c>
       <c r="J133" t="s">
@@ -11008,7 +11027,7 @@
         <v>50</v>
       </c>
       <c r="I134">
-        <f>SUM(C134:H134)</f>
+        <f t="shared" si="2"/>
         <v>325</v>
       </c>
       <c r="J134" t="s">
@@ -11059,7 +11078,7 @@
         <v>70</v>
       </c>
       <c r="I135">
-        <f>SUM(C135:H135)</f>
+        <f t="shared" si="2"/>
         <v>325</v>
       </c>
       <c r="J135" t="s">
@@ -11110,7 +11129,7 @@
         <v>45</v>
       </c>
       <c r="I136">
-        <f>SUM(C136:H136)</f>
+        <f t="shared" si="2"/>
         <v>325</v>
       </c>
       <c r="J136" t="s">
@@ -11161,7 +11180,7 @@
         <v>45</v>
       </c>
       <c r="I137">
-        <f>SUM(C137:H137)</f>
+        <f t="shared" si="2"/>
         <v>325</v>
       </c>
       <c r="J137" t="s">
@@ -11212,7 +11231,7 @@
         <v>65</v>
       </c>
       <c r="I138">
-        <f>SUM(C138:H138)</f>
+        <f t="shared" si="2"/>
         <v>325</v>
       </c>
       <c r="J138" t="s">
@@ -11263,7 +11282,7 @@
         <v>65</v>
       </c>
       <c r="I139">
-        <f>SUM(C139:H139)</f>
+        <f t="shared" si="2"/>
         <v>325</v>
       </c>
       <c r="J139" t="s">
@@ -11314,7 +11333,7 @@
         <v>65</v>
       </c>
       <c r="I140">
-        <f>SUM(C140:H140)</f>
+        <f t="shared" si="2"/>
         <v>325</v>
       </c>
       <c r="J140" t="s">
@@ -11365,7 +11384,7 @@
         <v>65</v>
       </c>
       <c r="I141">
-        <f>SUM(C141:H141)</f>
+        <f t="shared" si="2"/>
         <v>325</v>
       </c>
       <c r="J141" t="s">
@@ -11416,7 +11435,7 @@
         <v>65</v>
       </c>
       <c r="I142">
-        <f>SUM(C142:H142)</f>
+        <f t="shared" si="2"/>
         <v>325</v>
       </c>
       <c r="J142" t="s">
@@ -11467,7 +11486,7 @@
         <v>65</v>
       </c>
       <c r="I143">
-        <f>SUM(C143:H143)</f>
+        <f t="shared" si="2"/>
         <v>325</v>
       </c>
       <c r="J143" t="s">
@@ -11518,7 +11537,7 @@
         <v>65</v>
       </c>
       <c r="I144">
-        <f>SUM(C144:H144)</f>
+        <f t="shared" si="2"/>
         <v>325</v>
       </c>
       <c r="J144" t="s">
@@ -11569,7 +11588,7 @@
         <v>50</v>
       </c>
       <c r="I145">
-        <f>SUM(C145:H145)</f>
+        <f t="shared" si="2"/>
         <v>325</v>
       </c>
       <c r="J145" t="s">
@@ -11620,7 +11639,7 @@
         <v>25</v>
       </c>
       <c r="I146">
-        <f>SUM(C146:H146)</f>
+        <f t="shared" si="2"/>
         <v>325</v>
       </c>
       <c r="J146" t="s">
@@ -11671,7 +11690,7 @@
         <v>62</v>
       </c>
       <c r="I147">
-        <f>SUM(C147:H147)</f>
+        <f t="shared" si="2"/>
         <v>325</v>
       </c>
       <c r="J147" t="s">
@@ -11722,7 +11741,7 @@
         <v>62</v>
       </c>
       <c r="I148">
-        <f>SUM(C148:H148)</f>
+        <f t="shared" si="2"/>
         <v>325</v>
       </c>
       <c r="J148" t="s">
@@ -11773,7 +11792,7 @@
         <v>90</v>
       </c>
       <c r="I149">
-        <f>SUM(C149:H149)</f>
+        <f t="shared" si="2"/>
         <v>328</v>
       </c>
       <c r="J149" t="s">
@@ -11824,7 +11843,7 @@
         <v>41</v>
       </c>
       <c r="I150">
-        <f>SUM(C150:H150)</f>
+        <f t="shared" si="2"/>
         <v>329</v>
       </c>
       <c r="J150" t="s">
@@ -11875,7 +11894,7 @@
         <v>55</v>
       </c>
       <c r="I151">
-        <f>SUM(C151:H151)</f>
+        <f t="shared" si="2"/>
         <v>330</v>
       </c>
       <c r="J151" t="s">
@@ -11926,7 +11945,7 @@
         <v>55</v>
       </c>
       <c r="I152">
-        <f>SUM(C152:H152)</f>
+        <f t="shared" si="2"/>
         <v>330</v>
       </c>
       <c r="J152" t="s">
@@ -11977,7 +11996,7 @@
         <v>55</v>
       </c>
       <c r="I153">
-        <f>SUM(C153:H153)</f>
+        <f t="shared" si="2"/>
         <v>330</v>
       </c>
       <c r="J153" t="s">
@@ -12028,7 +12047,7 @@
         <v>55</v>
       </c>
       <c r="I154">
-        <f>SUM(C154:H154)</f>
+        <f t="shared" si="2"/>
         <v>330</v>
       </c>
       <c r="J154" t="s">
@@ -12079,7 +12098,7 @@
         <v>56</v>
       </c>
       <c r="I155">
-        <f>SUM(C155:H155)</f>
+        <f t="shared" si="2"/>
         <v>330</v>
       </c>
       <c r="J155" t="s">
@@ -12130,7 +12149,7 @@
         <v>50</v>
       </c>
       <c r="I156">
-        <f>SUM(C156:H156)</f>
+        <f t="shared" si="2"/>
         <v>330</v>
       </c>
       <c r="J156" t="s">
@@ -12181,7 +12200,7 @@
         <v>45</v>
       </c>
       <c r="I157">
-        <f>SUM(C157:H157)</f>
+        <f t="shared" si="2"/>
         <v>330</v>
       </c>
       <c r="J157" t="s">
@@ -12232,7 +12251,7 @@
         <v>50</v>
       </c>
       <c r="I158">
-        <f>SUM(C158:H158)</f>
+        <f t="shared" si="2"/>
         <v>330</v>
       </c>
       <c r="J158" t="s">
@@ -12257,7 +12276,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="159" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>620</v>
       </c>
@@ -12283,7 +12302,7 @@
         <v>40</v>
       </c>
       <c r="I159">
-        <f>SUM(C159:H159)</f>
+        <f t="shared" si="2"/>
         <v>330</v>
       </c>
       <c r="J159" t="s">
@@ -12305,7 +12324,7 @@
         <v>25</v>
       </c>
       <c r="P159" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="160" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
@@ -12334,7 +12353,7 @@
         <v>40</v>
       </c>
       <c r="I160">
-        <f>SUM(C160:H160)</f>
+        <f t="shared" si="2"/>
         <v>330</v>
       </c>
       <c r="J160" t="s">
@@ -12385,7 +12404,7 @@
         <v>80</v>
       </c>
       <c r="I161">
-        <f>SUM(C161:H161)</f>
+        <f t="shared" si="2"/>
         <v>330</v>
       </c>
       <c r="J161" t="s">
@@ -12436,7 +12455,7 @@
         <v>65</v>
       </c>
       <c r="I162">
-        <f>SUM(C162:H162)</f>
+        <f t="shared" si="2"/>
         <v>330</v>
       </c>
       <c r="J162" t="s">
@@ -12487,7 +12506,7 @@
         <v>30</v>
       </c>
       <c r="I163">
-        <f>SUM(C163:H163)</f>
+        <f t="shared" si="2"/>
         <v>330</v>
       </c>
       <c r="J163" t="s">
@@ -12538,7 +12557,7 @@
         <v>42</v>
       </c>
       <c r="I164">
-        <f>SUM(C164:H164)</f>
+        <f t="shared" si="2"/>
         <v>330</v>
       </c>
       <c r="J164" t="s">
@@ -12589,7 +12608,7 @@
         <v>55</v>
       </c>
       <c r="I165">
-        <f>SUM(C165:H165)</f>
+        <f t="shared" si="2"/>
         <v>330</v>
       </c>
       <c r="J165" t="s">
@@ -12640,7 +12659,7 @@
         <v>61</v>
       </c>
       <c r="I166">
-        <f>SUM(C166:H166)</f>
+        <f t="shared" si="2"/>
         <v>330</v>
       </c>
       <c r="J166" t="s">
@@ -12691,7 +12710,7 @@
         <v>60</v>
       </c>
       <c r="I167">
-        <f>SUM(C167:H167)</f>
+        <f t="shared" si="2"/>
         <v>334</v>
       </c>
       <c r="J167" t="s">
@@ -12742,7 +12761,7 @@
         <v>100</v>
       </c>
       <c r="I168">
-        <f>SUM(C168:H168)</f>
+        <f t="shared" si="2"/>
         <v>335</v>
       </c>
       <c r="J168" t="s">
@@ -12793,7 +12812,7 @@
         <v>40</v>
       </c>
       <c r="I169">
-        <f>SUM(C169:H169)</f>
+        <f t="shared" si="2"/>
         <v>335</v>
       </c>
       <c r="J169" t="s">
@@ -12844,7 +12863,7 @@
         <v>55</v>
       </c>
       <c r="I170">
-        <f>SUM(C170:H170)</f>
+        <f t="shared" si="2"/>
         <v>340</v>
       </c>
       <c r="J170" t="s">
@@ -12895,7 +12914,7 @@
         <v>45</v>
       </c>
       <c r="I171">
-        <f>SUM(C171:H171)</f>
+        <f t="shared" si="2"/>
         <v>340</v>
       </c>
       <c r="J171" t="s">
@@ -12946,7 +12965,7 @@
         <v>65</v>
       </c>
       <c r="I172">
-        <f>SUM(C172:H172)</f>
+        <f t="shared" si="2"/>
         <v>340</v>
       </c>
       <c r="J172" t="s">
@@ -12997,7 +13016,7 @@
         <v>70</v>
       </c>
       <c r="I173">
-        <f>SUM(C173:H173)</f>
+        <f t="shared" si="2"/>
         <v>340</v>
       </c>
       <c r="J173" t="s">
@@ -13048,7 +13067,7 @@
         <v>40</v>
       </c>
       <c r="I174">
-        <f>SUM(C174:H174)</f>
+        <f t="shared" si="2"/>
         <v>340</v>
       </c>
       <c r="J174" t="s">
@@ -13099,7 +13118,7 @@
         <v>50</v>
       </c>
       <c r="I175">
-        <f>SUM(C175:H175)</f>
+        <f t="shared" si="2"/>
         <v>340</v>
       </c>
       <c r="J175" t="s">
@@ -13150,7 +13169,7 @@
         <v>40</v>
       </c>
       <c r="I176">
-        <f>SUM(C176:H176)</f>
+        <f t="shared" si="2"/>
         <v>340</v>
       </c>
       <c r="J176" t="s">
@@ -13201,7 +13220,7 @@
         <v>30</v>
       </c>
       <c r="I177">
-        <f>SUM(C177:H177)</f>
+        <f t="shared" si="2"/>
         <v>345</v>
       </c>
       <c r="J177" t="s">
@@ -13252,7 +13271,7 @@
         <v>65</v>
       </c>
       <c r="I178">
-        <f>SUM(C178:H178)</f>
+        <f t="shared" si="2"/>
         <v>345</v>
       </c>
       <c r="J178" t="s">
@@ -13303,7 +13322,7 @@
         <v>55</v>
       </c>
       <c r="I179">
-        <f>SUM(C179:H179)</f>
+        <f t="shared" si="2"/>
         <v>345</v>
       </c>
       <c r="J179" t="s">
@@ -13354,7 +13373,7 @@
         <v>55</v>
       </c>
       <c r="I180">
-        <f>SUM(C180:H180)</f>
+        <f t="shared" si="2"/>
         <v>345</v>
       </c>
       <c r="J180" t="s">
@@ -13379,7 +13398,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="181" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>1007</v>
       </c>
@@ -13405,7 +13424,7 @@
         <v>44</v>
       </c>
       <c r="I181">
-        <f>SUM(C181:H181)</f>
+        <f t="shared" si="2"/>
         <v>348</v>
       </c>
       <c r="J181" t="s">
@@ -13456,7 +13475,7 @@
         <v>50</v>
       </c>
       <c r="I182">
-        <f>SUM(C182:H182)</f>
+        <f t="shared" si="2"/>
         <v>349</v>
       </c>
       <c r="J182" t="s">
@@ -13507,7 +13526,7 @@
         <v>50</v>
       </c>
       <c r="I183">
-        <f>SUM(C183:H183)</f>
+        <f t="shared" si="2"/>
         <v>350</v>
       </c>
       <c r="J183" t="s">
@@ -13558,7 +13577,7 @@
         <v>50</v>
       </c>
       <c r="I184">
-        <f>SUM(C184:H184)</f>
+        <f t="shared" si="2"/>
         <v>350</v>
       </c>
       <c r="J184" t="s">
@@ -13609,7 +13628,7 @@
         <v>50</v>
       </c>
       <c r="I185">
-        <f>SUM(C185:H185)</f>
+        <f t="shared" si="2"/>
         <v>350</v>
       </c>
       <c r="J185" t="s">
@@ -13634,7 +13653,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="186" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>976</v>
       </c>
@@ -13660,7 +13679,7 @@
         <v>30</v>
       </c>
       <c r="I186">
-        <f>SUM(C186:H186)</f>
+        <f t="shared" si="2"/>
         <v>350</v>
       </c>
       <c r="J186" t="s">
@@ -13682,10 +13701,10 @@
         <v>30</v>
       </c>
       <c r="P186" t="s">
-        <v>1098</v>
-      </c>
-    </row>
-    <row r="187" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="187" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>980</v>
       </c>
@@ -13711,7 +13730,7 @@
         <v>88</v>
       </c>
       <c r="I187">
-        <f>SUM(C187:H187)</f>
+        <f t="shared" si="2"/>
         <v>350</v>
       </c>
       <c r="J187" t="s">
@@ -13733,7 +13752,7 @@
         <v>30</v>
       </c>
       <c r="P187" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="188" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
@@ -13762,7 +13781,7 @@
         <v>55</v>
       </c>
       <c r="I188">
-        <f>SUM(C188:H188)</f>
+        <f t="shared" si="2"/>
         <v>355</v>
       </c>
       <c r="J188" t="s">
@@ -13813,7 +13832,7 @@
         <v>45</v>
       </c>
       <c r="I189">
-        <f>SUM(C189:H189)</f>
+        <f t="shared" si="2"/>
         <v>355</v>
       </c>
       <c r="J189" t="s">
@@ -13864,7 +13883,7 @@
         <v>87</v>
       </c>
       <c r="I190">
-        <f>SUM(C190:H190)</f>
+        <f t="shared" si="2"/>
         <v>355</v>
       </c>
       <c r="J190" t="s">
@@ -13915,7 +13934,7 @@
         <v>50</v>
       </c>
       <c r="I191">
-        <f>SUM(C191:H191)</f>
+        <f t="shared" si="2"/>
         <v>355</v>
       </c>
       <c r="J191" t="s">
@@ -13966,7 +13985,7 @@
         <v>55</v>
       </c>
       <c r="I192">
-        <f>SUM(C192:H192)</f>
+        <f t="shared" si="2"/>
         <v>360</v>
       </c>
       <c r="J192" t="s">
@@ -14017,7 +14036,7 @@
         <v>60</v>
       </c>
       <c r="I193">
-        <f>SUM(C193:H193)</f>
+        <f t="shared" si="2"/>
         <v>360</v>
       </c>
       <c r="J193" t="s">
@@ -14068,7 +14087,7 @@
         <v>30</v>
       </c>
       <c r="I194">
-        <f>SUM(C194:H194)</f>
+        <f t="shared" ref="I194:I257" si="3">SUM(C194:H194)</f>
         <v>361</v>
       </c>
       <c r="J194" t="s">
@@ -14119,7 +14138,7 @@
         <v>49</v>
       </c>
       <c r="I195">
-        <f>SUM(C195:H195)</f>
+        <f t="shared" si="3"/>
         <v>363</v>
       </c>
       <c r="J195" t="s">
@@ -14170,7 +14189,7 @@
         <v>55</v>
       </c>
       <c r="I196">
-        <f>SUM(C196:H196)</f>
+        <f t="shared" si="3"/>
         <v>365</v>
       </c>
       <c r="J196" t="s">
@@ -14221,7 +14240,7 @@
         <v>55</v>
       </c>
       <c r="I197">
-        <f>SUM(C197:H197)</f>
+        <f t="shared" si="3"/>
         <v>365</v>
       </c>
       <c r="J197" t="s">
@@ -14272,7 +14291,7 @@
         <v>55</v>
       </c>
       <c r="I198">
-        <f>SUM(C198:H198)</f>
+        <f t="shared" si="3"/>
         <v>365</v>
       </c>
       <c r="J198" t="s">
@@ -14323,7 +14342,7 @@
         <v>60</v>
       </c>
       <c r="I199">
-        <f>SUM(C199:H199)</f>
+        <f t="shared" si="3"/>
         <v>365</v>
       </c>
       <c r="J199" t="s">
@@ -14374,7 +14393,7 @@
         <v>45</v>
       </c>
       <c r="I200">
-        <f>SUM(C200:H200)</f>
+        <f t="shared" si="3"/>
         <v>375</v>
       </c>
       <c r="J200" t="s">
@@ -14425,7 +14444,7 @@
         <v>62</v>
       </c>
       <c r="I201">
-        <f>SUM(C201:H201)</f>
+        <f t="shared" si="3"/>
         <v>377</v>
       </c>
       <c r="J201" t="s">
@@ -14476,7 +14495,7 @@
         <v>51</v>
       </c>
       <c r="I202">
-        <f>SUM(C202:H202)</f>
+        <f t="shared" si="3"/>
         <v>384</v>
       </c>
       <c r="J202" t="s">
@@ -14527,7 +14546,7 @@
         <v>80</v>
       </c>
       <c r="I203">
-        <f>SUM(C203:H203)</f>
+        <f t="shared" si="3"/>
         <v>385</v>
       </c>
       <c r="J203" t="s">
@@ -14578,7 +14597,7 @@
         <v>50</v>
       </c>
       <c r="I204">
-        <f>SUM(C204:H204)</f>
+        <f t="shared" si="3"/>
         <v>385</v>
       </c>
       <c r="J204" t="s">
@@ -14629,7 +14648,7 @@
         <v>80</v>
       </c>
       <c r="I205">
-        <f>SUM(C205:H205)</f>
+        <f t="shared" si="3"/>
         <v>385</v>
       </c>
       <c r="J205" t="s">
@@ -14680,7 +14699,7 @@
         <v>45</v>
       </c>
       <c r="I206">
-        <f>SUM(C206:H206)</f>
+        <f t="shared" si="3"/>
         <v>385</v>
       </c>
       <c r="J206" t="s">
@@ -14731,7 +14750,7 @@
         <v>50</v>
       </c>
       <c r="I207">
-        <f>SUM(C207:H207)</f>
+        <f t="shared" si="3"/>
         <v>385</v>
       </c>
       <c r="J207" t="s">
@@ -14782,7 +14801,7 @@
         <v>50</v>
       </c>
       <c r="I208">
-        <f>SUM(C208:H208)</f>
+        <f t="shared" si="3"/>
         <v>385</v>
       </c>
       <c r="J208" t="s">
@@ -14833,7 +14852,7 @@
         <v>90</v>
       </c>
       <c r="I209">
-        <f>SUM(C209:H209)</f>
+        <f t="shared" si="3"/>
         <v>385</v>
       </c>
       <c r="J209" t="s">
@@ -14884,7 +14903,7 @@
         <v>45</v>
       </c>
       <c r="I210">
-        <f>SUM(C210:H210)</f>
+        <f t="shared" si="3"/>
         <v>390</v>
       </c>
       <c r="J210" t="s">
@@ -14935,7 +14954,7 @@
         <v>45</v>
       </c>
       <c r="I211">
-        <f>SUM(C211:H211)</f>
+        <f t="shared" si="3"/>
         <v>390</v>
       </c>
       <c r="J211" t="s">
@@ -14986,7 +15005,7 @@
         <v>45</v>
       </c>
       <c r="I212">
-        <f>SUM(C212:H212)</f>
+        <f t="shared" si="3"/>
         <v>390</v>
       </c>
       <c r="J212" t="s">
@@ -15037,7 +15056,7 @@
         <v>45</v>
       </c>
       <c r="I213">
-        <f>SUM(C213:H213)</f>
+        <f t="shared" si="3"/>
         <v>390</v>
       </c>
       <c r="J213" t="s">
@@ -15088,7 +15107,7 @@
         <v>45</v>
       </c>
       <c r="I214">
-        <f>SUM(C214:H214)</f>
+        <f t="shared" si="3"/>
         <v>390</v>
       </c>
       <c r="J214" t="s">
@@ -15139,7 +15158,7 @@
         <v>75</v>
       </c>
       <c r="I215">
-        <f>SUM(C215:H215)</f>
+        <f t="shared" si="3"/>
         <v>395</v>
       </c>
       <c r="J215" t="s">
@@ -15190,7 +15209,7 @@
         <v>75</v>
       </c>
       <c r="I216">
-        <f>SUM(C216:H216)</f>
+        <f t="shared" si="3"/>
         <v>395</v>
       </c>
       <c r="J216" t="s">
@@ -15241,7 +15260,7 @@
         <v>75</v>
       </c>
       <c r="I217">
-        <f>SUM(C217:H217)</f>
+        <f t="shared" si="3"/>
         <v>395</v>
       </c>
       <c r="J217" t="s">
@@ -15292,7 +15311,7 @@
         <v>75</v>
       </c>
       <c r="I218">
-        <f>SUM(C218:H218)</f>
+        <f t="shared" si="3"/>
         <v>400</v>
       </c>
       <c r="J218" t="s">
@@ -15343,7 +15362,7 @@
         <v>75</v>
       </c>
       <c r="I219">
-        <f>SUM(C219:H219)</f>
+        <f t="shared" si="3"/>
         <v>400</v>
       </c>
       <c r="J219" t="s">
@@ -15394,7 +15413,7 @@
         <v>70</v>
       </c>
       <c r="I220">
-        <f>SUM(C220:H220)</f>
+        <f t="shared" si="3"/>
         <v>400</v>
       </c>
       <c r="J220" t="s">
@@ -15445,7 +15464,7 @@
         <v>70</v>
       </c>
       <c r="I221">
-        <f>SUM(C221:H221)</f>
+        <f t="shared" si="3"/>
         <v>400</v>
       </c>
       <c r="J221" t="s">
@@ -15496,7 +15515,7 @@
         <v>80</v>
       </c>
       <c r="I222">
-        <f>SUM(C222:H222)</f>
+        <f t="shared" si="3"/>
         <v>400</v>
       </c>
       <c r="J222" t="s">
@@ -15521,7 +15540,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="223" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>789</v>
       </c>
@@ -15547,7 +15566,7 @@
         <v>35</v>
       </c>
       <c r="I223">
-        <f>SUM(C223:H223)</f>
+        <f t="shared" si="3"/>
         <v>400</v>
       </c>
       <c r="J223" t="s">
@@ -15598,7 +15617,7 @@
         <v>65</v>
       </c>
       <c r="I224">
-        <f>SUM(C224:H224)</f>
+        <f t="shared" si="3"/>
         <v>405</v>
       </c>
       <c r="J224" t="s">
@@ -15649,7 +15668,7 @@
         <v>80</v>
       </c>
       <c r="I225">
-        <f>SUM(C225:H225)</f>
+        <f t="shared" si="3"/>
         <v>405</v>
       </c>
       <c r="J225" t="s">
@@ -15700,7 +15719,7 @@
         <v>60</v>
       </c>
       <c r="I226">
-        <f>SUM(C226:H226)</f>
+        <f t="shared" si="3"/>
         <v>405</v>
       </c>
       <c r="J226" t="s">
@@ -15751,7 +15770,7 @@
         <v>60</v>
       </c>
       <c r="I227">
-        <f>SUM(C227:H227)</f>
+        <f t="shared" si="3"/>
         <v>405</v>
       </c>
       <c r="J227" t="s">
@@ -15802,7 +15821,7 @@
         <v>55</v>
       </c>
       <c r="I228">
-        <f>SUM(C228:H228)</f>
+        <f t="shared" si="3"/>
         <v>405</v>
       </c>
       <c r="J228" t="s">
@@ -15853,7 +15872,7 @@
         <v>55</v>
       </c>
       <c r="I229">
-        <f>SUM(C229:H229)</f>
+        <f t="shared" si="3"/>
         <v>405</v>
       </c>
       <c r="J229" t="s">
@@ -15904,7 +15923,7 @@
         <v>80</v>
       </c>
       <c r="I230">
-        <f>SUM(C230:H230)</f>
+        <f t="shared" si="3"/>
         <v>405</v>
       </c>
       <c r="J230" t="s">
@@ -15955,7 +15974,7 @@
         <v>80</v>
       </c>
       <c r="I231">
-        <f>SUM(C231:H231)</f>
+        <f t="shared" si="3"/>
         <v>405</v>
       </c>
       <c r="J231" t="s">
@@ -16006,7 +16025,7 @@
         <v>65</v>
       </c>
       <c r="I232">
-        <f>SUM(C232:H232)</f>
+        <f t="shared" si="3"/>
         <v>405</v>
       </c>
       <c r="J232" t="s">
@@ -16057,7 +16076,7 @@
         <v>65</v>
       </c>
       <c r="I233">
-        <f>SUM(C233:H233)</f>
+        <f t="shared" si="3"/>
         <v>405</v>
       </c>
       <c r="J233" t="s">
@@ -16108,7 +16127,7 @@
         <v>63</v>
       </c>
       <c r="I234">
-        <f>SUM(C234:H234)</f>
+        <f t="shared" si="3"/>
         <v>405</v>
       </c>
       <c r="J234" t="s">
@@ -16159,7 +16178,7 @@
         <v>42</v>
       </c>
       <c r="I235">
-        <f>SUM(C235:H235)</f>
+        <f t="shared" si="3"/>
         <v>405</v>
       </c>
       <c r="J235" t="s">
@@ -16210,7 +16229,7 @@
         <v>58</v>
       </c>
       <c r="I236">
-        <f>SUM(C236:H236)</f>
+        <f t="shared" si="3"/>
         <v>405</v>
       </c>
       <c r="J236" t="s">
@@ -16261,7 +16280,7 @@
         <v>65</v>
       </c>
       <c r="I237">
-        <f>SUM(C237:H237)</f>
+        <f t="shared" si="3"/>
         <v>405</v>
       </c>
       <c r="J237" t="s">
@@ -16312,7 +16331,7 @@
         <v>60</v>
       </c>
       <c r="I238">
-        <f>SUM(C238:H238)</f>
+        <f t="shared" si="3"/>
         <v>405</v>
       </c>
       <c r="J238" t="s">
@@ -16363,7 +16382,7 @@
         <v>70</v>
       </c>
       <c r="I239">
-        <f>SUM(C239:H239)</f>
+        <f t="shared" si="3"/>
         <v>405</v>
       </c>
       <c r="J239" t="s">
@@ -16414,7 +16433,7 @@
         <v>75</v>
       </c>
       <c r="I240">
-        <f>SUM(C240:H240)</f>
+        <f t="shared" si="3"/>
         <v>405</v>
       </c>
       <c r="J240" t="s">
@@ -16465,7 +16484,7 @@
         <v>85</v>
       </c>
       <c r="I241">
-        <f>SUM(C241:H241)</f>
+        <f t="shared" si="3"/>
         <v>405</v>
       </c>
       <c r="J241" t="s">
@@ -16516,7 +16535,7 @@
         <v>65</v>
       </c>
       <c r="I242">
-        <f>SUM(C242:H242)</f>
+        <f t="shared" si="3"/>
         <v>405</v>
       </c>
       <c r="J242" t="s">
@@ -16567,7 +16586,7 @@
         <v>52</v>
       </c>
       <c r="I243">
-        <f>SUM(C243:H243)</f>
+        <f t="shared" si="3"/>
         <v>405</v>
       </c>
       <c r="J243" t="s">
@@ -16618,7 +16637,7 @@
         <v>76</v>
       </c>
       <c r="I244">
-        <f>SUM(C244:H244)</f>
+        <f t="shared" si="3"/>
         <v>405</v>
       </c>
       <c r="J244" t="s">
@@ -16669,7 +16688,7 @@
         <v>90</v>
       </c>
       <c r="I245">
-        <f>SUM(C245:H245)</f>
+        <f t="shared" si="3"/>
         <v>405</v>
       </c>
       <c r="J245" t="s">
@@ -16720,7 +16739,7 @@
         <v>65</v>
       </c>
       <c r="I246">
-        <f>SUM(C246:H246)</f>
+        <f t="shared" si="3"/>
         <v>410</v>
       </c>
       <c r="J246" t="s">
@@ -16771,7 +16790,7 @@
         <v>65</v>
       </c>
       <c r="I247">
-        <f>SUM(C247:H247)</f>
+        <f t="shared" si="3"/>
         <v>410</v>
       </c>
       <c r="J247" t="s">
@@ -16822,7 +16841,7 @@
         <v>65</v>
       </c>
       <c r="I248">
-        <f>SUM(C248:H248)</f>
+        <f t="shared" si="3"/>
         <v>410</v>
       </c>
       <c r="J248" t="s">
@@ -16873,7 +16892,7 @@
         <v>95</v>
       </c>
       <c r="I249">
-        <f>SUM(C249:H249)</f>
+        <f t="shared" si="3"/>
         <v>410</v>
       </c>
       <c r="J249" t="s">
@@ -16924,7 +16943,7 @@
         <v>100</v>
       </c>
       <c r="I250">
-        <f>SUM(C250:H250)</f>
+        <f t="shared" si="3"/>
         <v>410</v>
       </c>
       <c r="J250" t="s">
@@ -16975,7 +16994,7 @@
         <v>70</v>
       </c>
       <c r="I251">
-        <f>SUM(C251:H251)</f>
+        <f t="shared" si="3"/>
         <v>410</v>
       </c>
       <c r="J251" t="s">
@@ -17026,7 +17045,7 @@
         <v>70</v>
       </c>
       <c r="I252">
-        <f>SUM(C252:H252)</f>
+        <f t="shared" si="3"/>
         <v>410</v>
       </c>
       <c r="J252" t="s">
@@ -17051,7 +17070,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="253" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>965</v>
       </c>
@@ -17077,7 +17096,7 @@
         <v>60</v>
       </c>
       <c r="I253">
-        <f>SUM(C253:H253)</f>
+        <f t="shared" si="3"/>
         <v>410</v>
       </c>
       <c r="J253" t="s">
@@ -17099,7 +17118,7 @@
         <v>0</v>
       </c>
       <c r="P253" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="254" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
@@ -17128,7 +17147,7 @@
         <v>55</v>
       </c>
       <c r="I254">
-        <f>SUM(C254:H254)</f>
+        <f t="shared" si="3"/>
         <v>410</v>
       </c>
       <c r="J254" t="s">
@@ -17179,7 +17198,7 @@
         <v>42</v>
       </c>
       <c r="I255">
-        <f>SUM(C255:H255)</f>
+        <f t="shared" si="3"/>
         <v>411</v>
       </c>
       <c r="J255" t="s">
@@ -17230,7 +17249,7 @@
         <v>70</v>
       </c>
       <c r="I256">
-        <f>SUM(C256:H256)</f>
+        <f t="shared" si="3"/>
         <v>413</v>
       </c>
       <c r="J256" t="s">
@@ -17281,7 +17300,7 @@
         <v>80</v>
       </c>
       <c r="I257">
-        <f>SUM(C257:H257)</f>
+        <f t="shared" si="3"/>
         <v>413</v>
       </c>
       <c r="J257" t="s">
@@ -17332,7 +17351,7 @@
         <v>70</v>
       </c>
       <c r="I258">
-        <f>SUM(C258:H258)</f>
+        <f t="shared" ref="I258:I321" si="4">SUM(C258:H258)</f>
         <v>420</v>
       </c>
       <c r="J258" t="s">
@@ -17383,7 +17402,7 @@
         <v>110</v>
       </c>
       <c r="I259">
-        <f>SUM(C259:H259)</f>
+        <f t="shared" si="4"/>
         <v>420</v>
       </c>
       <c r="J259" t="s">
@@ -17434,7 +17453,7 @@
         <v>70</v>
       </c>
       <c r="I260">
-        <f>SUM(C260:H260)</f>
+        <f t="shared" si="4"/>
         <v>420</v>
       </c>
       <c r="J260" t="s">
@@ -17485,7 +17504,7 @@
         <v>70</v>
       </c>
       <c r="I261">
-        <f>SUM(C261:H261)</f>
+        <f t="shared" si="4"/>
         <v>420</v>
       </c>
       <c r="J261" t="s">
@@ -17536,7 +17555,7 @@
         <v>70</v>
       </c>
       <c r="I262">
-        <f>SUM(C262:H262)</f>
+        <f t="shared" si="4"/>
         <v>420</v>
       </c>
       <c r="J262" t="s">
@@ -17587,7 +17606,7 @@
         <v>70</v>
       </c>
       <c r="I263">
-        <f>SUM(C263:H263)</f>
+        <f t="shared" si="4"/>
         <v>420</v>
       </c>
       <c r="J263" t="s">
@@ -17638,7 +17657,7 @@
         <v>50</v>
       </c>
       <c r="I264">
-        <f>SUM(C264:H264)</f>
+        <f t="shared" si="4"/>
         <v>420</v>
       </c>
       <c r="J264" t="s">
@@ -17689,7 +17708,7 @@
         <v>80</v>
       </c>
       <c r="I265">
-        <f>SUM(C265:H265)</f>
+        <f t="shared" si="4"/>
         <v>420</v>
       </c>
       <c r="J265" t="s">
@@ -17740,7 +17759,7 @@
         <v>105</v>
       </c>
       <c r="I266">
-        <f>SUM(C266:H266)</f>
+        <f t="shared" si="4"/>
         <v>424</v>
       </c>
       <c r="J266" t="s">
@@ -17791,7 +17810,7 @@
         <v>85</v>
       </c>
       <c r="I267">
-        <f>SUM(C267:H267)</f>
+        <f t="shared" si="4"/>
         <v>424</v>
       </c>
       <c r="J267" t="s">
@@ -17842,7 +17861,7 @@
         <v>95</v>
       </c>
       <c r="I268">
-        <f>SUM(C268:H268)</f>
+        <f t="shared" si="4"/>
         <v>424</v>
       </c>
       <c r="J268" t="s">
@@ -17893,7 +17912,7 @@
         <v>60</v>
       </c>
       <c r="I269">
-        <f>SUM(C269:H269)</f>
+        <f t="shared" si="4"/>
         <v>425</v>
       </c>
       <c r="J269" t="s">
@@ -17944,7 +17963,7 @@
         <v>105</v>
       </c>
       <c r="I270">
-        <f>SUM(C270:H270)</f>
+        <f t="shared" si="4"/>
         <v>425</v>
       </c>
       <c r="J270" t="s">
@@ -17995,7 +18014,7 @@
         <v>75</v>
       </c>
       <c r="I271">
-        <f>SUM(C271:H271)</f>
+        <f t="shared" si="4"/>
         <v>425</v>
       </c>
       <c r="J271" t="s">
@@ -18046,7 +18065,7 @@
         <v>70</v>
       </c>
       <c r="I272">
-        <f>SUM(C272:H272)</f>
+        <f t="shared" si="4"/>
         <v>425</v>
       </c>
       <c r="J272" t="s">
@@ -18097,7 +18116,7 @@
         <v>75</v>
       </c>
       <c r="I273">
-        <f>SUM(C273:H273)</f>
+        <f t="shared" si="4"/>
         <v>430</v>
       </c>
       <c r="J273" t="s">
@@ -18148,7 +18167,7 @@
         <v>75</v>
       </c>
       <c r="I274">
-        <f>SUM(C274:H274)</f>
+        <f t="shared" si="4"/>
         <v>430</v>
       </c>
       <c r="J274" t="s">
@@ -18199,7 +18218,7 @@
         <v>65</v>
       </c>
       <c r="I275">
-        <f>SUM(C275:H275)</f>
+        <f t="shared" si="4"/>
         <v>430</v>
       </c>
       <c r="J275" t="s">
@@ -18250,7 +18269,7 @@
         <v>75</v>
       </c>
       <c r="I276">
-        <f>SUM(C276:H276)</f>
+        <f t="shared" si="4"/>
         <v>430</v>
       </c>
       <c r="J276" t="s">
@@ -18301,7 +18320,7 @@
         <v>75</v>
       </c>
       <c r="I277">
-        <f>SUM(C277:H277)</f>
+        <f t="shared" si="4"/>
         <v>430</v>
       </c>
       <c r="J277" t="s">
@@ -18352,7 +18371,7 @@
         <v>75</v>
       </c>
       <c r="I278">
-        <f>SUM(C278:H278)</f>
+        <f t="shared" si="4"/>
         <v>430</v>
       </c>
       <c r="J278" t="s">
@@ -18403,7 +18422,7 @@
         <v>75</v>
       </c>
       <c r="I279">
-        <f>SUM(C279:H279)</f>
+        <f t="shared" si="4"/>
         <v>430</v>
       </c>
       <c r="J279" t="s">
@@ -18454,7 +18473,7 @@
         <v>50</v>
       </c>
       <c r="I280">
-        <f>SUM(C280:H280)</f>
+        <f t="shared" si="4"/>
         <v>430</v>
       </c>
       <c r="J280" t="s">
@@ -18505,7 +18524,7 @@
         <v>85</v>
       </c>
       <c r="I281">
-        <f>SUM(C281:H281)</f>
+        <f t="shared" si="4"/>
         <v>435</v>
       </c>
       <c r="J281" t="s">
@@ -18556,7 +18575,7 @@
         <v>85</v>
       </c>
       <c r="I282">
-        <f>SUM(C282:H282)</f>
+        <f t="shared" si="4"/>
         <v>435</v>
       </c>
       <c r="J282" t="s">
@@ -18607,7 +18626,7 @@
         <v>45</v>
       </c>
       <c r="I283">
-        <f>SUM(C283:H283)</f>
+        <f t="shared" si="4"/>
         <v>440</v>
       </c>
       <c r="J283" t="s">
@@ -18658,7 +18677,7 @@
         <v>55</v>
       </c>
       <c r="I284">
-        <f>SUM(C284:H284)</f>
+        <f t="shared" si="4"/>
         <v>440</v>
       </c>
       <c r="J284" t="s">
@@ -18709,7 +18728,7 @@
         <v>55</v>
       </c>
       <c r="I285">
-        <f>SUM(C285:H285)</f>
+        <f t="shared" si="4"/>
         <v>440</v>
       </c>
       <c r="J285" t="s">
@@ -18760,7 +18779,7 @@
         <v>75</v>
       </c>
       <c r="I286">
-        <f>SUM(C286:H286)</f>
+        <f t="shared" si="4"/>
         <v>440</v>
       </c>
       <c r="J286" t="s">
@@ -18811,7 +18830,7 @@
         <v>120</v>
       </c>
       <c r="I287">
-        <f>SUM(C287:H287)</f>
+        <f t="shared" si="4"/>
         <v>440</v>
       </c>
       <c r="J287" t="s">
@@ -18862,7 +18881,7 @@
         <v>77</v>
       </c>
       <c r="I288">
-        <f>SUM(C288:H288)</f>
+        <f t="shared" si="4"/>
         <v>440</v>
       </c>
       <c r="J288" t="s">
@@ -18913,7 +18932,7 @@
         <v>96</v>
       </c>
       <c r="I289">
-        <f>SUM(C289:H289)</f>
+        <f t="shared" si="4"/>
         <v>442</v>
       </c>
       <c r="J289" t="s">
@@ -18964,7 +18983,7 @@
         <v>70</v>
       </c>
       <c r="I290">
-        <f>SUM(C290:H290)</f>
+        <f t="shared" si="4"/>
         <v>450</v>
       </c>
       <c r="J290" t="s">
@@ -19015,7 +19034,7 @@
         <v>55</v>
       </c>
       <c r="I291">
-        <f>SUM(C291:H291)</f>
+        <f t="shared" si="4"/>
         <v>450</v>
       </c>
       <c r="J291" t="s">
@@ -19066,7 +19085,7 @@
         <v>65</v>
       </c>
       <c r="I292">
-        <f>SUM(C292:H292)</f>
+        <f t="shared" si="4"/>
         <v>450</v>
       </c>
       <c r="J292" t="s">
@@ -19117,7 +19136,7 @@
         <v>75</v>
       </c>
       <c r="I293">
-        <f>SUM(C293:H293)</f>
+        <f t="shared" si="4"/>
         <v>450</v>
       </c>
       <c r="J293" t="s">
@@ -19168,7 +19187,7 @@
         <v>65</v>
       </c>
       <c r="I294">
-        <f>SUM(C294:H294)</f>
+        <f t="shared" si="4"/>
         <v>450</v>
       </c>
       <c r="J294" t="s">
@@ -19219,7 +19238,7 @@
         <v>65</v>
       </c>
       <c r="I295">
-        <f>SUM(C295:H295)</f>
+        <f t="shared" si="4"/>
         <v>450</v>
       </c>
       <c r="J295" t="s">
@@ -19270,7 +19289,7 @@
         <v>70</v>
       </c>
       <c r="I296">
-        <f>SUM(C296:H296)</f>
+        <f t="shared" si="4"/>
         <v>450</v>
       </c>
       <c r="J296" t="s">
@@ -19321,7 +19340,7 @@
         <v>60</v>
       </c>
       <c r="I297">
-        <f>SUM(C297:H297)</f>
+        <f t="shared" si="4"/>
         <v>450</v>
       </c>
       <c r="J297" t="s">
@@ -19372,7 +19391,7 @@
         <v>78</v>
       </c>
       <c r="I298">
-        <f>SUM(C298:H298)</f>
+        <f t="shared" si="4"/>
         <v>450</v>
       </c>
       <c r="J298" t="s">
@@ -19423,7 +19442,7 @@
         <v>78</v>
       </c>
       <c r="I299">
-        <f>SUM(C299:H299)</f>
+        <f t="shared" si="4"/>
         <v>450</v>
       </c>
       <c r="J299" t="s">
@@ -19474,7 +19493,7 @@
         <v>59</v>
       </c>
       <c r="I300">
-        <f>SUM(C300:H300)</f>
+        <f t="shared" si="4"/>
         <v>452</v>
       </c>
       <c r="J300" t="s">
@@ -19525,7 +19544,7 @@
         <v>72</v>
       </c>
       <c r="I301">
-        <f>SUM(C301:H301)</f>
+        <f t="shared" si="4"/>
         <v>454</v>
       </c>
       <c r="J301" t="s">
@@ -19576,7 +19595,7 @@
         <v>95</v>
       </c>
       <c r="I302">
-        <f>SUM(C302:H302)</f>
+        <f t="shared" si="4"/>
         <v>455</v>
       </c>
       <c r="J302" t="s">
@@ -19627,7 +19646,7 @@
         <v>110</v>
       </c>
       <c r="I303">
-        <f>SUM(C303:H303)</f>
+        <f t="shared" si="4"/>
         <v>455</v>
       </c>
       <c r="J303" t="s">
@@ -19678,7 +19697,7 @@
         <v>110</v>
       </c>
       <c r="I304">
-        <f>SUM(C304:H304)</f>
+        <f t="shared" si="4"/>
         <v>455</v>
       </c>
       <c r="J304" t="s">
@@ -19729,7 +19748,7 @@
         <v>70</v>
       </c>
       <c r="I305">
-        <f>SUM(C305:H305)</f>
+        <f t="shared" si="4"/>
         <v>455</v>
       </c>
       <c r="J305" t="s">
@@ -19780,7 +19799,7 @@
         <v>110</v>
       </c>
       <c r="I306">
-        <f>SUM(C306:H306)</f>
+        <f t="shared" si="4"/>
         <v>455</v>
       </c>
       <c r="J306" t="s">
@@ -19831,7 +19850,7 @@
         <v>90</v>
       </c>
       <c r="I307">
-        <f>SUM(C307:H307)</f>
+        <f t="shared" si="4"/>
         <v>455</v>
       </c>
       <c r="J307" t="s">
@@ -19882,7 +19901,7 @@
         <v>60</v>
       </c>
       <c r="I308">
-        <f>SUM(C308:H308)</f>
+        <f t="shared" si="4"/>
         <v>458</v>
       </c>
       <c r="J308" t="s">
@@ -19933,7 +19952,7 @@
         <v>60</v>
       </c>
       <c r="I309">
-        <f>SUM(C309:H309)</f>
+        <f t="shared" si="4"/>
         <v>458</v>
       </c>
       <c r="J309" t="s">
@@ -19984,7 +20003,7 @@
         <v>120</v>
       </c>
       <c r="I310">
-        <f>SUM(C310:H310)</f>
+        <f t="shared" si="4"/>
         <v>460</v>
       </c>
       <c r="J310" t="s">
@@ -20009,7 +20028,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="311" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
         <v>595</v>
       </c>
@@ -20035,7 +20054,7 @@
         <v>100</v>
       </c>
       <c r="I311">
-        <f>SUM(C311:H311)</f>
+        <f t="shared" si="4"/>
         <v>460</v>
       </c>
       <c r="J311" t="s">
@@ -20057,7 +20076,7 @@
         <v>0</v>
       </c>
       <c r="P311" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="312" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
@@ -20086,7 +20105,7 @@
         <v>80</v>
       </c>
       <c r="I312">
-        <f>SUM(C312:H312)</f>
+        <f t="shared" si="4"/>
         <v>460</v>
       </c>
       <c r="J312" t="s">
@@ -20137,7 +20156,7 @@
         <v>80</v>
       </c>
       <c r="I313">
-        <f>SUM(C313:H313)</f>
+        <f t="shared" si="4"/>
         <v>460</v>
       </c>
       <c r="J313" t="s">
@@ -20188,7 +20207,7 @@
         <v>90</v>
       </c>
       <c r="I314">
-        <f>SUM(C314:H314)</f>
+        <f t="shared" si="4"/>
         <v>460</v>
       </c>
       <c r="J314" t="s">
@@ -20239,7 +20258,7 @@
         <v>90</v>
       </c>
       <c r="I315">
-        <f>SUM(C315:H315)</f>
+        <f t="shared" si="4"/>
         <v>460</v>
       </c>
       <c r="J315" t="s">
@@ -20290,7 +20309,7 @@
         <v>70</v>
       </c>
       <c r="I316">
-        <f>SUM(C316:H316)</f>
+        <f t="shared" si="4"/>
         <v>460</v>
       </c>
       <c r="J316" t="s">
@@ -20341,7 +20360,7 @@
         <v>70</v>
       </c>
       <c r="I317">
-        <f>SUM(C317:H317)</f>
+        <f t="shared" si="4"/>
         <v>460</v>
       </c>
       <c r="J317" t="s">
@@ -20392,7 +20411,7 @@
         <v>80</v>
       </c>
       <c r="I318">
-        <f>SUM(C318:H318)</f>
+        <f t="shared" si="4"/>
         <v>460</v>
       </c>
       <c r="J318" t="s">
@@ -20443,7 +20462,7 @@
         <v>85</v>
       </c>
       <c r="I319">
-        <f>SUM(C319:H319)</f>
+        <f t="shared" si="4"/>
         <v>460</v>
       </c>
       <c r="J319" t="s">
@@ -20494,7 +20513,7 @@
         <v>65</v>
       </c>
       <c r="I320">
-        <f>SUM(C320:H320)</f>
+        <f t="shared" si="4"/>
         <v>460</v>
       </c>
       <c r="J320" t="s">
@@ -20545,7 +20564,7 @@
         <v>87</v>
       </c>
       <c r="I321">
-        <f>SUM(C321:H321)</f>
+        <f t="shared" si="4"/>
         <v>460</v>
       </c>
       <c r="J321" t="s">
@@ -20596,7 +20615,7 @@
         <v>86</v>
       </c>
       <c r="I322">
-        <f>SUM(C322:H322)</f>
+        <f t="shared" ref="I322:I385" si="5">SUM(C322:H322)</f>
         <v>460</v>
       </c>
       <c r="J322" t="s">
@@ -20647,7 +20666,7 @@
         <v>65</v>
       </c>
       <c r="I323">
-        <f>SUM(C323:H323)</f>
+        <f t="shared" si="5"/>
         <v>465</v>
       </c>
       <c r="J323" t="s">
@@ -20698,7 +20717,7 @@
         <v>60</v>
       </c>
       <c r="I324">
-        <f>SUM(C324:H324)</f>
+        <f t="shared" si="5"/>
         <v>465</v>
       </c>
       <c r="J324" t="s">
@@ -20749,7 +20768,7 @@
         <v>100</v>
       </c>
       <c r="I325">
-        <f>SUM(C325:H325)</f>
+        <f t="shared" si="5"/>
         <v>465</v>
       </c>
       <c r="J325" t="s">
@@ -20800,7 +20819,7 @@
         <v>90</v>
       </c>
       <c r="I326">
-        <f>SUM(C326:H326)</f>
+        <f t="shared" si="5"/>
         <v>465</v>
       </c>
       <c r="J326" t="s">
@@ -20851,7 +20870,7 @@
         <v>90</v>
       </c>
       <c r="I327">
-        <f>SUM(C327:H327)</f>
+        <f t="shared" si="5"/>
         <v>465</v>
       </c>
       <c r="J327" t="s">
@@ -20902,7 +20921,7 @@
         <v>60</v>
       </c>
       <c r="I328">
-        <f>SUM(C328:H328)</f>
+        <f t="shared" si="5"/>
         <v>470</v>
       </c>
       <c r="J328" t="s">
@@ -20953,7 +20972,7 @@
         <v>85</v>
       </c>
       <c r="I329">
-        <f>SUM(C329:H329)</f>
+        <f t="shared" si="5"/>
         <v>470</v>
       </c>
       <c r="J329" t="s">
@@ -21004,7 +21023,7 @@
         <v>60</v>
       </c>
       <c r="I330">
-        <f>SUM(C330:H330)</f>
+        <f t="shared" si="5"/>
         <v>470</v>
       </c>
       <c r="J330" t="s">
@@ -21055,7 +21074,7 @@
         <v>110</v>
       </c>
       <c r="I331">
-        <f>SUM(C331:H331)</f>
+        <f t="shared" si="5"/>
         <v>470</v>
       </c>
       <c r="J331" t="s">
@@ -21106,7 +21125,7 @@
         <v>90</v>
       </c>
       <c r="I332">
-        <f>SUM(C332:H332)</f>
+        <f t="shared" si="5"/>
         <v>473</v>
       </c>
       <c r="J332" t="s">
@@ -21157,7 +21176,7 @@
         <v>95</v>
       </c>
       <c r="I333">
-        <f>SUM(C333:H333)</f>
+        <f t="shared" si="5"/>
         <v>475</v>
       </c>
       <c r="J333" t="s">
@@ -21208,7 +21227,7 @@
         <v>70</v>
       </c>
       <c r="I334">
-        <f>SUM(C334:H334)</f>
+        <f t="shared" si="5"/>
         <v>475</v>
       </c>
       <c r="J334" t="s">
@@ -21259,7 +21278,7 @@
         <v>100</v>
       </c>
       <c r="I335">
-        <f>SUM(C335:H335)</f>
+        <f t="shared" si="5"/>
         <v>475</v>
       </c>
       <c r="J335" t="s">
@@ -21310,7 +21329,7 @@
         <v>70</v>
       </c>
       <c r="I336">
-        <f>SUM(C336:H336)</f>
+        <f t="shared" si="5"/>
         <v>475</v>
       </c>
       <c r="J336" t="s">
@@ -21361,7 +21380,7 @@
         <v>65</v>
       </c>
       <c r="I337">
-        <f>SUM(C337:H337)</f>
+        <f t="shared" si="5"/>
         <v>475</v>
       </c>
       <c r="J337" t="s">
@@ -21412,7 +21431,7 @@
         <v>85</v>
       </c>
       <c r="I338">
-        <f>SUM(C338:H338)</f>
+        <f t="shared" si="5"/>
         <v>475</v>
       </c>
       <c r="J338" t="s">
@@ -21463,7 +21482,7 @@
         <v>60</v>
       </c>
       <c r="I339">
-        <f>SUM(C339:H339)</f>
+        <f t="shared" si="5"/>
         <v>475</v>
       </c>
       <c r="J339" t="s">
@@ -21514,7 +21533,7 @@
         <v>45</v>
       </c>
       <c r="I340">
-        <f>SUM(C340:H340)</f>
+        <f t="shared" si="5"/>
         <v>475</v>
       </c>
       <c r="J340" t="s">
@@ -21565,7 +21584,7 @@
         <v>75</v>
       </c>
       <c r="I341">
-        <f>SUM(C341:H341)</f>
+        <f t="shared" si="5"/>
         <v>475</v>
       </c>
       <c r="J341" t="s">
@@ -21616,7 +21635,7 @@
         <v>65</v>
       </c>
       <c r="I342">
-        <f>SUM(C342:H342)</f>
+        <f t="shared" si="5"/>
         <v>475</v>
       </c>
       <c r="J342" t="s">
@@ -21667,7 +21686,7 @@
         <v>130</v>
       </c>
       <c r="I343">
-        <f>SUM(C343:H343)</f>
+        <f t="shared" si="5"/>
         <v>475</v>
       </c>
       <c r="J343" t="s">
@@ -21718,7 +21737,7 @@
         <v>82</v>
       </c>
       <c r="I344">
-        <f>SUM(C344:H344)</f>
+        <f t="shared" si="5"/>
         <v>475</v>
       </c>
       <c r="J344" t="s">
@@ -21769,7 +21788,7 @@
         <v>82</v>
       </c>
       <c r="I345">
-        <f>SUM(C345:H345)</f>
+        <f t="shared" si="5"/>
         <v>475</v>
       </c>
       <c r="J345" t="s">
@@ -21820,7 +21839,7 @@
         <v>70</v>
       </c>
       <c r="I346">
-        <f>SUM(C346:H346)</f>
+        <f t="shared" si="5"/>
         <v>479</v>
       </c>
       <c r="J346" t="s">
@@ -21871,7 +21890,7 @@
         <v>61</v>
       </c>
       <c r="I347">
-        <f>SUM(C347:H347)</f>
+        <f t="shared" si="5"/>
         <v>479</v>
       </c>
       <c r="J347" t="s">
@@ -21922,7 +21941,7 @@
         <v>80</v>
       </c>
       <c r="I348">
-        <f>SUM(C348:H348)</f>
+        <f t="shared" si="5"/>
         <v>480</v>
       </c>
       <c r="J348" t="s">
@@ -21973,7 +21992,7 @@
         <v>80</v>
       </c>
       <c r="I349">
-        <f>SUM(C349:H349)</f>
+        <f t="shared" si="5"/>
         <v>480</v>
       </c>
       <c r="J349" t="s">
@@ -22024,7 +22043,7 @@
         <v>100</v>
       </c>
       <c r="I350">
-        <f>SUM(C350:H350)</f>
+        <f t="shared" si="5"/>
         <v>480</v>
       </c>
       <c r="J350" t="s">
@@ -22075,7 +22094,7 @@
         <v>86</v>
       </c>
       <c r="I351">
-        <f>SUM(C351:H351)</f>
+        <f t="shared" si="5"/>
         <v>480</v>
       </c>
       <c r="J351" t="s">
@@ -22126,7 +22145,7 @@
         <v>75</v>
       </c>
       <c r="I352">
-        <f>SUM(C352:H352)</f>
+        <f t="shared" si="5"/>
         <v>480</v>
       </c>
       <c r="J352" t="s">
@@ -22177,7 +22196,7 @@
         <v>75</v>
       </c>
       <c r="I353">
-        <f>SUM(C353:H353)</f>
+        <f t="shared" si="5"/>
         <v>480</v>
       </c>
       <c r="J353" t="s">
@@ -22202,7 +22221,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="354" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
         <v>834</v>
       </c>
@@ -22228,7 +22247,7 @@
         <v>55</v>
       </c>
       <c r="I354">
-        <f>SUM(C354:H354)</f>
+        <f t="shared" si="5"/>
         <v>480</v>
       </c>
       <c r="J354" t="s">
@@ -22253,7 +22272,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="355" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
         <v>1011</v>
       </c>
@@ -22279,7 +22298,7 @@
         <v>96</v>
       </c>
       <c r="I355">
-        <f>SUM(C355:H355)</f>
+        <f t="shared" si="5"/>
         <v>480</v>
       </c>
       <c r="J355" t="s">
@@ -22301,7 +22320,7 @@
         <v>0</v>
       </c>
       <c r="P355" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="356" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
@@ -22330,7 +22349,7 @@
         <v>80</v>
       </c>
       <c r="I356">
-        <f>SUM(C356:H356)</f>
+        <f t="shared" si="5"/>
         <v>480</v>
       </c>
       <c r="J356" t="s">
@@ -22381,7 +22400,7 @@
         <v>66</v>
       </c>
       <c r="I357">
-        <f>SUM(C357:H357)</f>
+        <f t="shared" si="5"/>
         <v>482</v>
       </c>
       <c r="J357" t="s">
@@ -22406,7 +22425,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="358" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
         <v>744</v>
       </c>
@@ -22432,7 +22451,7 @@
         <v>65</v>
       </c>
       <c r="I358">
-        <f>SUM(C358:H358)</f>
+        <f t="shared" si="5"/>
         <v>484</v>
       </c>
       <c r="J358" t="s">
@@ -22483,7 +22502,7 @@
         <v>50</v>
       </c>
       <c r="I359">
-        <f>SUM(C359:H359)</f>
+        <f t="shared" si="5"/>
         <v>485</v>
       </c>
       <c r="J359" t="s">
@@ -22534,7 +22553,7 @@
         <v>45</v>
       </c>
       <c r="I360">
-        <f>SUM(C360:H360)</f>
+        <f t="shared" si="5"/>
         <v>485</v>
       </c>
       <c r="J360" t="s">
@@ -22585,7 +22604,7 @@
         <v>100</v>
       </c>
       <c r="I361">
-        <f>SUM(C361:H361)</f>
+        <f t="shared" si="5"/>
         <v>485</v>
       </c>
       <c r="J361" t="s">
@@ -22636,7 +22655,7 @@
         <v>65</v>
       </c>
       <c r="I362">
-        <f>SUM(C362:H362)</f>
+        <f t="shared" si="5"/>
         <v>485</v>
       </c>
       <c r="J362" t="s">
@@ -22687,7 +22706,7 @@
         <v>60</v>
       </c>
       <c r="I363">
-        <f>SUM(C363:H363)</f>
+        <f t="shared" si="5"/>
         <v>485</v>
       </c>
       <c r="J363" t="s">
@@ -22738,7 +22757,7 @@
         <v>65</v>
       </c>
       <c r="I364">
-        <f>SUM(C364:H364)</f>
+        <f t="shared" si="5"/>
         <v>485</v>
       </c>
       <c r="J364" t="s">
@@ -22789,7 +22808,7 @@
         <v>60</v>
       </c>
       <c r="I365">
-        <f>SUM(C365:H365)</f>
+        <f t="shared" si="5"/>
         <v>485</v>
       </c>
       <c r="J365" t="s">
@@ -22840,7 +22859,7 @@
         <v>108</v>
       </c>
       <c r="I366">
-        <f>SUM(C366:H366)</f>
+        <f t="shared" si="5"/>
         <v>485</v>
       </c>
       <c r="J366" t="s">
@@ -22891,7 +22910,7 @@
         <v>85</v>
       </c>
       <c r="I367">
-        <f>SUM(C367:H367)</f>
+        <f t="shared" si="5"/>
         <v>490</v>
       </c>
       <c r="J367" t="s">
@@ -22942,7 +22961,7 @@
         <v>85</v>
       </c>
       <c r="I368">
-        <f>SUM(C368:H368)</f>
+        <f t="shared" si="5"/>
         <v>490</v>
       </c>
       <c r="J368" t="s">
@@ -22993,7 +23012,7 @@
         <v>80</v>
       </c>
       <c r="I369">
-        <f>SUM(C369:H369)</f>
+        <f t="shared" si="5"/>
         <v>490</v>
       </c>
       <c r="J369" t="s">
@@ -23044,7 +23063,7 @@
         <v>70</v>
       </c>
       <c r="I370">
-        <f>SUM(C370:H370)</f>
+        <f t="shared" si="5"/>
         <v>490</v>
       </c>
       <c r="J370" t="s">
@@ -23095,7 +23114,7 @@
         <v>70</v>
       </c>
       <c r="I371">
-        <f>SUM(C371:H371)</f>
+        <f t="shared" si="5"/>
         <v>490</v>
       </c>
       <c r="J371" t="s">
@@ -23146,7 +23165,7 @@
         <v>70</v>
       </c>
       <c r="I372">
-        <f>SUM(C372:H372)</f>
+        <f t="shared" si="5"/>
         <v>490</v>
       </c>
       <c r="J372" t="s">
@@ -23197,7 +23216,7 @@
         <v>70</v>
       </c>
       <c r="I373">
-        <f>SUM(C373:H373)</f>
+        <f t="shared" si="5"/>
         <v>490</v>
       </c>
       <c r="J373" t="s">
@@ -23248,7 +23267,7 @@
         <v>70</v>
       </c>
       <c r="I374">
-        <f>SUM(C374:H374)</f>
+        <f t="shared" si="5"/>
         <v>490</v>
       </c>
       <c r="J374" t="s">
@@ -23299,7 +23318,7 @@
         <v>70</v>
       </c>
       <c r="I375">
-        <f>SUM(C375:H375)</f>
+        <f t="shared" si="5"/>
         <v>490</v>
       </c>
       <c r="J375" t="s">
@@ -23350,7 +23369,7 @@
         <v>100</v>
       </c>
       <c r="I376">
-        <f>SUM(C376:H376)</f>
+        <f t="shared" si="5"/>
         <v>490</v>
       </c>
       <c r="J376" t="s">
@@ -23401,7 +23420,7 @@
         <v>75</v>
       </c>
       <c r="I377">
-        <f>SUM(C377:H377)</f>
+        <f t="shared" si="5"/>
         <v>490</v>
       </c>
       <c r="J377" t="s">
@@ -23452,7 +23471,7 @@
         <v>70</v>
       </c>
       <c r="I378">
-        <f>SUM(C378:H378)</f>
+        <f t="shared" si="5"/>
         <v>490</v>
       </c>
       <c r="J378" t="s">
@@ -23477,7 +23496,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="379" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
         <v>722</v>
       </c>
@@ -23503,7 +23522,7 @@
         <v>60</v>
       </c>
       <c r="I379">
-        <f>SUM(C379:H379)</f>
+        <f t="shared" si="5"/>
         <v>490</v>
       </c>
       <c r="J379" t="s">
@@ -23554,7 +23573,7 @@
         <v>85</v>
       </c>
       <c r="I380">
-        <f>SUM(C380:H380)</f>
+        <f t="shared" si="5"/>
         <v>495</v>
       </c>
       <c r="J380" t="s">
@@ -23605,7 +23624,7 @@
         <v>70</v>
       </c>
       <c r="I381">
-        <f>SUM(C381:H381)</f>
+        <f t="shared" si="5"/>
         <v>495</v>
       </c>
       <c r="J381" t="s">
@@ -23656,7 +23675,7 @@
         <v>70</v>
       </c>
       <c r="I382">
-        <f>SUM(C382:H382)</f>
+        <f t="shared" si="5"/>
         <v>495</v>
       </c>
       <c r="J382" t="s">
@@ -23707,7 +23726,7 @@
         <v>115</v>
       </c>
       <c r="I383">
-        <f>SUM(C383:H383)</f>
+        <f t="shared" si="5"/>
         <v>495</v>
       </c>
       <c r="J383" t="s">
@@ -23758,7 +23777,7 @@
         <v>105</v>
       </c>
       <c r="I384">
-        <f>SUM(C384:H384)</f>
+        <f t="shared" si="5"/>
         <v>495</v>
       </c>
       <c r="J384" t="s">
@@ -23783,7 +23802,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="385" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
         <v>784</v>
       </c>
@@ -23809,7 +23828,7 @@
         <v>95</v>
       </c>
       <c r="I385">
-        <f>SUM(C385:H385)</f>
+        <f t="shared" si="5"/>
         <v>495</v>
       </c>
       <c r="J385" t="s">
@@ -23860,7 +23879,7 @@
         <v>107</v>
       </c>
       <c r="I386">
-        <f>SUM(C386:H386)</f>
+        <f t="shared" ref="I386:I449" si="6">SUM(C386:H386)</f>
         <v>495</v>
       </c>
       <c r="J386" t="s">
@@ -23911,7 +23930,7 @@
         <v>80</v>
       </c>
       <c r="I387">
-        <f>SUM(C387:H387)</f>
+        <f t="shared" si="6"/>
         <v>495</v>
       </c>
       <c r="J387" t="s">
@@ -23936,7 +23955,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="388" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
         <v>979</v>
       </c>
@@ -23962,7 +23981,7 @@
         <v>50</v>
       </c>
       <c r="I388">
-        <f>SUM(C388:H388)</f>
+        <f t="shared" si="6"/>
         <v>495</v>
       </c>
       <c r="J388" t="s">
@@ -23984,10 +24003,10 @@
         <v>0</v>
       </c>
       <c r="P388" t="s">
-        <v>1098</v>
-      </c>
-    </row>
-    <row r="389" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="389" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
         <v>983</v>
       </c>
@@ -24013,7 +24032,7 @@
         <v>138</v>
       </c>
       <c r="I389">
-        <f>SUM(C389:H389)</f>
+        <f t="shared" si="6"/>
         <v>495</v>
       </c>
       <c r="J389" t="s">
@@ -24035,7 +24054,7 @@
         <v>0</v>
       </c>
       <c r="P389" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="390" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
@@ -24064,7 +24083,7 @@
         <v>50</v>
       </c>
       <c r="I390">
-        <f>SUM(C390:H390)</f>
+        <f t="shared" si="6"/>
         <v>495</v>
       </c>
       <c r="J390" t="s">
@@ -24089,7 +24108,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="391" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
         <v>1010</v>
       </c>
@@ -24115,7 +24134,7 @@
         <v>54</v>
       </c>
       <c r="I391">
-        <f>SUM(C391:H391)</f>
+        <f t="shared" si="6"/>
         <v>498</v>
       </c>
       <c r="J391" t="s">
@@ -24166,7 +24185,7 @@
         <v>102</v>
       </c>
       <c r="I392">
-        <f>SUM(C392:H392)</f>
+        <f t="shared" si="6"/>
         <v>499</v>
       </c>
       <c r="J392" t="s">
@@ -24217,7 +24236,7 @@
         <v>100</v>
       </c>
       <c r="I393">
-        <f>SUM(C393:H393)</f>
+        <f t="shared" si="6"/>
         <v>500</v>
       </c>
       <c r="J393" t="s">
@@ -24268,7 +24287,7 @@
         <v>80</v>
       </c>
       <c r="I394">
-        <f>SUM(C394:H394)</f>
+        <f t="shared" si="6"/>
         <v>500</v>
       </c>
       <c r="J394" t="s">
@@ -24319,7 +24338,7 @@
         <v>140</v>
       </c>
       <c r="I395">
-        <f>SUM(C395:H395)</f>
+        <f t="shared" si="6"/>
         <v>500</v>
       </c>
       <c r="J395" t="s">
@@ -24370,7 +24389,7 @@
         <v>80</v>
       </c>
       <c r="I396">
-        <f>SUM(C396:H396)</f>
+        <f t="shared" si="6"/>
         <v>500</v>
       </c>
       <c r="J396" t="s">
@@ -24421,7 +24440,7 @@
         <v>80</v>
       </c>
       <c r="I397">
-        <f>SUM(C397:H397)</f>
+        <f t="shared" si="6"/>
         <v>500</v>
       </c>
       <c r="J397" t="s">
@@ -24472,7 +24491,7 @@
         <v>80</v>
       </c>
       <c r="I398">
-        <f>SUM(C398:H398)</f>
+        <f t="shared" si="6"/>
         <v>500</v>
       </c>
       <c r="J398" t="s">
@@ -24523,7 +24542,7 @@
         <v>75</v>
       </c>
       <c r="I399">
-        <f>SUM(C399:H399)</f>
+        <f t="shared" si="6"/>
         <v>500</v>
       </c>
       <c r="J399" t="s">
@@ -24574,7 +24593,7 @@
         <v>70</v>
       </c>
       <c r="I400">
-        <f>SUM(C400:H400)</f>
+        <f t="shared" si="6"/>
         <v>500</v>
       </c>
       <c r="J400" t="s">
@@ -24625,7 +24644,7 @@
         <v>85</v>
       </c>
       <c r="I401">
-        <f>SUM(C401:H401)</f>
+        <f t="shared" si="6"/>
         <v>500</v>
       </c>
       <c r="J401" t="s">
@@ -24676,7 +24695,7 @@
         <v>80</v>
       </c>
       <c r="I402">
-        <f>SUM(C402:H402)</f>
+        <f t="shared" si="6"/>
         <v>500</v>
       </c>
       <c r="J402" t="s">
@@ -24727,7 +24746,7 @@
         <v>80</v>
       </c>
       <c r="I403">
-        <f>SUM(C403:H403)</f>
+        <f t="shared" si="6"/>
         <v>500</v>
       </c>
       <c r="J403" t="s">
@@ -24778,7 +24797,7 @@
         <v>100</v>
       </c>
       <c r="I404">
-        <f>SUM(C404:H404)</f>
+        <f t="shared" si="6"/>
         <v>500</v>
       </c>
       <c r="J404" t="s">
@@ -24829,7 +24848,7 @@
         <v>80</v>
       </c>
       <c r="I405">
-        <f>SUM(C405:H405)</f>
+        <f t="shared" si="6"/>
         <v>500</v>
       </c>
       <c r="J405" t="s">
@@ -24880,7 +24899,7 @@
         <v>70</v>
       </c>
       <c r="I406">
-        <f>SUM(C406:H406)</f>
+        <f t="shared" si="6"/>
         <v>500</v>
       </c>
       <c r="J406" t="s">
@@ -24931,7 +24950,7 @@
         <v>75</v>
       </c>
       <c r="I407">
-        <f>SUM(C407:H407)</f>
+        <f t="shared" si="6"/>
         <v>500</v>
       </c>
       <c r="J407" t="s">
@@ -24982,7 +25001,7 @@
         <v>95</v>
       </c>
       <c r="I408">
-        <f>SUM(C408:H408)</f>
+        <f t="shared" si="6"/>
         <v>500</v>
       </c>
       <c r="J408" t="s">
@@ -25033,7 +25052,7 @@
         <v>90</v>
       </c>
       <c r="I409">
-        <f>SUM(C409:H409)</f>
+        <f t="shared" si="6"/>
         <v>500</v>
       </c>
       <c r="J409" t="s">
@@ -25084,7 +25103,7 @@
         <v>95</v>
       </c>
       <c r="I410">
-        <f>SUM(C410:H410)</f>
+        <f t="shared" si="6"/>
         <v>500</v>
       </c>
       <c r="J410" t="s">
@@ -25135,7 +25154,7 @@
         <v>75</v>
       </c>
       <c r="I411">
-        <f>SUM(C411:H411)</f>
+        <f t="shared" si="6"/>
         <v>500</v>
       </c>
       <c r="J411" t="s">
@@ -25186,7 +25205,7 @@
         <v>75</v>
       </c>
       <c r="I412">
-        <f>SUM(C412:H412)</f>
+        <f t="shared" si="6"/>
         <v>500</v>
       </c>
       <c r="J412" t="s">
@@ -25237,7 +25256,7 @@
         <v>80</v>
       </c>
       <c r="I413">
-        <f>SUM(C413:H413)</f>
+        <f t="shared" si="6"/>
         <v>500</v>
       </c>
       <c r="J413" t="s">
@@ -25262,7 +25281,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="414" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
         <v>623</v>
       </c>
@@ -25288,7 +25307,7 @@
         <v>60</v>
       </c>
       <c r="I414">
-        <f>SUM(C414:H414)</f>
+        <f t="shared" si="6"/>
         <v>500</v>
       </c>
       <c r="J414" t="s">
@@ -25310,7 +25329,7 @@
         <v>0</v>
       </c>
       <c r="P414" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="415" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
@@ -25339,7 +25358,7 @@
         <v>110</v>
       </c>
       <c r="I415">
-        <f>SUM(C415:H415)</f>
+        <f t="shared" si="6"/>
         <v>500</v>
       </c>
       <c r="J415" t="s">
@@ -25390,7 +25409,7 @@
         <v>60</v>
       </c>
       <c r="I416">
-        <f>SUM(C416:H416)</f>
+        <f t="shared" si="6"/>
         <v>500</v>
       </c>
       <c r="J416" t="s">
@@ -25415,7 +25434,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="417" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
         <v>792</v>
       </c>
@@ -25441,7 +25460,7 @@
         <v>45</v>
       </c>
       <c r="I417">
-        <f>SUM(C417:H417)</f>
+        <f t="shared" si="6"/>
         <v>500</v>
       </c>
       <c r="J417" t="s">
@@ -25492,7 +25511,7 @@
         <v>120</v>
       </c>
       <c r="I418">
-        <f>SUM(C418:H418)</f>
+        <f t="shared" si="6"/>
         <v>500</v>
       </c>
       <c r="J418" t="s">
@@ -25543,7 +25562,7 @@
         <v>116</v>
       </c>
       <c r="I419">
-        <f>SUM(C419:H419)</f>
+        <f t="shared" si="6"/>
         <v>500</v>
       </c>
       <c r="J419" t="s">
@@ -25594,7 +25613,7 @@
         <v>75</v>
       </c>
       <c r="I420">
-        <f>SUM(C420:H420)</f>
+        <f t="shared" si="6"/>
         <v>500</v>
       </c>
       <c r="J420" t="s">
@@ -25645,7 +25664,7 @@
         <v>70</v>
       </c>
       <c r="I421">
-        <f>SUM(C421:H421)</f>
+        <f t="shared" si="6"/>
         <v>500</v>
       </c>
       <c r="J421" t="s">
@@ -25696,7 +25715,7 @@
         <v>85</v>
       </c>
       <c r="I422">
-        <f>SUM(C422:H422)</f>
+        <f t="shared" si="6"/>
         <v>500</v>
       </c>
       <c r="J422" t="s">
@@ -25747,7 +25766,7 @@
         <v>85</v>
       </c>
       <c r="I423">
-        <f>SUM(C423:H423)</f>
+        <f t="shared" si="6"/>
         <v>505</v>
       </c>
       <c r="J423" t="s">
@@ -25798,7 +25817,7 @@
         <v>75</v>
       </c>
       <c r="I424">
-        <f>SUM(C424:H424)</f>
+        <f t="shared" si="6"/>
         <v>505</v>
       </c>
       <c r="J424" t="s">
@@ -25849,7 +25868,7 @@
         <v>100</v>
       </c>
       <c r="I425">
-        <f>SUM(C425:H425)</f>
+        <f t="shared" si="6"/>
         <v>505</v>
       </c>
       <c r="J425" t="s">
@@ -25900,7 +25919,7 @@
         <v>100</v>
       </c>
       <c r="I426">
-        <f>SUM(C426:H426)</f>
+        <f t="shared" si="6"/>
         <v>505</v>
       </c>
       <c r="J426" t="s">
@@ -25951,7 +25970,7 @@
         <v>230</v>
       </c>
       <c r="I427">
-        <f>SUM(C427:H427)</f>
+        <f t="shared" si="6"/>
         <v>505</v>
       </c>
       <c r="J427" t="s">
@@ -26002,7 +26021,7 @@
         <v>105</v>
       </c>
       <c r="I428">
-        <f>SUM(C428:H428)</f>
+        <f t="shared" si="6"/>
         <v>505</v>
       </c>
       <c r="J428" t="s">
@@ -26053,7 +26072,7 @@
         <v>82</v>
       </c>
       <c r="I429">
-        <f>SUM(C429:H429)</f>
+        <f t="shared" si="6"/>
         <v>507</v>
       </c>
       <c r="J429" t="s">
@@ -26104,7 +26123,7 @@
         <v>90</v>
       </c>
       <c r="I430">
-        <f>SUM(C430:H430)</f>
+        <f t="shared" si="6"/>
         <v>510</v>
       </c>
       <c r="J430" t="s">
@@ -26155,7 +26174,7 @@
         <v>95</v>
       </c>
       <c r="I431">
-        <f>SUM(C431:H431)</f>
+        <f t="shared" si="6"/>
         <v>510</v>
       </c>
       <c r="J431" t="s">
@@ -26206,7 +26225,7 @@
         <v>100</v>
       </c>
       <c r="I432">
-        <f>SUM(C432:H432)</f>
+        <f t="shared" si="6"/>
         <v>510</v>
       </c>
       <c r="J432" t="s">
@@ -26257,7 +26276,7 @@
         <v>70</v>
       </c>
       <c r="I433">
-        <f>SUM(C433:H433)</f>
+        <f t="shared" si="6"/>
         <v>510</v>
       </c>
       <c r="J433" t="s">
@@ -26308,7 +26327,7 @@
         <v>70</v>
       </c>
       <c r="I434">
-        <f>SUM(C434:H434)</f>
+        <f t="shared" si="6"/>
         <v>510</v>
       </c>
       <c r="J434" t="s">
@@ -26359,7 +26378,7 @@
         <v>90</v>
       </c>
       <c r="I435">
-        <f>SUM(C435:H435)</f>
+        <f t="shared" si="6"/>
         <v>510</v>
       </c>
       <c r="J435" t="s">
@@ -26410,7 +26429,7 @@
         <v>110</v>
       </c>
       <c r="I436">
-        <f>SUM(C436:H436)</f>
+        <f t="shared" si="6"/>
         <v>510</v>
       </c>
       <c r="J436" t="s">
@@ -26461,7 +26480,7 @@
         <v>70</v>
       </c>
       <c r="I437">
-        <f>SUM(C437:H437)</f>
+        <f t="shared" si="6"/>
         <v>510</v>
       </c>
       <c r="J437" t="s">
@@ -26512,7 +26531,7 @@
         <v>115</v>
       </c>
       <c r="I438">
-        <f>SUM(C438:H438)</f>
+        <f t="shared" si="6"/>
         <v>510</v>
       </c>
       <c r="J438" t="s">
@@ -26563,7 +26582,7 @@
         <v>65</v>
       </c>
       <c r="I439">
-        <f>SUM(C439:H439)</f>
+        <f t="shared" si="6"/>
         <v>510</v>
       </c>
       <c r="J439" t="s">
@@ -26614,7 +26633,7 @@
         <v>65</v>
       </c>
       <c r="I440">
-        <f>SUM(C440:H440)</f>
+        <f t="shared" si="6"/>
         <v>510</v>
       </c>
       <c r="J440" t="s">
@@ -26665,7 +26684,7 @@
         <v>85</v>
       </c>
       <c r="I441">
-        <f>SUM(C441:H441)</f>
+        <f t="shared" si="6"/>
         <v>510</v>
       </c>
       <c r="J441" t="s">
@@ -26716,7 +26735,7 @@
         <v>80</v>
       </c>
       <c r="I442">
-        <f>SUM(C442:H442)</f>
+        <f t="shared" si="6"/>
         <v>510</v>
       </c>
       <c r="J442" t="s">
@@ -26767,7 +26786,7 @@
         <v>130</v>
       </c>
       <c r="I443">
-        <f>SUM(C443:H443)</f>
+        <f t="shared" si="6"/>
         <v>510</v>
       </c>
       <c r="J443" t="s">
@@ -26818,7 +26837,7 @@
         <v>105</v>
       </c>
       <c r="I444">
-        <f>SUM(C444:H444)</f>
+        <f t="shared" si="6"/>
         <v>510</v>
       </c>
       <c r="J444" t="s">
@@ -26869,7 +26888,7 @@
         <v>85</v>
       </c>
       <c r="I445">
-        <f>SUM(C445:H445)</f>
+        <f t="shared" si="6"/>
         <v>510</v>
       </c>
       <c r="J445" t="s">
@@ -26920,7 +26939,7 @@
         <v>75</v>
       </c>
       <c r="I446">
-        <f>SUM(C446:H446)</f>
+        <f t="shared" si="6"/>
         <v>510</v>
       </c>
       <c r="J446" t="s">
@@ -26971,7 +26990,7 @@
         <v>75</v>
       </c>
       <c r="I447">
-        <f>SUM(C447:H447)</f>
+        <f t="shared" si="6"/>
         <v>510</v>
       </c>
       <c r="J447" t="s">
@@ -27022,7 +27041,7 @@
         <v>75</v>
       </c>
       <c r="I448">
-        <f>SUM(C448:H448)</f>
+        <f t="shared" si="6"/>
         <v>510</v>
       </c>
       <c r="J448" t="s">
@@ -27073,7 +27092,7 @@
         <v>120</v>
       </c>
       <c r="I449">
-        <f>SUM(C449:H449)</f>
+        <f t="shared" si="6"/>
         <v>515</v>
       </c>
       <c r="J449" t="s">
@@ -27124,7 +27143,7 @@
         <v>75</v>
       </c>
       <c r="I450">
-        <f>SUM(C450:H450)</f>
+        <f t="shared" ref="I450:I513" si="7">SUM(C450:H450)</f>
         <v>515</v>
       </c>
       <c r="J450" t="s">
@@ -27175,7 +27194,7 @@
         <v>95</v>
       </c>
       <c r="I451">
-        <f>SUM(C451:H451)</f>
+        <f t="shared" si="7"/>
         <v>515</v>
       </c>
       <c r="J451" t="s">
@@ -27226,7 +27245,7 @@
         <v>95</v>
       </c>
       <c r="I452">
-        <f>SUM(C452:H452)</f>
+        <f t="shared" si="7"/>
         <v>515</v>
       </c>
       <c r="J452" t="s">
@@ -27277,7 +27296,7 @@
         <v>56</v>
       </c>
       <c r="I453">
-        <f>SUM(C453:H453)</f>
+        <f t="shared" si="7"/>
         <v>515</v>
       </c>
       <c r="J453" t="s">
@@ -27328,7 +27347,7 @@
         <v>55</v>
       </c>
       <c r="I454">
-        <f>SUM(C454:H454)</f>
+        <f t="shared" si="7"/>
         <v>515</v>
       </c>
       <c r="J454" t="s">
@@ -27379,7 +27398,7 @@
         <v>115</v>
       </c>
       <c r="I455">
-        <f>SUM(C455:H455)</f>
+        <f t="shared" si="7"/>
         <v>518</v>
       </c>
       <c r="J455" t="s">
@@ -27430,7 +27449,7 @@
         <v>115</v>
       </c>
       <c r="I456">
-        <f>SUM(C456:H456)</f>
+        <f t="shared" si="7"/>
         <v>518</v>
       </c>
       <c r="J456" t="s">
@@ -27481,7 +27500,7 @@
         <v>85</v>
       </c>
       <c r="I457">
-        <f>SUM(C457:H457)</f>
+        <f t="shared" si="7"/>
         <v>520</v>
       </c>
       <c r="J457" t="s">
@@ -27532,7 +27551,7 @@
         <v>75</v>
       </c>
       <c r="I458">
-        <f>SUM(C458:H458)</f>
+        <f t="shared" si="7"/>
         <v>520</v>
       </c>
       <c r="J458" t="s">
@@ -27583,7 +27602,7 @@
         <v>65</v>
       </c>
       <c r="I459">
-        <f>SUM(C459:H459)</f>
+        <f t="shared" si="7"/>
         <v>520</v>
       </c>
       <c r="J459" t="s">
@@ -27634,7 +27653,7 @@
         <v>65</v>
       </c>
       <c r="I460">
-        <f>SUM(C460:H460)</f>
+        <f t="shared" si="7"/>
         <v>520</v>
       </c>
       <c r="J460" t="s">
@@ -27685,7 +27704,7 @@
         <v>100</v>
       </c>
       <c r="I461">
-        <f>SUM(C461:H461)</f>
+        <f t="shared" si="7"/>
         <v>520</v>
       </c>
       <c r="J461" t="s">
@@ -27736,7 +27755,7 @@
         <v>90</v>
       </c>
       <c r="I462">
-        <f>SUM(C462:H462)</f>
+        <f t="shared" si="7"/>
         <v>520</v>
       </c>
       <c r="J462" t="s">
@@ -27787,7 +27806,7 @@
         <v>70</v>
       </c>
       <c r="I463">
-        <f>SUM(C463:H463)</f>
+        <f t="shared" si="7"/>
         <v>520</v>
       </c>
       <c r="J463" t="s">
@@ -27838,7 +27857,7 @@
         <v>75</v>
       </c>
       <c r="I464">
-        <f>SUM(C464:H464)</f>
+        <f t="shared" si="7"/>
         <v>520</v>
       </c>
       <c r="J464" t="s">
@@ -27889,7 +27908,7 @@
         <v>75</v>
       </c>
       <c r="I465">
-        <f>SUM(C465:H465)</f>
+        <f t="shared" si="7"/>
         <v>520</v>
       </c>
       <c r="J465" t="s">
@@ -27940,7 +27959,7 @@
         <v>81</v>
       </c>
       <c r="I466">
-        <f>SUM(C466:H466)</f>
+        <f t="shared" si="7"/>
         <v>520</v>
       </c>
       <c r="J466" t="s">
@@ -27991,7 +28010,7 @@
         <v>73</v>
       </c>
       <c r="I467">
-        <f>SUM(C467:H467)</f>
+        <f t="shared" si="7"/>
         <v>520</v>
       </c>
       <c r="J467" t="s">
@@ -28042,7 +28061,7 @@
         <v>80</v>
       </c>
       <c r="I468">
-        <f>SUM(C468:H468)</f>
+        <f t="shared" si="7"/>
         <v>520</v>
       </c>
       <c r="J468" t="s">
@@ -28093,7 +28112,7 @@
         <v>107</v>
       </c>
       <c r="I469">
-        <f>SUM(C469:H469)</f>
+        <f t="shared" si="7"/>
         <v>520</v>
       </c>
       <c r="J469" t="s">
@@ -28144,7 +28163,7 @@
         <v>107</v>
       </c>
       <c r="I470">
-        <f>SUM(C470:H470)</f>
+        <f t="shared" si="7"/>
         <v>520</v>
       </c>
       <c r="J470" t="s">
@@ -28195,7 +28214,7 @@
         <v>107</v>
       </c>
       <c r="I471">
-        <f>SUM(C471:H471)</f>
+        <f t="shared" si="7"/>
         <v>520</v>
       </c>
       <c r="J471" t="s">
@@ -28246,7 +28265,7 @@
         <v>107</v>
       </c>
       <c r="I472">
-        <f>SUM(C472:H472)</f>
+        <f t="shared" si="7"/>
         <v>520</v>
       </c>
       <c r="J472" t="s">
@@ -28297,7 +28316,7 @@
         <v>107</v>
       </c>
       <c r="I473">
-        <f>SUM(C473:H473)</f>
+        <f t="shared" si="7"/>
         <v>520</v>
       </c>
       <c r="J473" t="s">
@@ -28348,7 +28367,7 @@
         <v>79</v>
       </c>
       <c r="I474">
-        <f>SUM(C474:H474)</f>
+        <f t="shared" si="7"/>
         <v>523</v>
       </c>
       <c r="J474" t="s">
@@ -28399,7 +28418,7 @@
         <v>95</v>
       </c>
       <c r="I475">
-        <f>SUM(C475:H475)</f>
+        <f t="shared" si="7"/>
         <v>525</v>
       </c>
       <c r="J475" t="s">
@@ -28450,7 +28469,7 @@
         <v>95</v>
       </c>
       <c r="I476">
-        <f>SUM(C476:H476)</f>
+        <f t="shared" si="7"/>
         <v>525</v>
       </c>
       <c r="J476" t="s">
@@ -28501,7 +28520,7 @@
         <v>110</v>
       </c>
       <c r="I477">
-        <f>SUM(C477:H477)</f>
+        <f t="shared" si="7"/>
         <v>525</v>
       </c>
       <c r="J477" t="s">
@@ -28552,7 +28571,7 @@
         <v>45</v>
       </c>
       <c r="I478">
-        <f>SUM(C478:H478)</f>
+        <f t="shared" si="7"/>
         <v>525</v>
       </c>
       <c r="J478" t="s">
@@ -28603,7 +28622,7 @@
         <v>100</v>
       </c>
       <c r="I479">
-        <f>SUM(C479:H479)</f>
+        <f t="shared" si="7"/>
         <v>525</v>
       </c>
       <c r="J479" t="s">
@@ -28654,7 +28673,7 @@
         <v>95</v>
       </c>
       <c r="I480">
-        <f>SUM(C480:H480)</f>
+        <f t="shared" si="7"/>
         <v>525</v>
       </c>
       <c r="J480" t="s">
@@ -28705,7 +28724,7 @@
         <v>95</v>
       </c>
       <c r="I481">
-        <f>SUM(C481:H481)</f>
+        <f t="shared" si="7"/>
         <v>525</v>
       </c>
       <c r="J481" t="s">
@@ -28756,7 +28775,7 @@
         <v>130</v>
       </c>
       <c r="I482">
-        <f>SUM(C482:H482)</f>
+        <f t="shared" si="7"/>
         <v>525</v>
       </c>
       <c r="J482" t="s">
@@ -28807,7 +28826,7 @@
         <v>65</v>
       </c>
       <c r="I483">
-        <f>SUM(C483:H483)</f>
+        <f t="shared" si="7"/>
         <v>525</v>
       </c>
       <c r="J483" t="s">
@@ -28858,7 +28877,7 @@
         <v>95</v>
       </c>
       <c r="I484">
-        <f>SUM(C484:H484)</f>
+        <f t="shared" si="7"/>
         <v>525</v>
       </c>
       <c r="J484" t="s">
@@ -28909,7 +28928,7 @@
         <v>130</v>
       </c>
       <c r="I485">
-        <f>SUM(C485:H485)</f>
+        <f t="shared" si="7"/>
         <v>525</v>
       </c>
       <c r="J485" t="s">
@@ -28960,7 +28979,7 @@
         <v>100</v>
       </c>
       <c r="I486">
-        <f>SUM(C486:H486)</f>
+        <f t="shared" si="7"/>
         <v>525</v>
       </c>
       <c r="J486" t="s">
@@ -29011,7 +29030,7 @@
         <v>90</v>
       </c>
       <c r="I487">
-        <f>SUM(C487:H487)</f>
+        <f t="shared" si="7"/>
         <v>525</v>
       </c>
       <c r="J487" t="s">
@@ -29062,7 +29081,7 @@
         <v>75</v>
       </c>
       <c r="I488">
-        <f>SUM(C488:H488)</f>
+        <f t="shared" si="7"/>
         <v>525</v>
       </c>
       <c r="J488" t="s">
@@ -29113,7 +29132,7 @@
         <v>150</v>
       </c>
       <c r="I489">
-        <f>SUM(C489:H489)</f>
+        <f t="shared" si="7"/>
         <v>525</v>
       </c>
       <c r="J489" t="s">
@@ -29164,7 +29183,7 @@
         <v>135</v>
       </c>
       <c r="I490">
-        <f>SUM(C490:H490)</f>
+        <f t="shared" si="7"/>
         <v>525</v>
       </c>
       <c r="J490" t="s">
@@ -29215,7 +29234,7 @@
         <v>85</v>
       </c>
       <c r="I491">
-        <f>SUM(C491:H491)</f>
+        <f t="shared" si="7"/>
         <v>525</v>
       </c>
       <c r="J491" t="s">
@@ -29266,7 +29285,7 @@
         <v>70</v>
       </c>
       <c r="I492">
-        <f>SUM(C492:H492)</f>
+        <f t="shared" si="7"/>
         <v>525</v>
       </c>
       <c r="J492" t="s">
@@ -29317,7 +29336,7 @@
         <v>72</v>
       </c>
       <c r="I493">
-        <f>SUM(C493:H493)</f>
+        <f t="shared" si="7"/>
         <v>525</v>
       </c>
       <c r="J493" t="s">
@@ -29368,7 +29387,7 @@
         <v>105</v>
       </c>
       <c r="I494">
-        <f>SUM(C494:H494)</f>
+        <f t="shared" si="7"/>
         <v>530</v>
       </c>
       <c r="J494" t="s">
@@ -29419,7 +29438,7 @@
         <v>83</v>
       </c>
       <c r="I495">
-        <f>SUM(C495:H495)</f>
+        <f t="shared" si="7"/>
         <v>530</v>
       </c>
       <c r="J495" t="s">
@@ -29470,7 +29489,7 @@
         <v>60</v>
       </c>
       <c r="I496">
-        <f>SUM(C496:H496)</f>
+        <f t="shared" si="7"/>
         <v>530</v>
       </c>
       <c r="J496" t="s">
@@ -29521,7 +29540,7 @@
         <v>85</v>
       </c>
       <c r="I497">
-        <f>SUM(C497:H497)</f>
+        <f t="shared" si="7"/>
         <v>530</v>
       </c>
       <c r="J497" t="s">
@@ -29572,7 +29591,7 @@
         <v>70</v>
       </c>
       <c r="I498">
-        <f>SUM(C498:H498)</f>
+        <f t="shared" si="7"/>
         <v>530</v>
       </c>
       <c r="J498" t="s">
@@ -29623,7 +29642,7 @@
         <v>60</v>
       </c>
       <c r="I499">
-        <f>SUM(C499:H499)</f>
+        <f t="shared" si="7"/>
         <v>530</v>
       </c>
       <c r="J499" t="s">
@@ -29674,7 +29693,7 @@
         <v>90</v>
       </c>
       <c r="I500">
-        <f>SUM(C500:H500)</f>
+        <f t="shared" si="7"/>
         <v>530</v>
       </c>
       <c r="J500" t="s">
@@ -29725,7 +29744,7 @@
         <v>101</v>
       </c>
       <c r="I501">
-        <f>SUM(C501:H501)</f>
+        <f t="shared" si="7"/>
         <v>530</v>
       </c>
       <c r="J501" t="s">
@@ -29776,7 +29795,7 @@
         <v>85</v>
       </c>
       <c r="I502">
-        <f>SUM(C502:H502)</f>
+        <f t="shared" si="7"/>
         <v>534</v>
       </c>
       <c r="J502" t="s">
@@ -29827,7 +29846,7 @@
         <v>85</v>
       </c>
       <c r="I503">
-        <f>SUM(C503:H503)</f>
+        <f t="shared" si="7"/>
         <v>534</v>
       </c>
       <c r="J503" t="s">
@@ -29878,7 +29897,7 @@
         <v>85</v>
       </c>
       <c r="I504">
-        <f>SUM(C504:H504)</f>
+        <f t="shared" si="7"/>
         <v>534</v>
       </c>
       <c r="J504" t="s">
@@ -29929,7 +29948,7 @@
         <v>71</v>
       </c>
       <c r="I505">
-        <f>SUM(C505:H505)</f>
+        <f t="shared" si="7"/>
         <v>534</v>
       </c>
       <c r="J505" t="s">
@@ -29980,7 +29999,7 @@
         <v>95</v>
       </c>
       <c r="I506">
-        <f>SUM(C506:H506)</f>
+        <f t="shared" si="7"/>
         <v>535</v>
       </c>
       <c r="J506" t="s">
@@ -30031,7 +30050,7 @@
         <v>80</v>
       </c>
       <c r="I507">
-        <f>SUM(C507:H507)</f>
+        <f t="shared" si="7"/>
         <v>535</v>
       </c>
       <c r="J507" t="s">
@@ -30082,7 +30101,7 @@
         <v>90</v>
       </c>
       <c r="I508">
-        <f>SUM(C508:H508)</f>
+        <f t="shared" si="7"/>
         <v>535</v>
       </c>
       <c r="J508" t="s">
@@ -30133,7 +30152,7 @@
         <v>55</v>
       </c>
       <c r="I509">
-        <f>SUM(C509:H509)</f>
+        <f t="shared" si="7"/>
         <v>535</v>
       </c>
       <c r="J509" t="s">
@@ -30184,7 +30203,7 @@
         <v>50</v>
       </c>
       <c r="I510">
-        <f>SUM(C510:H510)</f>
+        <f t="shared" si="7"/>
         <v>535</v>
       </c>
       <c r="J510" t="s">
@@ -30235,7 +30254,7 @@
         <v>75</v>
       </c>
       <c r="I511">
-        <f>SUM(C511:H511)</f>
+        <f t="shared" si="7"/>
         <v>535</v>
       </c>
       <c r="J511" t="s">
@@ -30286,7 +30305,7 @@
         <v>90</v>
       </c>
       <c r="I512">
-        <f>SUM(C512:H512)</f>
+        <f t="shared" si="7"/>
         <v>535</v>
       </c>
       <c r="J512" t="s">
@@ -30337,7 +30356,7 @@
         <v>110</v>
       </c>
       <c r="I513">
-        <f>SUM(C513:H513)</f>
+        <f t="shared" si="7"/>
         <v>540</v>
       </c>
       <c r="J513" t="s">
@@ -30388,7 +30407,7 @@
         <v>100</v>
       </c>
       <c r="I514">
-        <f>SUM(C514:H514)</f>
+        <f t="shared" ref="I514:I577" si="8">SUM(C514:H514)</f>
         <v>540</v>
       </c>
       <c r="J514" t="s">
@@ -30439,7 +30458,7 @@
         <v>135</v>
       </c>
       <c r="I515">
-        <f>SUM(C515:H515)</f>
+        <f t="shared" si="8"/>
         <v>540</v>
       </c>
       <c r="J515" t="s">
@@ -30490,7 +30509,7 @@
         <v>95</v>
       </c>
       <c r="I516">
-        <f>SUM(C516:H516)</f>
+        <f t="shared" si="8"/>
         <v>540</v>
       </c>
       <c r="J516" t="s">
@@ -30541,7 +30560,7 @@
         <v>85</v>
       </c>
       <c r="I517">
-        <f>SUM(C517:H517)</f>
+        <f t="shared" si="8"/>
         <v>540</v>
       </c>
       <c r="J517" t="s">
@@ -30592,7 +30611,7 @@
         <v>95</v>
       </c>
       <c r="I518">
-        <f>SUM(C518:H518)</f>
+        <f t="shared" si="8"/>
         <v>540</v>
       </c>
       <c r="J518" t="s">
@@ -30643,7 +30662,7 @@
         <v>105</v>
       </c>
       <c r="I519">
-        <f>SUM(C519:H519)</f>
+        <f t="shared" si="8"/>
         <v>540</v>
       </c>
       <c r="J519" t="s">
@@ -30694,7 +30713,7 @@
         <v>125</v>
       </c>
       <c r="I520">
-        <f>SUM(C520:H520)</f>
+        <f t="shared" si="8"/>
         <v>540</v>
       </c>
       <c r="J520" t="s">
@@ -30745,7 +30764,7 @@
         <v>100</v>
       </c>
       <c r="I521">
-        <f>SUM(C521:H521)</f>
+        <f t="shared" si="8"/>
         <v>545</v>
       </c>
       <c r="J521" t="s">
@@ -30796,7 +30815,7 @@
         <v>115</v>
       </c>
       <c r="I522">
-        <f>SUM(C522:H522)</f>
+        <f t="shared" si="8"/>
         <v>545</v>
       </c>
       <c r="J522" t="s">
@@ -30847,7 +30866,7 @@
         <v>80</v>
       </c>
       <c r="I523">
-        <f>SUM(C523:H523)</f>
+        <f t="shared" si="8"/>
         <v>550</v>
       </c>
       <c r="J523" t="s">
@@ -30898,7 +30917,7 @@
         <v>80</v>
       </c>
       <c r="I524">
-        <f>SUM(C524:H524)</f>
+        <f t="shared" si="8"/>
         <v>555</v>
       </c>
       <c r="J524" t="s">
@@ -30949,7 +30968,7 @@
         <v>80</v>
       </c>
       <c r="I525">
-        <f>SUM(C525:H525)</f>
+        <f t="shared" si="8"/>
         <v>555</v>
       </c>
       <c r="J525" t="s">
@@ -31000,7 +31019,7 @@
         <v>65</v>
       </c>
       <c r="I526">
-        <f>SUM(C526:H526)</f>
+        <f t="shared" si="8"/>
         <v>555</v>
       </c>
       <c r="J526" t="s">
@@ -31051,7 +31070,7 @@
         <v>125</v>
       </c>
       <c r="I527">
-        <f>SUM(C527:H527)</f>
+        <f t="shared" si="8"/>
         <v>580</v>
       </c>
       <c r="J527" t="s">
@@ -31102,7 +31121,7 @@
         <v>90</v>
       </c>
       <c r="I528">
-        <f>SUM(C528:H528)</f>
+        <f t="shared" si="8"/>
         <v>580</v>
       </c>
       <c r="J528" t="s">
@@ -31153,7 +31172,7 @@
         <v>85</v>
       </c>
       <c r="I529">
-        <f>SUM(C529:H529)</f>
+        <f t="shared" si="8"/>
         <v>580</v>
       </c>
       <c r="J529" t="s">
@@ -31204,7 +31223,7 @@
         <v>100</v>
       </c>
       <c r="I530">
-        <f>SUM(C530:H530)</f>
+        <f t="shared" si="8"/>
         <v>580</v>
       </c>
       <c r="J530" t="s">
@@ -31255,7 +31274,7 @@
         <v>90</v>
       </c>
       <c r="I531">
-        <f>SUM(C531:H531)</f>
+        <f t="shared" si="8"/>
         <v>580</v>
       </c>
       <c r="J531" t="s">
@@ -31306,7 +31325,7 @@
         <v>125</v>
       </c>
       <c r="I532">
-        <f>SUM(C532:H532)</f>
+        <f t="shared" si="8"/>
         <v>580</v>
       </c>
       <c r="J532" t="s">
@@ -31357,7 +31376,7 @@
         <v>100</v>
       </c>
       <c r="I533">
-        <f>SUM(C533:H533)</f>
+        <f t="shared" si="8"/>
         <v>580</v>
       </c>
       <c r="J533" t="s">
@@ -31408,7 +31427,7 @@
         <v>75</v>
       </c>
       <c r="I534">
-        <f>SUM(C534:H534)</f>
+        <f t="shared" si="8"/>
         <v>580</v>
       </c>
       <c r="J534" t="s">
@@ -31459,7 +31478,7 @@
         <v>115</v>
       </c>
       <c r="I535">
-        <f>SUM(C535:H535)</f>
+        <f t="shared" si="8"/>
         <v>580</v>
       </c>
       <c r="J535" t="s">
@@ -31510,7 +31529,7 @@
         <v>100</v>
       </c>
       <c r="I536">
-        <f>SUM(C536:H536)</f>
+        <f t="shared" si="8"/>
         <v>580</v>
       </c>
       <c r="J536" t="s">
@@ -31561,7 +31580,7 @@
         <v>200</v>
       </c>
       <c r="I537">
-        <f>SUM(C537:H537)</f>
+        <f t="shared" si="8"/>
         <v>580</v>
       </c>
       <c r="J537" t="s">
@@ -31612,7 +31631,7 @@
         <v>150</v>
       </c>
       <c r="I538">
-        <f>SUM(C538:H538)</f>
+        <f t="shared" si="8"/>
         <v>580</v>
       </c>
       <c r="J538" t="s">
@@ -31663,7 +31682,7 @@
         <v>130</v>
       </c>
       <c r="I539">
-        <f>SUM(C539:H539)</f>
+        <f t="shared" si="8"/>
         <v>580</v>
       </c>
       <c r="J539" t="s">
@@ -31714,7 +31733,7 @@
         <v>105</v>
       </c>
       <c r="I540">
-        <f>SUM(C540:H540)</f>
+        <f t="shared" si="8"/>
         <v>580</v>
       </c>
       <c r="J540" t="s">
@@ -31765,7 +31784,7 @@
         <v>70</v>
       </c>
       <c r="I541">
-        <f>SUM(C541:H541)</f>
+        <f t="shared" si="8"/>
         <v>580</v>
       </c>
       <c r="J541" t="s">
@@ -31816,7 +31835,7 @@
         <v>100</v>
       </c>
       <c r="I542">
-        <f>SUM(C542:H542)</f>
+        <f t="shared" si="8"/>
         <v>600</v>
       </c>
       <c r="J542" t="s">
@@ -31867,7 +31886,7 @@
         <v>100</v>
       </c>
       <c r="I543">
-        <f>SUM(C543:H543)</f>
+        <f t="shared" si="8"/>
         <v>600</v>
       </c>
       <c r="J543" t="s">
@@ -31918,7 +31937,7 @@
         <v>100</v>
       </c>
       <c r="I544">
-        <f>SUM(C544:H544)</f>
+        <f t="shared" si="8"/>
         <v>600</v>
       </c>
       <c r="J544" t="s">
@@ -31969,7 +31988,7 @@
         <v>100</v>
       </c>
       <c r="I545">
-        <f>SUM(C545:H545)</f>
+        <f t="shared" si="8"/>
         <v>600</v>
       </c>
       <c r="J545" t="s">
@@ -32020,7 +32039,7 @@
         <v>80</v>
       </c>
       <c r="I546">
-        <f>SUM(C546:H546)</f>
+        <f t="shared" si="8"/>
         <v>600</v>
       </c>
       <c r="J546" t="s">
@@ -32071,7 +32090,7 @@
         <v>90</v>
       </c>
       <c r="I547">
-        <f>SUM(C547:H547)</f>
+        <f t="shared" si="8"/>
         <v>600</v>
       </c>
       <c r="J547" t="s">
@@ -32122,7 +32141,7 @@
         <v>130</v>
       </c>
       <c r="I548">
-        <f>SUM(C548:H548)</f>
+        <f t="shared" si="8"/>
         <v>600</v>
       </c>
       <c r="J548" t="s">
@@ -32173,7 +32192,7 @@
         <v>110</v>
       </c>
       <c r="I549">
-        <f>SUM(C549:H549)</f>
+        <f t="shared" si="8"/>
         <v>600</v>
       </c>
       <c r="J549" t="s">
@@ -32224,7 +32243,7 @@
         <v>100</v>
       </c>
       <c r="I550">
-        <f>SUM(C550:H550)</f>
+        <f t="shared" si="8"/>
         <v>600</v>
       </c>
       <c r="J550" t="s">
@@ -32275,7 +32294,7 @@
         <v>50</v>
       </c>
       <c r="I551">
-        <f>SUM(C551:H551)</f>
+        <f t="shared" si="8"/>
         <v>600</v>
       </c>
       <c r="J551" t="s">
@@ -32326,7 +32345,7 @@
         <v>20</v>
       </c>
       <c r="I552">
-        <f>SUM(C552:H552)</f>
+        <f t="shared" si="8"/>
         <v>600</v>
       </c>
       <c r="J552" t="s">
@@ -32377,7 +32396,7 @@
         <v>160</v>
       </c>
       <c r="I553">
-        <f>SUM(C553:H553)</f>
+        <f t="shared" si="8"/>
         <v>600</v>
       </c>
       <c r="J553" t="s">
@@ -32428,7 +32447,7 @@
         <v>90</v>
       </c>
       <c r="I554">
-        <f>SUM(C554:H554)</f>
+        <f t="shared" si="8"/>
         <v>600</v>
       </c>
       <c r="J554" t="s">
@@ -32479,7 +32498,7 @@
         <v>85</v>
       </c>
       <c r="I555">
-        <f>SUM(C555:H555)</f>
+        <f t="shared" si="8"/>
         <v>600</v>
       </c>
       <c r="J555" t="s">
@@ -32530,7 +32549,7 @@
         <v>106</v>
       </c>
       <c r="I556">
-        <f>SUM(C556:H556)</f>
+        <f t="shared" si="8"/>
         <v>600</v>
       </c>
       <c r="J556" t="s">
@@ -32581,7 +32600,7 @@
         <v>130</v>
       </c>
       <c r="I557">
-        <f>SUM(C557:H557)</f>
+        <f t="shared" si="8"/>
         <v>600</v>
       </c>
       <c r="J557" t="s">
@@ -32632,7 +32651,7 @@
         <v>100</v>
       </c>
       <c r="I558">
-        <f>SUM(C558:H558)</f>
+        <f t="shared" si="8"/>
         <v>600</v>
       </c>
       <c r="J558" t="s">
@@ -32683,7 +32702,7 @@
         <v>90</v>
       </c>
       <c r="I559">
-        <f>SUM(C559:H559)</f>
+        <f t="shared" si="8"/>
         <v>600</v>
       </c>
       <c r="J559" t="s">
@@ -32734,7 +32753,7 @@
         <v>100</v>
       </c>
       <c r="I560">
-        <f>SUM(C560:H560)</f>
+        <f t="shared" si="8"/>
         <v>600</v>
       </c>
       <c r="J560" t="s">
@@ -32785,7 +32804,7 @@
         <v>75</v>
       </c>
       <c r="I561">
-        <f>SUM(C561:H561)</f>
+        <f t="shared" si="8"/>
         <v>600</v>
       </c>
       <c r="J561" t="s">
@@ -32836,7 +32855,7 @@
         <v>65</v>
       </c>
       <c r="I562">
-        <f>SUM(C562:H562)</f>
+        <f t="shared" si="8"/>
         <v>670</v>
       </c>
       <c r="J562" t="s">
@@ -32887,7 +32906,7 @@
         <v>140</v>
       </c>
       <c r="I563">
-        <f>SUM(C563:H563)</f>
+        <f t="shared" si="8"/>
         <v>670</v>
       </c>
       <c r="J563" t="s">
@@ -32938,7 +32957,7 @@
         <v>90</v>
       </c>
       <c r="I564">
-        <f>SUM(C564:H564)</f>
+        <f t="shared" si="8"/>
         <v>670</v>
       </c>
       <c r="J564" t="s">
@@ -32989,7 +33008,7 @@
         <v>110</v>
       </c>
       <c r="I565">
-        <f>SUM(C565:H565)</f>
+        <f t="shared" si="8"/>
         <v>670</v>
       </c>
       <c r="J565" t="s">
@@ -33040,7 +33059,7 @@
         <v>90</v>
       </c>
       <c r="I566">
-        <f>SUM(C566:H566)</f>
+        <f t="shared" si="8"/>
         <v>680</v>
       </c>
       <c r="J566" t="s">
@@ -33091,7 +33110,7 @@
         <v>154</v>
       </c>
       <c r="I567">
-        <f>SUM(C567:H567)</f>
+        <f t="shared" si="8"/>
         <v>680</v>
       </c>
       <c r="J567" t="s">
@@ -33142,7 +33161,7 @@
         <v>154</v>
       </c>
       <c r="I568">
-        <f>SUM(C568:H568)</f>
+        <f t="shared" si="8"/>
         <v>680</v>
       </c>
       <c r="J568" t="s">
@@ -33193,7 +33212,7 @@
         <v>90</v>
       </c>
       <c r="I569">
-        <f>SUM(C569:H569)</f>
+        <f t="shared" si="8"/>
         <v>680</v>
       </c>
       <c r="J569" t="s">
@@ -33244,7 +33263,7 @@
         <v>100</v>
       </c>
       <c r="I570">
-        <f>SUM(C570:H570)</f>
+        <f t="shared" si="8"/>
         <v>680</v>
       </c>
       <c r="J570" t="s">
@@ -33295,7 +33314,7 @@
         <v>120</v>
       </c>
       <c r="I571">
-        <f>SUM(C571:H571)</f>
+        <f t="shared" si="8"/>
         <v>680</v>
       </c>
       <c r="J571" t="s">
@@ -33346,7 +33365,7 @@
         <v>120</v>
       </c>
       <c r="I572">
-        <f>SUM(C572:H572)</f>
+        <f t="shared" si="8"/>
         <v>680</v>
       </c>
       <c r="J572" t="s">
@@ -33397,7 +33416,7 @@
         <v>120</v>
       </c>
       <c r="I573">
-        <f>SUM(C573:H573)</f>
+        <f t="shared" si="8"/>
         <v>680</v>
       </c>
       <c r="J573" t="s">
@@ -33448,7 +33467,7 @@
         <v>120</v>
       </c>
       <c r="I574">
-        <f>SUM(C574:H574)</f>
+        <f t="shared" si="8"/>
         <v>680</v>
       </c>
       <c r="J574" t="s">
@@ -33499,7 +33518,7 @@
         <v>100</v>
       </c>
       <c r="I575">
-        <f>SUM(C575:H575)</f>
+        <f t="shared" si="8"/>
         <v>680</v>
       </c>
       <c r="J575" t="s">
@@ -33526,14 +33545,10 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:P575" xr:uid="{DA2BF836-2FD5-4520-BC72-6D688307FCF3}">
-    <filterColumn colId="11">
-      <filters>
-        <filter val="GROWTH_FLUCTUATING"/>
-      </filters>
-    </filterColumn>
     <filterColumn colId="15">
       <filters>
-        <filter val="Y"/>
+        <filter val="M"/>
+        <filter val="R"/>
       </filters>
     </filterColumn>
   </autoFilter>
